--- a/Terminefussball_2026_Frühjahr.xlsx
+++ b/Terminefussball_2026_Frühjahr.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DTB\asv-neufeld\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4752F430-6655-4FC0-946F-0EDD8E6EDB11}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94038BA8-A699-4A8A-B481-C96524DA503D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -978,7 +978,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="125">
+  <cellXfs count="126">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1266,6 +1266,7 @@
     <xf numFmtId="0" fontId="6" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
@@ -3861,6 +3862,7 @@
     <col min="4" max="4" width="8.33203125" style="39" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="11.44140625" style="39"/>
     <col min="6" max="6" width="14.44140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.5546875" style="125"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.3">
@@ -3882,7 +3884,7 @@
       <c r="F1" t="s">
         <v>141</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="125" t="s">
         <v>135</v>
       </c>
       <c r="H1" t="s">
@@ -3909,7 +3911,7 @@
         <f>UPPER('Nach Mannschaften sortiert'!F2)</f>
         <v>RUST</v>
       </c>
-      <c r="G2" t="str">
+      <c r="G2" s="125" t="str">
         <f>'Nach Mannschaften sortiert'!H2</f>
         <v>Auswärts</v>
       </c>
@@ -3939,7 +3941,7 @@
         <f>UPPER('Nach Mannschaften sortiert'!F3)</f>
         <v>NEUFELD</v>
       </c>
-      <c r="G3" t="str">
+      <c r="G3" s="125" t="str">
         <f>'Nach Mannschaften sortiert'!H3</f>
         <v>Heim</v>
       </c>
@@ -3969,7 +3971,7 @@
         <f>UPPER('Nach Mannschaften sortiert'!F4)</f>
         <v>GATTENDORF</v>
       </c>
-      <c r="G4" t="str">
+      <c r="G4" s="125" t="str">
         <f>'Nach Mannschaften sortiert'!H4</f>
         <v>Auswärts</v>
       </c>
@@ -3999,7 +4001,7 @@
         <f>UPPER('Nach Mannschaften sortiert'!F5)</f>
         <v>NEUFELD</v>
       </c>
-      <c r="G5" t="str">
+      <c r="G5" s="125" t="str">
         <f>'Nach Mannschaften sortiert'!H5</f>
         <v>Heim</v>
       </c>
@@ -4029,7 +4031,7 @@
         <f>UPPER('Nach Mannschaften sortiert'!F6)</f>
         <v>ANDAU</v>
       </c>
-      <c r="G6" t="str">
+      <c r="G6" s="125" t="str">
         <f>'Nach Mannschaften sortiert'!H6</f>
         <v>Auswärts</v>
       </c>
@@ -4059,7 +4061,7 @@
         <f>UPPER('Nach Mannschaften sortiert'!F7)</f>
         <v>NEUFELD</v>
       </c>
-      <c r="G7" t="str">
+      <c r="G7" s="125" t="str">
         <f>'Nach Mannschaften sortiert'!H7</f>
         <v>Heim</v>
       </c>
@@ -4089,7 +4091,7 @@
         <f>UPPER('Nach Mannschaften sortiert'!F8)</f>
         <v>DEUTSCH JAHRNDORF</v>
       </c>
-      <c r="G8" t="str">
+      <c r="G8" s="125" t="str">
         <f>'Nach Mannschaften sortiert'!H8</f>
         <v>Auswärts</v>
       </c>
@@ -4119,7 +4121,7 @@
         <f>UPPER('Nach Mannschaften sortiert'!F9)</f>
         <v>NEUFELD</v>
       </c>
-      <c r="G9" t="str">
+      <c r="G9" s="125" t="str">
         <f>'Nach Mannschaften sortiert'!H9</f>
         <v>Heim</v>
       </c>
@@ -4149,7 +4151,7 @@
         <f>UPPER('Nach Mannschaften sortiert'!F10)</f>
         <v>GOLS</v>
       </c>
-      <c r="G10" t="str">
+      <c r="G10" s="125" t="str">
         <f>'Nach Mannschaften sortiert'!H10</f>
         <v>Auswärts</v>
       </c>
@@ -4179,7 +4181,7 @@
         <f>UPPER('Nach Mannschaften sortiert'!F11)</f>
         <v>NEUFELD</v>
       </c>
-      <c r="G11" t="str">
+      <c r="G11" s="125" t="str">
         <f>'Nach Mannschaften sortiert'!H11</f>
         <v>Heim</v>
       </c>
@@ -4209,7 +4211,7 @@
         <f>UPPER('Nach Mannschaften sortiert'!F12)</f>
         <v>WIMPASSING</v>
       </c>
-      <c r="G12" t="str">
+      <c r="G12" s="125" t="str">
         <f>'Nach Mannschaften sortiert'!H12</f>
         <v>Auswärts</v>
       </c>
@@ -4239,7 +4241,7 @@
         <f>UPPER('Nach Mannschaften sortiert'!F13)</f>
         <v>WINDEN</v>
       </c>
-      <c r="G13" t="str">
+      <c r="G13" s="125" t="str">
         <f>'Nach Mannschaften sortiert'!H13</f>
         <v>Auswärts</v>
       </c>
@@ -4269,7 +4271,7 @@
         <f>UPPER('Nach Mannschaften sortiert'!F14)</f>
         <v>NEUFELD</v>
       </c>
-      <c r="G14" t="str">
+      <c r="G14" s="125" t="str">
         <f>'Nach Mannschaften sortiert'!H14</f>
         <v>Heim</v>
       </c>
@@ -4299,7 +4301,7 @@
         <f>UPPER('Nach Mannschaften sortiert'!F15)</f>
         <v>RUST</v>
       </c>
-      <c r="G15" t="str">
+      <c r="G15" s="125" t="str">
         <f>'Nach Mannschaften sortiert'!H15</f>
         <v>Auswärts</v>
       </c>
@@ -4329,7 +4331,7 @@
         <f>UPPER('Nach Mannschaften sortiert'!F16)</f>
         <v>NEUFELD</v>
       </c>
-      <c r="G16" t="str">
+      <c r="G16" s="125" t="str">
         <f>'Nach Mannschaften sortiert'!H16</f>
         <v>Heim</v>
       </c>
@@ -4359,7 +4361,7 @@
         <f>UPPER('Nach Mannschaften sortiert'!F17)</f>
         <v>GATTENDORF</v>
       </c>
-      <c r="G17" t="str">
+      <c r="G17" s="125" t="str">
         <f>'Nach Mannschaften sortiert'!H17</f>
         <v>Auswärts</v>
       </c>
@@ -4389,7 +4391,7 @@
         <f>UPPER('Nach Mannschaften sortiert'!F18)</f>
         <v>NEUFELD</v>
       </c>
-      <c r="G18" t="str">
+      <c r="G18" s="125" t="str">
         <f>'Nach Mannschaften sortiert'!H18</f>
         <v>Heim</v>
       </c>
@@ -4419,7 +4421,7 @@
         <f>UPPER('Nach Mannschaften sortiert'!F19)</f>
         <v>ANDAU</v>
       </c>
-      <c r="G19" t="str">
+      <c r="G19" s="125" t="str">
         <f>'Nach Mannschaften sortiert'!H19</f>
         <v>Auswärts</v>
       </c>
@@ -4449,7 +4451,7 @@
         <f>UPPER('Nach Mannschaften sortiert'!F20)</f>
         <v>NEUFELD</v>
       </c>
-      <c r="G20" t="str">
+      <c r="G20" s="125" t="str">
         <f>'Nach Mannschaften sortiert'!H20</f>
         <v>Heim</v>
       </c>
@@ -4479,7 +4481,7 @@
         <f>UPPER('Nach Mannschaften sortiert'!F21)</f>
         <v>DEUTSCH JAHRNDORF</v>
       </c>
-      <c r="G21" t="str">
+      <c r="G21" s="125" t="str">
         <f>'Nach Mannschaften sortiert'!H21</f>
         <v>Auswärts</v>
       </c>
@@ -4509,7 +4511,7 @@
         <f>UPPER('Nach Mannschaften sortiert'!F22)</f>
         <v>NEUFELD</v>
       </c>
-      <c r="G22" t="str">
+      <c r="G22" s="125" t="str">
         <f>'Nach Mannschaften sortiert'!H22</f>
         <v>Heim</v>
       </c>
@@ -4539,7 +4541,7 @@
         <f>UPPER('Nach Mannschaften sortiert'!F23)</f>
         <v>GOLS</v>
       </c>
-      <c r="G23" t="str">
+      <c r="G23" s="125" t="str">
         <f>'Nach Mannschaften sortiert'!H23</f>
         <v>Auswärts</v>
       </c>
@@ -4569,7 +4571,7 @@
         <f>UPPER('Nach Mannschaften sortiert'!F24)</f>
         <v>NEUFELD</v>
       </c>
-      <c r="G24" t="str">
+      <c r="G24" s="125" t="str">
         <f>'Nach Mannschaften sortiert'!H24</f>
         <v>Heim</v>
       </c>
@@ -4599,7 +4601,7 @@
         <f>UPPER('Nach Mannschaften sortiert'!F25)</f>
         <v>WIMPASSING</v>
       </c>
-      <c r="G25" t="str">
+      <c r="G25" s="125" t="str">
         <f>'Nach Mannschaften sortiert'!H25</f>
         <v>Auswärts</v>
       </c>
@@ -4629,7 +4631,7 @@
         <f>UPPER('Nach Mannschaften sortiert'!F26)</f>
         <v>WINDEN</v>
       </c>
-      <c r="G26" t="str">
+      <c r="G26" s="125" t="str">
         <f>'Nach Mannschaften sortiert'!H26</f>
         <v>Auswärts</v>
       </c>
@@ -4659,7 +4661,7 @@
         <f>UPPER('Nach Mannschaften sortiert'!F27)</f>
         <v>NEUFELD</v>
       </c>
-      <c r="G27" t="str">
+      <c r="G27" s="125" t="str">
         <f>'Nach Mannschaften sortiert'!H27</f>
         <v>Heim</v>
       </c>
@@ -4689,7 +4691,7 @@
         <f>UPPER('Nach Mannschaften sortiert'!F28)</f>
         <v>SV LEITHAPRODERSDORF</v>
       </c>
-      <c r="G28" t="str">
+      <c r="G28" s="125" t="str">
         <f>'Nach Mannschaften sortiert'!H28</f>
         <v>Auswärts</v>
       </c>
@@ -4719,7 +4721,7 @@
         <f>UPPER('Nach Mannschaften sortiert'!F29)</f>
         <v>WIMPASSING</v>
       </c>
-      <c r="G29" t="str">
+      <c r="G29" s="125" t="str">
         <f>'Nach Mannschaften sortiert'!H29</f>
         <v>Heim</v>
       </c>
@@ -4749,7 +4751,7 @@
         <f>UPPER('Nach Mannschaften sortiert'!F30)</f>
         <v>WOLFAU</v>
       </c>
-      <c r="G30" t="str">
+      <c r="G30" s="125" t="str">
         <f>'Nach Mannschaften sortiert'!H30</f>
         <v>Auswärts</v>
       </c>
@@ -4779,7 +4781,7 @@
         <f>UPPER('Nach Mannschaften sortiert'!F31)</f>
         <v>NEUFELD</v>
       </c>
-      <c r="G31" t="str">
+      <c r="G31" s="125" t="str">
         <f>'Nach Mannschaften sortiert'!H31</f>
         <v>Heim</v>
       </c>
@@ -4809,7 +4811,7 @@
         <f>UPPER('Nach Mannschaften sortiert'!F32)</f>
         <v>ST. GEORGEN</v>
       </c>
-      <c r="G32" t="str">
+      <c r="G32" s="125" t="str">
         <f>'Nach Mannschaften sortiert'!H32</f>
         <v>Auswärts</v>
       </c>
@@ -4839,7 +4841,7 @@
         <f>UPPER('Nach Mannschaften sortiert'!F33)</f>
         <v>WIMPASSING</v>
       </c>
-      <c r="G33" t="str">
+      <c r="G33" s="125" t="str">
         <f>'Nach Mannschaften sortiert'!H33</f>
         <v>Heim</v>
       </c>
@@ -4869,7 +4871,7 @@
         <f>UPPER('Nach Mannschaften sortiert'!F34)</f>
         <v>BERNSTEIN</v>
       </c>
-      <c r="G34" t="str">
+      <c r="G34" s="125" t="str">
         <f>'Nach Mannschaften sortiert'!H34</f>
         <v>Auswärts</v>
       </c>
@@ -4899,7 +4901,7 @@
         <f>UPPER('Nach Mannschaften sortiert'!F35)</f>
         <v>WIMPASSING</v>
       </c>
-      <c r="G35" t="str">
+      <c r="G35" s="125" t="str">
         <f>'Nach Mannschaften sortiert'!H35</f>
         <v>Heim</v>
       </c>
@@ -4929,7 +4931,7 @@
         <f>UPPER('Nach Mannschaften sortiert'!F36)</f>
         <v>KIRCHSCHLAG</v>
       </c>
-      <c r="G36" t="str">
+      <c r="G36" s="125" t="str">
         <f>'Nach Mannschaften sortiert'!H36</f>
         <v>Auswärts</v>
       </c>
@@ -4959,7 +4961,7 @@
         <f>UPPER('Nach Mannschaften sortiert'!F37)</f>
         <v>NEUFELD</v>
       </c>
-      <c r="G37" t="str">
+      <c r="G37" s="125" t="str">
         <f>'Nach Mannschaften sortiert'!H37</f>
         <v>Heim</v>
       </c>
@@ -4989,7 +4991,7 @@
         <f>UPPER('Nach Mannschaften sortiert'!F38)</f>
         <v>NEUFELD</v>
       </c>
-      <c r="G38" t="str">
+      <c r="G38" s="125" t="str">
         <f>'Nach Mannschaften sortiert'!H38</f>
         <v>Heim</v>
       </c>
@@ -5019,7 +5021,7 @@
         <f>UPPER('Nach Mannschaften sortiert'!F39)</f>
         <v>WIMPASSING</v>
       </c>
-      <c r="G39" t="str">
+      <c r="G39" s="125" t="str">
         <f>'Nach Mannschaften sortiert'!H39</f>
         <v>Heim</v>
       </c>
@@ -5049,7 +5051,7 @@
         <f>UPPER('Nach Mannschaften sortiert'!F40)</f>
         <v>NEUSIEDL</v>
       </c>
-      <c r="G40" t="str">
+      <c r="G40" s="125" t="str">
         <f>'Nach Mannschaften sortiert'!H40</f>
         <v>Auswärts</v>
       </c>
@@ -5079,7 +5081,7 @@
         <f>UPPER('Nach Mannschaften sortiert'!F41)</f>
         <v>NEUFELD</v>
       </c>
-      <c r="G41" t="str">
+      <c r="G41" s="125" t="str">
         <f>'Nach Mannschaften sortiert'!H41</f>
         <v>Heim</v>
       </c>
@@ -5109,7 +5111,7 @@
         <f>UPPER('Nach Mannschaften sortiert'!F42)</f>
         <v>PARNDORF</v>
       </c>
-      <c r="G42" t="str">
+      <c r="G42" s="125" t="str">
         <f>'Nach Mannschaften sortiert'!H42</f>
         <v>Auswärts</v>
       </c>
@@ -5139,7 +5141,7 @@
         <f>UPPER('Nach Mannschaften sortiert'!F43)</f>
         <v>GROßHÖFLEIN</v>
       </c>
-      <c r="G43" t="str">
+      <c r="G43" s="125" t="str">
         <f>'Nach Mannschaften sortiert'!H43</f>
         <v>Auswärts</v>
       </c>
@@ -5169,7 +5171,7 @@
         <f>UPPER('Nach Mannschaften sortiert'!F44)</f>
         <v>WIMPASSING</v>
       </c>
-      <c r="G44" t="str">
+      <c r="G44" s="125" t="str">
         <f>'Nach Mannschaften sortiert'!H44</f>
         <v>Heim</v>
       </c>
@@ -5199,7 +5201,7 @@
         <f>UPPER('Nach Mannschaften sortiert'!F45)</f>
         <v>WIESEN</v>
       </c>
-      <c r="G45" t="str">
+      <c r="G45" s="125" t="str">
         <f>'Nach Mannschaften sortiert'!H45</f>
         <v>Auswärts</v>
       </c>
@@ -5229,7 +5231,7 @@
         <f>UPPER('Nach Mannschaften sortiert'!F46)</f>
         <v>NEUFELD</v>
       </c>
-      <c r="G46" t="str">
+      <c r="G46" s="125" t="str">
         <f>'Nach Mannschaften sortiert'!H46</f>
         <v>Heim</v>
       </c>
@@ -5259,7 +5261,7 @@
         <f>UPPER('Nach Mannschaften sortiert'!F47)</f>
         <v>PAMA</v>
       </c>
-      <c r="G47" t="str">
+      <c r="G47" s="125" t="str">
         <f>'Nach Mannschaften sortiert'!H47</f>
         <v>Auswärts</v>
       </c>
@@ -5289,7 +5291,7 @@
         <f>UPPER('Nach Mannschaften sortiert'!F48)</f>
         <v>KITTSEE</v>
       </c>
-      <c r="G48" t="str">
+      <c r="G48" s="125" t="str">
         <f>'Nach Mannschaften sortiert'!H48</f>
         <v>Auswärts</v>
       </c>
@@ -5319,7 +5321,7 @@
         <f>UPPER('Nach Mannschaften sortiert'!F49)</f>
         <v>NEUFELD</v>
       </c>
-      <c r="G49" t="str">
+      <c r="G49" s="125" t="str">
         <f>'Nach Mannschaften sortiert'!H49</f>
         <v>Heim</v>
       </c>
@@ -5349,7 +5351,7 @@
         <f>UPPER('Nach Mannschaften sortiert'!F50)</f>
         <v>WULKAPRODERSDORF</v>
       </c>
-      <c r="G50" t="str">
+      <c r="G50" s="125" t="str">
         <f>'Nach Mannschaften sortiert'!H50</f>
         <v>Auswärts</v>
       </c>
@@ -5379,7 +5381,7 @@
         <f>UPPER('Nach Mannschaften sortiert'!F51)</f>
         <v>NEUFELD</v>
       </c>
-      <c r="G51" t="str">
+      <c r="G51" s="125" t="str">
         <f>'Nach Mannschaften sortiert'!H51</f>
         <v>Heim</v>
       </c>
@@ -5409,7 +5411,7 @@
         <f>UPPER('Nach Mannschaften sortiert'!F52)</f>
         <v>NEUFELD</v>
       </c>
-      <c r="G52" t="str">
+      <c r="G52" s="125" t="str">
         <f>'Nach Mannschaften sortiert'!H52</f>
         <v>Heim</v>
       </c>
@@ -5439,7 +5441,7 @@
         <f>UPPER('Nach Mannschaften sortiert'!F53)</f>
         <v>LEITHAPRODERSDORF</v>
       </c>
-      <c r="G53" t="str">
+      <c r="G53" s="125" t="str">
         <f>'Nach Mannschaften sortiert'!H53</f>
         <v>Auswärts</v>
       </c>
@@ -5469,7 +5471,7 @@
         <f>UPPER('Nach Mannschaften sortiert'!F54)</f>
         <v>NEUFELD</v>
       </c>
-      <c r="G54" t="str">
+      <c r="G54" s="125" t="str">
         <f>'Nach Mannschaften sortiert'!H54</f>
         <v>Heim</v>
       </c>
@@ -5499,7 +5501,7 @@
         <f>UPPER('Nach Mannschaften sortiert'!F55)</f>
         <v>RUST</v>
       </c>
-      <c r="G55" t="str">
+      <c r="G55" s="125" t="str">
         <f>'Nach Mannschaften sortiert'!H55</f>
         <v>Auswärts</v>
       </c>
@@ -5529,7 +5531,7 @@
         <f>UPPER('Nach Mannschaften sortiert'!F56)</f>
         <v>NEUFELD</v>
       </c>
-      <c r="G56" t="str">
+      <c r="G56" s="125" t="str">
         <f>'Nach Mannschaften sortiert'!H56</f>
         <v>Heim</v>
       </c>
@@ -5559,7 +5561,7 @@
         <f>UPPER('Nach Mannschaften sortiert'!F57)</f>
         <v>LEITHAPRODERSDORF</v>
       </c>
-      <c r="G57" t="str">
+      <c r="G57" s="125" t="str">
         <f>'Nach Mannschaften sortiert'!H57</f>
         <v>Auswärts</v>
       </c>
@@ -5589,7 +5591,7 @@
         <f>UPPER('Nach Mannschaften sortiert'!F58)</f>
         <v>KITTSEE</v>
       </c>
-      <c r="G58" t="str">
+      <c r="G58" s="125" t="str">
         <f>'Nach Mannschaften sortiert'!H58</f>
         <v>Auswärts</v>
       </c>
@@ -5619,7 +5621,7 @@
         <f>UPPER('Nach Mannschaften sortiert'!F59)</f>
         <v>NEUFELD</v>
       </c>
-      <c r="G59" t="str">
+      <c r="G59" s="125" t="str">
         <f>'Nach Mannschaften sortiert'!H59</f>
         <v>Heim</v>
       </c>
@@ -5649,7 +5651,7 @@
         <f>UPPER('Nach Mannschaften sortiert'!F60)</f>
         <v>BREITENBRUNN</v>
       </c>
-      <c r="G60" t="str">
+      <c r="G60" s="125" t="str">
         <f>'Nach Mannschaften sortiert'!H60</f>
         <v>Auswärts</v>
       </c>
@@ -5679,7 +5681,7 @@
         <f>UPPER('Nach Mannschaften sortiert'!F61)</f>
         <v>NEUFELD</v>
       </c>
-      <c r="G61" t="str">
+      <c r="G61" s="125" t="str">
         <f>'Nach Mannschaften sortiert'!H61</f>
         <v>Heim</v>
       </c>
@@ -5709,7 +5711,7 @@
         <f>UPPER('Nach Mannschaften sortiert'!F62)</f>
         <v>STEINBRUNN</v>
       </c>
-      <c r="G62" t="str">
+      <c r="G62" s="125" t="str">
         <f>'Nach Mannschaften sortiert'!H62</f>
         <v>Auswärts</v>
       </c>
@@ -5739,7 +5741,7 @@
         <f>UPPER('Nach Mannschaften sortiert'!F63)</f>
         <v>NEUFELD</v>
       </c>
-      <c r="G63" t="str">
+      <c r="G63" s="125" t="str">
         <f>'Nach Mannschaften sortiert'!H63</f>
         <v>Heim</v>
       </c>
@@ -5769,7 +5771,7 @@
         <f>UPPER('Nach Mannschaften sortiert'!F64)</f>
         <v>KLINGENBACH</v>
       </c>
-      <c r="G64" t="str">
+      <c r="G64" s="125" t="str">
         <f>'Nach Mannschaften sortiert'!H64</f>
         <v>Auswärts</v>
       </c>
@@ -5799,7 +5801,7 @@
         <f>UPPER('Nach Mannschaften sortiert'!F65)</f>
         <v>NEUFELD</v>
       </c>
-      <c r="G65" t="str">
+      <c r="G65" s="125" t="str">
         <f>'Nach Mannschaften sortiert'!H65</f>
         <v>Heim</v>
       </c>
@@ -5829,7 +5831,7 @@
         <f>UPPER('Nach Mannschaften sortiert'!F66)</f>
         <v>NEUFELD</v>
       </c>
-      <c r="G66" t="str">
+      <c r="G66" s="125" t="str">
         <f>'Nach Mannschaften sortiert'!H66</f>
         <v>Heim</v>
       </c>
@@ -5859,7 +5861,7 @@
         <f>UPPER('Nach Mannschaften sortiert'!F67)</f>
         <v>ST. MARGARETHEN</v>
       </c>
-      <c r="G67" t="str">
+      <c r="G67" s="125" t="str">
         <f>'Nach Mannschaften sortiert'!H67</f>
         <v>Auswärts</v>
       </c>
@@ -5889,7 +5891,7 @@
         <f>UPPER('Nach Mannschaften sortiert'!F68)</f>
         <v>NEUFELD</v>
       </c>
-      <c r="G68" t="str">
+      <c r="G68" s="125" t="str">
         <f>'Nach Mannschaften sortiert'!H68</f>
         <v>Heim</v>
       </c>
@@ -5919,7 +5921,7 @@
         <f>UPPER('Nach Mannschaften sortiert'!F69)</f>
         <v>STOTZING</v>
       </c>
-      <c r="G69" t="str">
+      <c r="G69" s="125" t="str">
         <f>'Nach Mannschaften sortiert'!H69</f>
         <v>Auswärts</v>
       </c>
@@ -5949,7 +5951,7 @@
         <f>UPPER('Nach Mannschaften sortiert'!F70)</f>
         <v>NEUFELD</v>
       </c>
-      <c r="G70" t="str">
+      <c r="G70" s="125" t="str">
         <f>'Nach Mannschaften sortiert'!H70</f>
         <v>Heim</v>
       </c>
@@ -5979,7 +5981,7 @@
         <f>UPPER('Nach Mannschaften sortiert'!F71)</f>
         <v>STEINBRUNN</v>
       </c>
-      <c r="G71" t="str">
+      <c r="G71" s="125" t="str">
         <f>'Nach Mannschaften sortiert'!H71</f>
         <v>Auswärts</v>
       </c>
@@ -6009,7 +6011,7 @@
         <f>UPPER('Nach Mannschaften sortiert'!F72)</f>
         <v>SIEGENDORF</v>
       </c>
-      <c r="G72" t="str">
+      <c r="G72" s="125" t="str">
         <f>'Nach Mannschaften sortiert'!H72</f>
         <v>Auswärts</v>
       </c>
@@ -6039,7 +6041,7 @@
         <f>UPPER('Nach Mannschaften sortiert'!F73)</f>
         <v>LEITHAPRODERSDORF</v>
       </c>
-      <c r="G73" t="str">
+      <c r="G73" s="125" t="str">
         <f>'Nach Mannschaften sortiert'!H73</f>
         <v>Auswärts</v>
       </c>
@@ -6069,7 +6071,7 @@
         <f>UPPER('Nach Mannschaften sortiert'!F74)</f>
         <v>ST. GEORGEN</v>
       </c>
-      <c r="G74" t="str">
+      <c r="G74" s="125" t="str">
         <f>'Nach Mannschaften sortiert'!H74</f>
         <v>Auswärts</v>
       </c>
@@ -6099,7 +6101,7 @@
         <f>UPPER('Nach Mannschaften sortiert'!F75)</f>
         <v>NEUFELD</v>
       </c>
-      <c r="G75" t="str">
+      <c r="G75" s="125" t="str">
         <f>'Nach Mannschaften sortiert'!H75</f>
         <v>Heim</v>
       </c>
@@ -6129,7 +6131,7 @@
         <f>UPPER('Nach Mannschaften sortiert'!F76)</f>
         <v>SIEGENDORF</v>
       </c>
-      <c r="G76" t="str">
+      <c r="G76" s="125" t="str">
         <f>'Nach Mannschaften sortiert'!H76</f>
         <v>Auswärts</v>
       </c>
@@ -6159,7 +6161,7 @@
         <f>UPPER('Nach Mannschaften sortiert'!F77)</f>
         <v>PURBACH</v>
       </c>
-      <c r="G77" t="str">
+      <c r="G77" s="125" t="str">
         <f>'Nach Mannschaften sortiert'!H77</f>
         <v>Auswärts</v>
       </c>
@@ -6189,7 +6191,7 @@
         <f>UPPER('Nach Mannschaften sortiert'!F78)</f>
         <v>LEITHAPRODERSDORF</v>
       </c>
-      <c r="G78" t="str">
+      <c r="G78" s="125" t="str">
         <f>'Nach Mannschaften sortiert'!H78</f>
         <v>Auswärts</v>
       </c>
@@ -6219,7 +6221,7 @@
         <f>UPPER('Nach Mannschaften sortiert'!F79)</f>
         <v>ST. GEORGEN</v>
       </c>
-      <c r="G79" t="str">
+      <c r="G79" s="125" t="str">
         <f>'Nach Mannschaften sortiert'!H79</f>
         <v>Auswärts</v>
       </c>
@@ -6249,7 +6251,7 @@
         <f>UPPER('Nach Mannschaften sortiert'!F80)</f>
         <v>NEUFELD</v>
       </c>
-      <c r="G80" t="str">
+      <c r="G80" s="125" t="str">
         <f>'Nach Mannschaften sortiert'!H80</f>
         <v>Heim</v>
       </c>
@@ -6279,7 +6281,7 @@
         <f>UPPER('Nach Mannschaften sortiert'!F81)</f>
         <v>EISENSTADT</v>
       </c>
-      <c r="G81" t="str">
+      <c r="G81" s="125" t="str">
         <f>'Nach Mannschaften sortiert'!H81</f>
         <v>Auswärts</v>
       </c>
@@ -6309,7 +6311,7 @@
         <f>UPPER('Nach Mannschaften sortiert'!F82)</f>
         <v>WULKAPRODERSDORF</v>
       </c>
-      <c r="G82" t="str">
+      <c r="G82" s="125" t="str">
         <f>'Nach Mannschaften sortiert'!H82</f>
         <v>Auswärts</v>
       </c>
@@ -6339,7 +6341,7 @@
         <f>UPPER('Nach Mannschaften sortiert'!F83)</f>
         <v>WIMPASSING</v>
       </c>
-      <c r="G83" t="str">
+      <c r="G83" s="125" t="str">
         <f>'Nach Mannschaften sortiert'!H83</f>
         <v>Auswärts</v>
       </c>
@@ -6369,7 +6371,7 @@
         <f>UPPER('Nach Mannschaften sortiert'!F84)</f>
         <v>ST. GEORGEN</v>
       </c>
-      <c r="G84" t="str">
+      <c r="G84" s="125" t="str">
         <f>'Nach Mannschaften sortiert'!H84</f>
         <v>Auswärts</v>
       </c>
@@ -6398,7 +6400,7 @@
         <f>UPPER('Nach Mannschaften sortiert'!F85)</f>
         <v>NEUFELD</v>
       </c>
-      <c r="G85" t="str">
+      <c r="G85" s="125" t="str">
         <f>'Nach Mannschaften sortiert'!H85</f>
         <v>Heim</v>
       </c>
@@ -6427,7 +6429,7 @@
         <f>UPPER('Nach Mannschaften sortiert'!F86)</f>
         <v>NEUFELD</v>
       </c>
-      <c r="G86" t="str">
+      <c r="G86" s="125" t="str">
         <f>'Nach Mannschaften sortiert'!H86</f>
         <v>Heim</v>
       </c>
@@ -6456,7 +6458,7 @@
         <f>UPPER('Nach Mannschaften sortiert'!F87)</f>
         <v>NEUFELD</v>
       </c>
-      <c r="G87" t="str">
+      <c r="G87" s="125" t="str">
         <f>'Nach Mannschaften sortiert'!H87</f>
         <v>Heim</v>
       </c>
@@ -6485,7 +6487,7 @@
         <f>UPPER('Nach Mannschaften sortiert'!F88)</f>
         <v>NEUFELD</v>
       </c>
-      <c r="G88" t="str">
+      <c r="G88" s="125" t="str">
         <f>'Nach Mannschaften sortiert'!H88</f>
         <v>Heim</v>
       </c>
@@ -6514,7 +6516,7 @@
         <f>UPPER('Nach Mannschaften sortiert'!F89)</f>
         <v>NEUFELD</v>
       </c>
-      <c r="G89" t="str">
+      <c r="G89" s="125" t="str">
         <f>'Nach Mannschaften sortiert'!H89</f>
         <v>Heim</v>
       </c>

--- a/Terminefussball_2026_Frühjahr.xlsx
+++ b/Terminefussball_2026_Frühjahr.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DTB\asv-neufeld\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94038BA8-A699-4A8A-B481-C96524DA503D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{404E1852-B9DA-4D3B-B326-5178DED93246}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="553" uniqueCount="144">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="555" uniqueCount="145">
   <si>
     <t>Mannschaft</t>
   </si>
@@ -476,6 +476,9 @@
   </si>
   <si>
     <t>GGG</t>
+  </si>
+  <si>
+    <t>ABGESAGT!!!</t>
   </si>
 </sst>
 </file>
@@ -4824,7 +4827,7 @@
         <v>U16</v>
       </c>
     </row>
-    <row r="33" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B33" s="105">
         <f>'Nach Mannschaften sortiert'!D33</f>
         <v>46151</v>
@@ -4854,7 +4857,7 @@
         <v>U16</v>
       </c>
     </row>
-    <row r="34" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B34" s="105">
         <f>'Nach Mannschaften sortiert'!D34</f>
         <v>46159</v>
@@ -4884,7 +4887,7 @@
         <v>U16</v>
       </c>
     </row>
-    <row r="35" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B35" s="105">
         <f>'Nach Mannschaften sortiert'!D35</f>
         <v>46102</v>
@@ -4914,7 +4917,7 @@
         <v>U16</v>
       </c>
     </row>
-    <row r="36" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B36" s="105">
         <f>'Nach Mannschaften sortiert'!D36</f>
         <v>46173</v>
@@ -4944,7 +4947,7 @@
         <v>U16</v>
       </c>
     </row>
-    <row r="37" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B37" s="105">
         <f>'Nach Mannschaften sortiert'!D37</f>
         <v>46180</v>
@@ -4974,7 +4977,7 @@
         <v>U16</v>
       </c>
     </row>
-    <row r="38" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B38" s="105">
         <f>'Nach Mannschaften sortiert'!D38</f>
         <v>46124</v>
@@ -5004,7 +5007,7 @@
         <v>U15</v>
       </c>
     </row>
-    <row r="39" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B39" s="105">
         <f>'Nach Mannschaften sortiert'!D39</f>
         <v>46128</v>
@@ -5034,7 +5037,7 @@
         <v>U15</v>
       </c>
     </row>
-    <row r="40" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B40" s="105">
         <f>'Nach Mannschaften sortiert'!D40</f>
         <v>46137</v>
@@ -5064,7 +5067,7 @@
         <v>U15</v>
       </c>
     </row>
-    <row r="41" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B41" s="105">
         <f>'Nach Mannschaften sortiert'!D41</f>
         <v>46145</v>
@@ -5094,7 +5097,7 @@
         <v>U15</v>
       </c>
     </row>
-    <row r="42" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B42" s="105">
         <f>'Nach Mannschaften sortiert'!D42</f>
         <v>46157</v>
@@ -5124,7 +5127,7 @@
         <v>U15</v>
       </c>
     </row>
-    <row r="43" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B43" s="105">
         <f>'Nach Mannschaften sortiert'!D43</f>
         <v>46165</v>
@@ -5154,7 +5157,7 @@
         <v>U15</v>
       </c>
     </row>
-    <row r="44" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B44" s="105">
         <f>'Nach Mannschaften sortiert'!D44</f>
         <v>46173</v>
@@ -5184,7 +5187,7 @@
         <v>U15</v>
       </c>
     </row>
-    <row r="45" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B45" s="105">
         <f>'Nach Mannschaften sortiert'!D45</f>
         <v>46179</v>
@@ -5214,7 +5217,10 @@
         <v>U15</v>
       </c>
     </row>
-    <row r="46" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A46" t="s">
+        <v>144</v>
+      </c>
       <c r="B46" s="105">
         <f>'Nach Mannschaften sortiert'!D46</f>
         <v>46109</v>
@@ -5244,7 +5250,7 @@
         <v>U14</v>
       </c>
     </row>
-    <row r="47" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B47" s="105">
         <f>'Nach Mannschaften sortiert'!D47</f>
         <v>46122</v>
@@ -5274,7 +5280,7 @@
         <v>U14</v>
       </c>
     </row>
-    <row r="48" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B48" s="105">
         <f>'Nach Mannschaften sortiert'!D48</f>
         <v>46131</v>
@@ -5304,7 +5310,7 @@
         <v>U14</v>
       </c>
     </row>
-    <row r="49" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B49" s="105">
         <f>'Nach Mannschaften sortiert'!D49</f>
         <v>46137</v>
@@ -5334,7 +5340,7 @@
         <v>U14</v>
       </c>
     </row>
-    <row r="50" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B50" s="105">
         <f>'Nach Mannschaften sortiert'!D50</f>
         <v>46151</v>
@@ -5364,7 +5370,7 @@
         <v>U14</v>
       </c>
     </row>
-    <row r="51" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B51" s="105">
         <f>'Nach Mannschaften sortiert'!D51</f>
         <v>46158</v>
@@ -5394,7 +5400,7 @@
         <v>U14</v>
       </c>
     </row>
-    <row r="52" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B52" s="105">
         <f>'Nach Mannschaften sortiert'!D52</f>
         <v>46163</v>
@@ -5424,7 +5430,7 @@
         <v>U14</v>
       </c>
     </row>
-    <row r="53" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B53" s="105">
         <f>'Nach Mannschaften sortiert'!D53</f>
         <v>46171</v>
@@ -5454,7 +5460,10 @@
         <v>U14</v>
       </c>
     </row>
-    <row r="54" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A54" t="s">
+        <v>144</v>
+      </c>
       <c r="B54" s="105">
         <f>'Nach Mannschaften sortiert'!D54</f>
         <v>46110</v>
@@ -5484,7 +5493,7 @@
         <v>U13</v>
       </c>
     </row>
-    <row r="55" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B55" s="105">
         <f>'Nach Mannschaften sortiert'!D55</f>
         <v>46130</v>
@@ -5514,7 +5523,7 @@
         <v>U13</v>
       </c>
     </row>
-    <row r="56" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B56" s="105">
         <f>'Nach Mannschaften sortiert'!D56</f>
         <v>46138</v>
@@ -5544,7 +5553,7 @@
         <v>U13</v>
       </c>
     </row>
-    <row r="57" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B57" s="105">
         <f>'Nach Mannschaften sortiert'!D57</f>
         <v>46145</v>
@@ -5574,7 +5583,7 @@
         <v>U13</v>
       </c>
     </row>
-    <row r="58" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B58" s="105">
         <f>'Nach Mannschaften sortiert'!D58</f>
         <v>46151</v>
@@ -5604,7 +5613,7 @@
         <v>U13</v>
       </c>
     </row>
-    <row r="59" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B59" s="105">
         <f>'Nach Mannschaften sortiert'!D59</f>
         <v>46167</v>
@@ -5634,7 +5643,7 @@
         <v>U13</v>
       </c>
     </row>
-    <row r="60" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B60" s="105">
         <f>'Nach Mannschaften sortiert'!D60</f>
         <v>46173</v>
@@ -5664,7 +5673,7 @@
         <v>U13</v>
       </c>
     </row>
-    <row r="61" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B61" s="105">
         <f>'Nach Mannschaften sortiert'!D61</f>
         <v>46180</v>
@@ -5694,7 +5703,7 @@
         <v>U13</v>
       </c>
     </row>
-    <row r="62" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B62" s="105">
         <f>'Nach Mannschaften sortiert'!D62</f>
         <v>46109</v>
@@ -5724,7 +5733,7 @@
         <v>U11</v>
       </c>
     </row>
-    <row r="63" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B63" s="105">
         <f>'Nach Mannschaften sortiert'!D63</f>
         <v>46123</v>
@@ -5754,7 +5763,7 @@
         <v>U11</v>
       </c>
     </row>
-    <row r="64" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B64" s="105">
         <f>'Nach Mannschaften sortiert'!D64</f>
         <v>46131</v>

--- a/Terminefussball_2026_Frühjahr.xlsx
+++ b/Terminefussball_2026_Frühjahr.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DTB\asv-neufeld\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{404E1852-B9DA-4D3B-B326-5178DED93246}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{332A2D47-6615-4684-9B3E-7C29891E4A78}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="555" uniqueCount="145">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="556" uniqueCount="146">
   <si>
     <t>Mannschaft</t>
   </si>
@@ -479,6 +479,9 @@
   </si>
   <si>
     <t>ABGESAGT!!!</t>
+  </si>
+  <si>
+    <t>STATUS</t>
   </si>
 </sst>
 </file>
@@ -1242,6 +1245,7 @@
     <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="20" fontId="0" fillId="11" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="20" fontId="0" fillId="15" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="6" fillId="13" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="6" fillId="13" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="6" fillId="13" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
@@ -1269,7 +1273,6 @@
     <xf numFmtId="0" fontId="6" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
@@ -3857,7 +3860,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E571BD24-40DC-4066-8BBA-CF3C23365042}">
-  <dimension ref="A1:I89"/>
+  <dimension ref="A1:J89"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="11.44140625" style="105"/>
@@ -3865,10 +3868,10 @@
     <col min="4" max="4" width="8.33203125" style="39" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="11.44140625" style="39"/>
     <col min="6" max="6" width="14.44140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="11.5546875" style="125"/>
+    <col min="7" max="7" width="11.5546875" style="108"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>133</v>
       </c>
@@ -3887,7 +3890,7 @@
       <c r="F1" t="s">
         <v>141</v>
       </c>
-      <c r="G1" s="125" t="s">
+      <c r="G1" s="108" t="s">
         <v>135</v>
       </c>
       <c r="H1" t="s">
@@ -3896,8 +3899,11 @@
       <c r="I1" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J1" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B2" s="105">
         <f>'Nach Mannschaften sortiert'!D2</f>
         <v>46096</v>
@@ -3914,7 +3920,7 @@
         <f>UPPER('Nach Mannschaften sortiert'!F2)</f>
         <v>RUST</v>
       </c>
-      <c r="G2" s="125" t="str">
+      <c r="G2" s="108" t="str">
         <f>'Nach Mannschaften sortiert'!H2</f>
         <v>Auswärts</v>
       </c>
@@ -3927,7 +3933,7 @@
         <v>KM</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B3" s="105">
         <f>'Nach Mannschaften sortiert'!D3</f>
         <v>46102</v>
@@ -3944,7 +3950,7 @@
         <f>UPPER('Nach Mannschaften sortiert'!F3)</f>
         <v>NEUFELD</v>
       </c>
-      <c r="G3" s="125" t="str">
+      <c r="G3" s="108" t="str">
         <f>'Nach Mannschaften sortiert'!H3</f>
         <v>Heim</v>
       </c>
@@ -3957,7 +3963,7 @@
         <v>KM</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B4" s="105">
         <f>'Nach Mannschaften sortiert'!D4</f>
         <v>46109</v>
@@ -3974,7 +3980,7 @@
         <f>UPPER('Nach Mannschaften sortiert'!F4)</f>
         <v>GATTENDORF</v>
       </c>
-      <c r="G4" s="125" t="str">
+      <c r="G4" s="108" t="str">
         <f>'Nach Mannschaften sortiert'!H4</f>
         <v>Auswärts</v>
       </c>
@@ -3987,7 +3993,7 @@
         <v>KM</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B5" s="105">
         <f>'Nach Mannschaften sortiert'!D5</f>
         <v>46116</v>
@@ -4004,7 +4010,7 @@
         <f>UPPER('Nach Mannschaften sortiert'!F5)</f>
         <v>NEUFELD</v>
       </c>
-      <c r="G5" s="125" t="str">
+      <c r="G5" s="108" t="str">
         <f>'Nach Mannschaften sortiert'!H5</f>
         <v>Heim</v>
       </c>
@@ -4017,7 +4023,7 @@
         <v>KM</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B6" s="105">
         <f>'Nach Mannschaften sortiert'!D6</f>
         <v>46124</v>
@@ -4034,7 +4040,7 @@
         <f>UPPER('Nach Mannschaften sortiert'!F6)</f>
         <v>ANDAU</v>
       </c>
-      <c r="G6" s="125" t="str">
+      <c r="G6" s="108" t="str">
         <f>'Nach Mannschaften sortiert'!H6</f>
         <v>Auswärts</v>
       </c>
@@ -4047,7 +4053,7 @@
         <v>KM</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B7" s="105">
         <f>'Nach Mannschaften sortiert'!D7</f>
         <v>46130</v>
@@ -4064,7 +4070,7 @@
         <f>UPPER('Nach Mannschaften sortiert'!F7)</f>
         <v>NEUFELD</v>
       </c>
-      <c r="G7" s="125" t="str">
+      <c r="G7" s="108" t="str">
         <f>'Nach Mannschaften sortiert'!H7</f>
         <v>Heim</v>
       </c>
@@ -4077,7 +4083,7 @@
         <v>KM</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B8" s="105">
         <f>'Nach Mannschaften sortiert'!D8</f>
         <v>46136</v>
@@ -4094,7 +4100,7 @@
         <f>UPPER('Nach Mannschaften sortiert'!F8)</f>
         <v>DEUTSCH JAHRNDORF</v>
       </c>
-      <c r="G8" s="125" t="str">
+      <c r="G8" s="108" t="str">
         <f>'Nach Mannschaften sortiert'!H8</f>
         <v>Auswärts</v>
       </c>
@@ -4107,7 +4113,7 @@
         <v>KM</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B9" s="105">
         <f>'Nach Mannschaften sortiert'!D9</f>
         <v>46144</v>
@@ -4124,7 +4130,7 @@
         <f>UPPER('Nach Mannschaften sortiert'!F9)</f>
         <v>NEUFELD</v>
       </c>
-      <c r="G9" s="125" t="str">
+      <c r="G9" s="108" t="str">
         <f>'Nach Mannschaften sortiert'!H9</f>
         <v>Heim</v>
       </c>
@@ -4137,7 +4143,7 @@
         <v>KM</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B10" s="105">
         <f>'Nach Mannschaften sortiert'!D10</f>
         <v>46151</v>
@@ -4154,7 +4160,7 @@
         <f>UPPER('Nach Mannschaften sortiert'!F10)</f>
         <v>GOLS</v>
       </c>
-      <c r="G10" s="125" t="str">
+      <c r="G10" s="108" t="str">
         <f>'Nach Mannschaften sortiert'!H10</f>
         <v>Auswärts</v>
       </c>
@@ -4167,7 +4173,7 @@
         <v>KM</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B11" s="105">
         <f>'Nach Mannschaften sortiert'!D11</f>
         <v>46157</v>
@@ -4184,7 +4190,7 @@
         <f>UPPER('Nach Mannschaften sortiert'!F11)</f>
         <v>NEUFELD</v>
       </c>
-      <c r="G11" s="125" t="str">
+      <c r="G11" s="108" t="str">
         <f>'Nach Mannschaften sortiert'!H11</f>
         <v>Heim</v>
       </c>
@@ -4197,7 +4203,7 @@
         <v>KM</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B12" s="105">
         <f>'Nach Mannschaften sortiert'!D12</f>
         <v>46166</v>
@@ -4214,7 +4220,7 @@
         <f>UPPER('Nach Mannschaften sortiert'!F12)</f>
         <v>WIMPASSING</v>
       </c>
-      <c r="G12" s="125" t="str">
+      <c r="G12" s="108" t="str">
         <f>'Nach Mannschaften sortiert'!H12</f>
         <v>Auswärts</v>
       </c>
@@ -4227,7 +4233,7 @@
         <v>KM</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B13" s="105">
         <f>'Nach Mannschaften sortiert'!D13</f>
         <v>46172</v>
@@ -4244,7 +4250,7 @@
         <f>UPPER('Nach Mannschaften sortiert'!F13)</f>
         <v>WINDEN</v>
       </c>
-      <c r="G13" s="125" t="str">
+      <c r="G13" s="108" t="str">
         <f>'Nach Mannschaften sortiert'!H13</f>
         <v>Auswärts</v>
       </c>
@@ -4257,7 +4263,7 @@
         <v>KM</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B14" s="105">
         <f>'Nach Mannschaften sortiert'!D14</f>
         <v>46179</v>
@@ -4274,7 +4280,7 @@
         <f>UPPER('Nach Mannschaften sortiert'!F14)</f>
         <v>NEUFELD</v>
       </c>
-      <c r="G14" s="125" t="str">
+      <c r="G14" s="108" t="str">
         <f>'Nach Mannschaften sortiert'!H14</f>
         <v>Heim</v>
       </c>
@@ -4287,7 +4293,7 @@
         <v>KM</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B15" s="105">
         <f>'Nach Mannschaften sortiert'!D15</f>
         <v>46096</v>
@@ -4304,7 +4310,7 @@
         <f>UPPER('Nach Mannschaften sortiert'!F15)</f>
         <v>RUST</v>
       </c>
-      <c r="G15" s="125" t="str">
+      <c r="G15" s="108" t="str">
         <f>'Nach Mannschaften sortiert'!H15</f>
         <v>Auswärts</v>
       </c>
@@ -4317,7 +4323,7 @@
         <v>U23</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B16" s="105">
         <f>'Nach Mannschaften sortiert'!D16</f>
         <v>46102</v>
@@ -4334,7 +4340,7 @@
         <f>UPPER('Nach Mannschaften sortiert'!F16)</f>
         <v>NEUFELD</v>
       </c>
-      <c r="G16" s="125" t="str">
+      <c r="G16" s="108" t="str">
         <f>'Nach Mannschaften sortiert'!H16</f>
         <v>Heim</v>
       </c>
@@ -4364,7 +4370,7 @@
         <f>UPPER('Nach Mannschaften sortiert'!F17)</f>
         <v>GATTENDORF</v>
       </c>
-      <c r="G17" s="125" t="str">
+      <c r="G17" s="108" t="str">
         <f>'Nach Mannschaften sortiert'!H17</f>
         <v>Auswärts</v>
       </c>
@@ -4394,7 +4400,7 @@
         <f>UPPER('Nach Mannschaften sortiert'!F18)</f>
         <v>NEUFELD</v>
       </c>
-      <c r="G18" s="125" t="str">
+      <c r="G18" s="108" t="str">
         <f>'Nach Mannschaften sortiert'!H18</f>
         <v>Heim</v>
       </c>
@@ -4424,7 +4430,7 @@
         <f>UPPER('Nach Mannschaften sortiert'!F19)</f>
         <v>ANDAU</v>
       </c>
-      <c r="G19" s="125" t="str">
+      <c r="G19" s="108" t="str">
         <f>'Nach Mannschaften sortiert'!H19</f>
         <v>Auswärts</v>
       </c>
@@ -4454,7 +4460,7 @@
         <f>UPPER('Nach Mannschaften sortiert'!F20)</f>
         <v>NEUFELD</v>
       </c>
-      <c r="G20" s="125" t="str">
+      <c r="G20" s="108" t="str">
         <f>'Nach Mannschaften sortiert'!H20</f>
         <v>Heim</v>
       </c>
@@ -4484,7 +4490,7 @@
         <f>UPPER('Nach Mannschaften sortiert'!F21)</f>
         <v>DEUTSCH JAHRNDORF</v>
       </c>
-      <c r="G21" s="125" t="str">
+      <c r="G21" s="108" t="str">
         <f>'Nach Mannschaften sortiert'!H21</f>
         <v>Auswärts</v>
       </c>
@@ -4514,7 +4520,7 @@
         <f>UPPER('Nach Mannschaften sortiert'!F22)</f>
         <v>NEUFELD</v>
       </c>
-      <c r="G22" s="125" t="str">
+      <c r="G22" s="108" t="str">
         <f>'Nach Mannschaften sortiert'!H22</f>
         <v>Heim</v>
       </c>
@@ -4544,7 +4550,7 @@
         <f>UPPER('Nach Mannschaften sortiert'!F23)</f>
         <v>GOLS</v>
       </c>
-      <c r="G23" s="125" t="str">
+      <c r="G23" s="108" t="str">
         <f>'Nach Mannschaften sortiert'!H23</f>
         <v>Auswärts</v>
       </c>
@@ -4574,7 +4580,7 @@
         <f>UPPER('Nach Mannschaften sortiert'!F24)</f>
         <v>NEUFELD</v>
       </c>
-      <c r="G24" s="125" t="str">
+      <c r="G24" s="108" t="str">
         <f>'Nach Mannschaften sortiert'!H24</f>
         <v>Heim</v>
       </c>
@@ -4604,7 +4610,7 @@
         <f>UPPER('Nach Mannschaften sortiert'!F25)</f>
         <v>WIMPASSING</v>
       </c>
-      <c r="G25" s="125" t="str">
+      <c r="G25" s="108" t="str">
         <f>'Nach Mannschaften sortiert'!H25</f>
         <v>Auswärts</v>
       </c>
@@ -4634,7 +4640,7 @@
         <f>UPPER('Nach Mannschaften sortiert'!F26)</f>
         <v>WINDEN</v>
       </c>
-      <c r="G26" s="125" t="str">
+      <c r="G26" s="108" t="str">
         <f>'Nach Mannschaften sortiert'!H26</f>
         <v>Auswärts</v>
       </c>
@@ -4664,7 +4670,7 @@
         <f>UPPER('Nach Mannschaften sortiert'!F27)</f>
         <v>NEUFELD</v>
       </c>
-      <c r="G27" s="125" t="str">
+      <c r="G27" s="108" t="str">
         <f>'Nach Mannschaften sortiert'!H27</f>
         <v>Heim</v>
       </c>
@@ -4694,7 +4700,7 @@
         <f>UPPER('Nach Mannschaften sortiert'!F28)</f>
         <v>SV LEITHAPRODERSDORF</v>
       </c>
-      <c r="G28" s="125" t="str">
+      <c r="G28" s="108" t="str">
         <f>'Nach Mannschaften sortiert'!H28</f>
         <v>Auswärts</v>
       </c>
@@ -4724,7 +4730,7 @@
         <f>UPPER('Nach Mannschaften sortiert'!F29)</f>
         <v>WIMPASSING</v>
       </c>
-      <c r="G29" s="125" t="str">
+      <c r="G29" s="108" t="str">
         <f>'Nach Mannschaften sortiert'!H29</f>
         <v>Heim</v>
       </c>
@@ -4754,7 +4760,7 @@
         <f>UPPER('Nach Mannschaften sortiert'!F30)</f>
         <v>WOLFAU</v>
       </c>
-      <c r="G30" s="125" t="str">
+      <c r="G30" s="108" t="str">
         <f>'Nach Mannschaften sortiert'!H30</f>
         <v>Auswärts</v>
       </c>
@@ -4784,7 +4790,7 @@
         <f>UPPER('Nach Mannschaften sortiert'!F31)</f>
         <v>NEUFELD</v>
       </c>
-      <c r="G31" s="125" t="str">
+      <c r="G31" s="108" t="str">
         <f>'Nach Mannschaften sortiert'!H31</f>
         <v>Heim</v>
       </c>
@@ -4814,7 +4820,7 @@
         <f>UPPER('Nach Mannschaften sortiert'!F32)</f>
         <v>ST. GEORGEN</v>
       </c>
-      <c r="G32" s="125" t="str">
+      <c r="G32" s="108" t="str">
         <f>'Nach Mannschaften sortiert'!H32</f>
         <v>Auswärts</v>
       </c>
@@ -4827,7 +4833,7 @@
         <v>U16</v>
       </c>
     </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="33" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B33" s="105">
         <f>'Nach Mannschaften sortiert'!D33</f>
         <v>46151</v>
@@ -4844,7 +4850,7 @@
         <f>UPPER('Nach Mannschaften sortiert'!F33)</f>
         <v>WIMPASSING</v>
       </c>
-      <c r="G33" s="125" t="str">
+      <c r="G33" s="108" t="str">
         <f>'Nach Mannschaften sortiert'!H33</f>
         <v>Heim</v>
       </c>
@@ -4857,7 +4863,7 @@
         <v>U16</v>
       </c>
     </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="34" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B34" s="105">
         <f>'Nach Mannschaften sortiert'!D34</f>
         <v>46159</v>
@@ -4874,7 +4880,7 @@
         <f>UPPER('Nach Mannschaften sortiert'!F34)</f>
         <v>BERNSTEIN</v>
       </c>
-      <c r="G34" s="125" t="str">
+      <c r="G34" s="108" t="str">
         <f>'Nach Mannschaften sortiert'!H34</f>
         <v>Auswärts</v>
       </c>
@@ -4887,7 +4893,7 @@
         <v>U16</v>
       </c>
     </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="35" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B35" s="105">
         <f>'Nach Mannschaften sortiert'!D35</f>
         <v>46102</v>
@@ -4904,7 +4910,7 @@
         <f>UPPER('Nach Mannschaften sortiert'!F35)</f>
         <v>WIMPASSING</v>
       </c>
-      <c r="G35" s="125" t="str">
+      <c r="G35" s="108" t="str">
         <f>'Nach Mannschaften sortiert'!H35</f>
         <v>Heim</v>
       </c>
@@ -4917,7 +4923,7 @@
         <v>U16</v>
       </c>
     </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="36" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B36" s="105">
         <f>'Nach Mannschaften sortiert'!D36</f>
         <v>46173</v>
@@ -4934,7 +4940,7 @@
         <f>UPPER('Nach Mannschaften sortiert'!F36)</f>
         <v>KIRCHSCHLAG</v>
       </c>
-      <c r="G36" s="125" t="str">
+      <c r="G36" s="108" t="str">
         <f>'Nach Mannschaften sortiert'!H36</f>
         <v>Auswärts</v>
       </c>
@@ -4947,7 +4953,7 @@
         <v>U16</v>
       </c>
     </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="37" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B37" s="105">
         <f>'Nach Mannschaften sortiert'!D37</f>
         <v>46180</v>
@@ -4964,7 +4970,7 @@
         <f>UPPER('Nach Mannschaften sortiert'!F37)</f>
         <v>NEUFELD</v>
       </c>
-      <c r="G37" s="125" t="str">
+      <c r="G37" s="108" t="str">
         <f>'Nach Mannschaften sortiert'!H37</f>
         <v>Heim</v>
       </c>
@@ -4977,7 +4983,7 @@
         <v>U16</v>
       </c>
     </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="38" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B38" s="105">
         <f>'Nach Mannschaften sortiert'!D38</f>
         <v>46124</v>
@@ -4994,7 +5000,7 @@
         <f>UPPER('Nach Mannschaften sortiert'!F38)</f>
         <v>NEUFELD</v>
       </c>
-      <c r="G38" s="125" t="str">
+      <c r="G38" s="108" t="str">
         <f>'Nach Mannschaften sortiert'!H38</f>
         <v>Heim</v>
       </c>
@@ -5007,7 +5013,7 @@
         <v>U15</v>
       </c>
     </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="39" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B39" s="105">
         <f>'Nach Mannschaften sortiert'!D39</f>
         <v>46128</v>
@@ -5024,7 +5030,7 @@
         <f>UPPER('Nach Mannschaften sortiert'!F39)</f>
         <v>WIMPASSING</v>
       </c>
-      <c r="G39" s="125" t="str">
+      <c r="G39" s="108" t="str">
         <f>'Nach Mannschaften sortiert'!H39</f>
         <v>Heim</v>
       </c>
@@ -5037,7 +5043,7 @@
         <v>U15</v>
       </c>
     </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="40" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B40" s="105">
         <f>'Nach Mannschaften sortiert'!D40</f>
         <v>46137</v>
@@ -5054,7 +5060,7 @@
         <f>UPPER('Nach Mannschaften sortiert'!F40)</f>
         <v>NEUSIEDL</v>
       </c>
-      <c r="G40" s="125" t="str">
+      <c r="G40" s="108" t="str">
         <f>'Nach Mannschaften sortiert'!H40</f>
         <v>Auswärts</v>
       </c>
@@ -5067,7 +5073,7 @@
         <v>U15</v>
       </c>
     </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="41" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B41" s="105">
         <f>'Nach Mannschaften sortiert'!D41</f>
         <v>46145</v>
@@ -5084,7 +5090,7 @@
         <f>UPPER('Nach Mannschaften sortiert'!F41)</f>
         <v>NEUFELD</v>
       </c>
-      <c r="G41" s="125" t="str">
+      <c r="G41" s="108" t="str">
         <f>'Nach Mannschaften sortiert'!H41</f>
         <v>Heim</v>
       </c>
@@ -5097,7 +5103,7 @@
         <v>U15</v>
       </c>
     </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="42" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B42" s="105">
         <f>'Nach Mannschaften sortiert'!D42</f>
         <v>46157</v>
@@ -5114,7 +5120,7 @@
         <f>UPPER('Nach Mannschaften sortiert'!F42)</f>
         <v>PARNDORF</v>
       </c>
-      <c r="G42" s="125" t="str">
+      <c r="G42" s="108" t="str">
         <f>'Nach Mannschaften sortiert'!H42</f>
         <v>Auswärts</v>
       </c>
@@ -5127,7 +5133,7 @@
         <v>U15</v>
       </c>
     </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="43" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B43" s="105">
         <f>'Nach Mannschaften sortiert'!D43</f>
         <v>46165</v>
@@ -5144,7 +5150,7 @@
         <f>UPPER('Nach Mannschaften sortiert'!F43)</f>
         <v>GROßHÖFLEIN</v>
       </c>
-      <c r="G43" s="125" t="str">
+      <c r="G43" s="108" t="str">
         <f>'Nach Mannschaften sortiert'!H43</f>
         <v>Auswärts</v>
       </c>
@@ -5157,7 +5163,7 @@
         <v>U15</v>
       </c>
     </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="44" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B44" s="105">
         <f>'Nach Mannschaften sortiert'!D44</f>
         <v>46173</v>
@@ -5174,7 +5180,7 @@
         <f>UPPER('Nach Mannschaften sortiert'!F44)</f>
         <v>WIMPASSING</v>
       </c>
-      <c r="G44" s="125" t="str">
+      <c r="G44" s="108" t="str">
         <f>'Nach Mannschaften sortiert'!H44</f>
         <v>Heim</v>
       </c>
@@ -5187,7 +5193,7 @@
         <v>U15</v>
       </c>
     </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="45" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B45" s="105">
         <f>'Nach Mannschaften sortiert'!D45</f>
         <v>46179</v>
@@ -5204,7 +5210,7 @@
         <f>UPPER('Nach Mannschaften sortiert'!F45)</f>
         <v>WIESEN</v>
       </c>
-      <c r="G45" s="125" t="str">
+      <c r="G45" s="108" t="str">
         <f>'Nach Mannschaften sortiert'!H45</f>
         <v>Auswärts</v>
       </c>
@@ -5217,10 +5223,7 @@
         <v>U15</v>
       </c>
     </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A46" t="s">
-        <v>144</v>
-      </c>
+    <row r="46" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B46" s="105">
         <f>'Nach Mannschaften sortiert'!D46</f>
         <v>46109</v>
@@ -5237,7 +5240,7 @@
         <f>UPPER('Nach Mannschaften sortiert'!F46)</f>
         <v>NEUFELD</v>
       </c>
-      <c r="G46" s="125" t="str">
+      <c r="G46" s="108" t="str">
         <f>'Nach Mannschaften sortiert'!H46</f>
         <v>Heim</v>
       </c>
@@ -5249,8 +5252,11 @@
         <f>'Nach Mannschaften sortiert'!C46</f>
         <v>U14</v>
       </c>
-    </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J46" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="47" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B47" s="105">
         <f>'Nach Mannschaften sortiert'!D47</f>
         <v>46122</v>
@@ -5267,7 +5273,7 @@
         <f>UPPER('Nach Mannschaften sortiert'!F47)</f>
         <v>PAMA</v>
       </c>
-      <c r="G47" s="125" t="str">
+      <c r="G47" s="108" t="str">
         <f>'Nach Mannschaften sortiert'!H47</f>
         <v>Auswärts</v>
       </c>
@@ -5280,7 +5286,7 @@
         <v>U14</v>
       </c>
     </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="48" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B48" s="105">
         <f>'Nach Mannschaften sortiert'!D48</f>
         <v>46131</v>
@@ -5297,7 +5303,7 @@
         <f>UPPER('Nach Mannschaften sortiert'!F48)</f>
         <v>KITTSEE</v>
       </c>
-      <c r="G48" s="125" t="str">
+      <c r="G48" s="108" t="str">
         <f>'Nach Mannschaften sortiert'!H48</f>
         <v>Auswärts</v>
       </c>
@@ -5310,7 +5316,7 @@
         <v>U14</v>
       </c>
     </row>
-    <row r="49" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="49" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B49" s="105">
         <f>'Nach Mannschaften sortiert'!D49</f>
         <v>46137</v>
@@ -5327,7 +5333,7 @@
         <f>UPPER('Nach Mannschaften sortiert'!F49)</f>
         <v>NEUFELD</v>
       </c>
-      <c r="G49" s="125" t="str">
+      <c r="G49" s="108" t="str">
         <f>'Nach Mannschaften sortiert'!H49</f>
         <v>Heim</v>
       </c>
@@ -5340,7 +5346,7 @@
         <v>U14</v>
       </c>
     </row>
-    <row r="50" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="50" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B50" s="105">
         <f>'Nach Mannschaften sortiert'!D50</f>
         <v>46151</v>
@@ -5357,7 +5363,7 @@
         <f>UPPER('Nach Mannschaften sortiert'!F50)</f>
         <v>WULKAPRODERSDORF</v>
       </c>
-      <c r="G50" s="125" t="str">
+      <c r="G50" s="108" t="str">
         <f>'Nach Mannschaften sortiert'!H50</f>
         <v>Auswärts</v>
       </c>
@@ -5370,7 +5376,7 @@
         <v>U14</v>
       </c>
     </row>
-    <row r="51" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="51" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B51" s="105">
         <f>'Nach Mannschaften sortiert'!D51</f>
         <v>46158</v>
@@ -5387,7 +5393,7 @@
         <f>UPPER('Nach Mannschaften sortiert'!F51)</f>
         <v>NEUFELD</v>
       </c>
-      <c r="G51" s="125" t="str">
+      <c r="G51" s="108" t="str">
         <f>'Nach Mannschaften sortiert'!H51</f>
         <v>Heim</v>
       </c>
@@ -5400,7 +5406,7 @@
         <v>U14</v>
       </c>
     </row>
-    <row r="52" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="52" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B52" s="105">
         <f>'Nach Mannschaften sortiert'!D52</f>
         <v>46163</v>
@@ -5417,7 +5423,7 @@
         <f>UPPER('Nach Mannschaften sortiert'!F52)</f>
         <v>NEUFELD</v>
       </c>
-      <c r="G52" s="125" t="str">
+      <c r="G52" s="108" t="str">
         <f>'Nach Mannschaften sortiert'!H52</f>
         <v>Heim</v>
       </c>
@@ -5430,7 +5436,7 @@
         <v>U14</v>
       </c>
     </row>
-    <row r="53" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="53" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B53" s="105">
         <f>'Nach Mannschaften sortiert'!D53</f>
         <v>46171</v>
@@ -5447,7 +5453,7 @@
         <f>UPPER('Nach Mannschaften sortiert'!F53)</f>
         <v>LEITHAPRODERSDORF</v>
       </c>
-      <c r="G53" s="125" t="str">
+      <c r="G53" s="108" t="str">
         <f>'Nach Mannschaften sortiert'!H53</f>
         <v>Auswärts</v>
       </c>
@@ -5460,10 +5466,7 @@
         <v>U14</v>
       </c>
     </row>
-    <row r="54" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A54" t="s">
-        <v>144</v>
-      </c>
+    <row r="54" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B54" s="105">
         <f>'Nach Mannschaften sortiert'!D54</f>
         <v>46110</v>
@@ -5480,7 +5483,7 @@
         <f>UPPER('Nach Mannschaften sortiert'!F54)</f>
         <v>NEUFELD</v>
       </c>
-      <c r="G54" s="125" t="str">
+      <c r="G54" s="108" t="str">
         <f>'Nach Mannschaften sortiert'!H54</f>
         <v>Heim</v>
       </c>
@@ -5492,8 +5495,11 @@
         <f>'Nach Mannschaften sortiert'!C54</f>
         <v>U13</v>
       </c>
-    </row>
-    <row r="55" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J54" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="55" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B55" s="105">
         <f>'Nach Mannschaften sortiert'!D55</f>
         <v>46130</v>
@@ -5510,7 +5516,7 @@
         <f>UPPER('Nach Mannschaften sortiert'!F55)</f>
         <v>RUST</v>
       </c>
-      <c r="G55" s="125" t="str">
+      <c r="G55" s="108" t="str">
         <f>'Nach Mannschaften sortiert'!H55</f>
         <v>Auswärts</v>
       </c>
@@ -5523,7 +5529,7 @@
         <v>U13</v>
       </c>
     </row>
-    <row r="56" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="56" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B56" s="105">
         <f>'Nach Mannschaften sortiert'!D56</f>
         <v>46138</v>
@@ -5540,7 +5546,7 @@
         <f>UPPER('Nach Mannschaften sortiert'!F56)</f>
         <v>NEUFELD</v>
       </c>
-      <c r="G56" s="125" t="str">
+      <c r="G56" s="108" t="str">
         <f>'Nach Mannschaften sortiert'!H56</f>
         <v>Heim</v>
       </c>
@@ -5553,7 +5559,7 @@
         <v>U13</v>
       </c>
     </row>
-    <row r="57" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="57" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B57" s="105">
         <f>'Nach Mannschaften sortiert'!D57</f>
         <v>46145</v>
@@ -5570,7 +5576,7 @@
         <f>UPPER('Nach Mannschaften sortiert'!F57)</f>
         <v>LEITHAPRODERSDORF</v>
       </c>
-      <c r="G57" s="125" t="str">
+      <c r="G57" s="108" t="str">
         <f>'Nach Mannschaften sortiert'!H57</f>
         <v>Auswärts</v>
       </c>
@@ -5583,7 +5589,7 @@
         <v>U13</v>
       </c>
     </row>
-    <row r="58" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="58" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B58" s="105">
         <f>'Nach Mannschaften sortiert'!D58</f>
         <v>46151</v>
@@ -5600,7 +5606,7 @@
         <f>UPPER('Nach Mannschaften sortiert'!F58)</f>
         <v>KITTSEE</v>
       </c>
-      <c r="G58" s="125" t="str">
+      <c r="G58" s="108" t="str">
         <f>'Nach Mannschaften sortiert'!H58</f>
         <v>Auswärts</v>
       </c>
@@ -5613,7 +5619,7 @@
         <v>U13</v>
       </c>
     </row>
-    <row r="59" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="59" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B59" s="105">
         <f>'Nach Mannschaften sortiert'!D59</f>
         <v>46167</v>
@@ -5630,7 +5636,7 @@
         <f>UPPER('Nach Mannschaften sortiert'!F59)</f>
         <v>NEUFELD</v>
       </c>
-      <c r="G59" s="125" t="str">
+      <c r="G59" s="108" t="str">
         <f>'Nach Mannschaften sortiert'!H59</f>
         <v>Heim</v>
       </c>
@@ -5643,7 +5649,7 @@
         <v>U13</v>
       </c>
     </row>
-    <row r="60" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="60" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B60" s="105">
         <f>'Nach Mannschaften sortiert'!D60</f>
         <v>46173</v>
@@ -5660,7 +5666,7 @@
         <f>UPPER('Nach Mannschaften sortiert'!F60)</f>
         <v>BREITENBRUNN</v>
       </c>
-      <c r="G60" s="125" t="str">
+      <c r="G60" s="108" t="str">
         <f>'Nach Mannschaften sortiert'!H60</f>
         <v>Auswärts</v>
       </c>
@@ -5673,7 +5679,7 @@
         <v>U13</v>
       </c>
     </row>
-    <row r="61" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="61" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B61" s="105">
         <f>'Nach Mannschaften sortiert'!D61</f>
         <v>46180</v>
@@ -5690,7 +5696,7 @@
         <f>UPPER('Nach Mannschaften sortiert'!F61)</f>
         <v>NEUFELD</v>
       </c>
-      <c r="G61" s="125" t="str">
+      <c r="G61" s="108" t="str">
         <f>'Nach Mannschaften sortiert'!H61</f>
         <v>Heim</v>
       </c>
@@ -5703,7 +5709,7 @@
         <v>U13</v>
       </c>
     </row>
-    <row r="62" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="62" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B62" s="105">
         <f>'Nach Mannschaften sortiert'!D62</f>
         <v>46109</v>
@@ -5720,7 +5726,7 @@
         <f>UPPER('Nach Mannschaften sortiert'!F62)</f>
         <v>STEINBRUNN</v>
       </c>
-      <c r="G62" s="125" t="str">
+      <c r="G62" s="108" t="str">
         <f>'Nach Mannschaften sortiert'!H62</f>
         <v>Auswärts</v>
       </c>
@@ -5733,7 +5739,7 @@
         <v>U11</v>
       </c>
     </row>
-    <row r="63" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="63" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B63" s="105">
         <f>'Nach Mannschaften sortiert'!D63</f>
         <v>46123</v>
@@ -5750,7 +5756,7 @@
         <f>UPPER('Nach Mannschaften sortiert'!F63)</f>
         <v>NEUFELD</v>
       </c>
-      <c r="G63" s="125" t="str">
+      <c r="G63" s="108" t="str">
         <f>'Nach Mannschaften sortiert'!H63</f>
         <v>Heim</v>
       </c>
@@ -5763,7 +5769,7 @@
         <v>U11</v>
       </c>
     </row>
-    <row r="64" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="64" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B64" s="105">
         <f>'Nach Mannschaften sortiert'!D64</f>
         <v>46131</v>
@@ -5780,7 +5786,7 @@
         <f>UPPER('Nach Mannschaften sortiert'!F64)</f>
         <v>KLINGENBACH</v>
       </c>
-      <c r="G64" s="125" t="str">
+      <c r="G64" s="108" t="str">
         <f>'Nach Mannschaften sortiert'!H64</f>
         <v>Auswärts</v>
       </c>
@@ -5810,7 +5816,7 @@
         <f>UPPER('Nach Mannschaften sortiert'!F65)</f>
         <v>NEUFELD</v>
       </c>
-      <c r="G65" s="125" t="str">
+      <c r="G65" s="108" t="str">
         <f>'Nach Mannschaften sortiert'!H65</f>
         <v>Heim</v>
       </c>
@@ -5840,7 +5846,7 @@
         <f>UPPER('Nach Mannschaften sortiert'!F66)</f>
         <v>NEUFELD</v>
       </c>
-      <c r="G66" s="125" t="str">
+      <c r="G66" s="108" t="str">
         <f>'Nach Mannschaften sortiert'!H66</f>
         <v>Heim</v>
       </c>
@@ -5870,7 +5876,7 @@
         <f>UPPER('Nach Mannschaften sortiert'!F67)</f>
         <v>ST. MARGARETHEN</v>
       </c>
-      <c r="G67" s="125" t="str">
+      <c r="G67" s="108" t="str">
         <f>'Nach Mannschaften sortiert'!H67</f>
         <v>Auswärts</v>
       </c>
@@ -5900,7 +5906,7 @@
         <f>UPPER('Nach Mannschaften sortiert'!F68)</f>
         <v>NEUFELD</v>
       </c>
-      <c r="G68" s="125" t="str">
+      <c r="G68" s="108" t="str">
         <f>'Nach Mannschaften sortiert'!H68</f>
         <v>Heim</v>
       </c>
@@ -5930,7 +5936,7 @@
         <f>UPPER('Nach Mannschaften sortiert'!F69)</f>
         <v>STOTZING</v>
       </c>
-      <c r="G69" s="125" t="str">
+      <c r="G69" s="108" t="str">
         <f>'Nach Mannschaften sortiert'!H69</f>
         <v>Auswärts</v>
       </c>
@@ -5960,7 +5966,7 @@
         <f>UPPER('Nach Mannschaften sortiert'!F70)</f>
         <v>NEUFELD</v>
       </c>
-      <c r="G70" s="125" t="str">
+      <c r="G70" s="108" t="str">
         <f>'Nach Mannschaften sortiert'!H70</f>
         <v>Heim</v>
       </c>
@@ -5990,7 +5996,7 @@
         <f>UPPER('Nach Mannschaften sortiert'!F71)</f>
         <v>STEINBRUNN</v>
       </c>
-      <c r="G71" s="125" t="str">
+      <c r="G71" s="108" t="str">
         <f>'Nach Mannschaften sortiert'!H71</f>
         <v>Auswärts</v>
       </c>
@@ -6020,7 +6026,7 @@
         <f>UPPER('Nach Mannschaften sortiert'!F72)</f>
         <v>SIEGENDORF</v>
       </c>
-      <c r="G72" s="125" t="str">
+      <c r="G72" s="108" t="str">
         <f>'Nach Mannschaften sortiert'!H72</f>
         <v>Auswärts</v>
       </c>
@@ -6050,7 +6056,7 @@
         <f>UPPER('Nach Mannschaften sortiert'!F73)</f>
         <v>LEITHAPRODERSDORF</v>
       </c>
-      <c r="G73" s="125" t="str">
+      <c r="G73" s="108" t="str">
         <f>'Nach Mannschaften sortiert'!H73</f>
         <v>Auswärts</v>
       </c>
@@ -6080,7 +6086,7 @@
         <f>UPPER('Nach Mannschaften sortiert'!F74)</f>
         <v>ST. GEORGEN</v>
       </c>
-      <c r="G74" s="125" t="str">
+      <c r="G74" s="108" t="str">
         <f>'Nach Mannschaften sortiert'!H74</f>
         <v>Auswärts</v>
       </c>
@@ -6110,7 +6116,7 @@
         <f>UPPER('Nach Mannschaften sortiert'!F75)</f>
         <v>NEUFELD</v>
       </c>
-      <c r="G75" s="125" t="str">
+      <c r="G75" s="108" t="str">
         <f>'Nach Mannschaften sortiert'!H75</f>
         <v>Heim</v>
       </c>
@@ -6140,7 +6146,7 @@
         <f>UPPER('Nach Mannschaften sortiert'!F76)</f>
         <v>SIEGENDORF</v>
       </c>
-      <c r="G76" s="125" t="str">
+      <c r="G76" s="108" t="str">
         <f>'Nach Mannschaften sortiert'!H76</f>
         <v>Auswärts</v>
       </c>
@@ -6170,7 +6176,7 @@
         <f>UPPER('Nach Mannschaften sortiert'!F77)</f>
         <v>PURBACH</v>
       </c>
-      <c r="G77" s="125" t="str">
+      <c r="G77" s="108" t="str">
         <f>'Nach Mannschaften sortiert'!H77</f>
         <v>Auswärts</v>
       </c>
@@ -6200,7 +6206,7 @@
         <f>UPPER('Nach Mannschaften sortiert'!F78)</f>
         <v>LEITHAPRODERSDORF</v>
       </c>
-      <c r="G78" s="125" t="str">
+      <c r="G78" s="108" t="str">
         <f>'Nach Mannschaften sortiert'!H78</f>
         <v>Auswärts</v>
       </c>
@@ -6230,7 +6236,7 @@
         <f>UPPER('Nach Mannschaften sortiert'!F79)</f>
         <v>ST. GEORGEN</v>
       </c>
-      <c r="G79" s="125" t="str">
+      <c r="G79" s="108" t="str">
         <f>'Nach Mannschaften sortiert'!H79</f>
         <v>Auswärts</v>
       </c>
@@ -6260,7 +6266,7 @@
         <f>UPPER('Nach Mannschaften sortiert'!F80)</f>
         <v>NEUFELD</v>
       </c>
-      <c r="G80" s="125" t="str">
+      <c r="G80" s="108" t="str">
         <f>'Nach Mannschaften sortiert'!H80</f>
         <v>Heim</v>
       </c>
@@ -6290,7 +6296,7 @@
         <f>UPPER('Nach Mannschaften sortiert'!F81)</f>
         <v>EISENSTADT</v>
       </c>
-      <c r="G81" s="125" t="str">
+      <c r="G81" s="108" t="str">
         <f>'Nach Mannschaften sortiert'!H81</f>
         <v>Auswärts</v>
       </c>
@@ -6320,7 +6326,7 @@
         <f>UPPER('Nach Mannschaften sortiert'!F82)</f>
         <v>WULKAPRODERSDORF</v>
       </c>
-      <c r="G82" s="125" t="str">
+      <c r="G82" s="108" t="str">
         <f>'Nach Mannschaften sortiert'!H82</f>
         <v>Auswärts</v>
       </c>
@@ -6350,7 +6356,7 @@
         <f>UPPER('Nach Mannschaften sortiert'!F83)</f>
         <v>WIMPASSING</v>
       </c>
-      <c r="G83" s="125" t="str">
+      <c r="G83" s="108" t="str">
         <f>'Nach Mannschaften sortiert'!H83</f>
         <v>Auswärts</v>
       </c>
@@ -6380,7 +6386,7 @@
         <f>UPPER('Nach Mannschaften sortiert'!F84)</f>
         <v>ST. GEORGEN</v>
       </c>
-      <c r="G84" s="125" t="str">
+      <c r="G84" s="108" t="str">
         <f>'Nach Mannschaften sortiert'!H84</f>
         <v>Auswärts</v>
       </c>
@@ -6409,7 +6415,7 @@
         <f>UPPER('Nach Mannschaften sortiert'!F85)</f>
         <v>NEUFELD</v>
       </c>
-      <c r="G85" s="125" t="str">
+      <c r="G85" s="108" t="str">
         <f>'Nach Mannschaften sortiert'!H85</f>
         <v>Heim</v>
       </c>
@@ -6438,7 +6444,7 @@
         <f>UPPER('Nach Mannschaften sortiert'!F86)</f>
         <v>NEUFELD</v>
       </c>
-      <c r="G86" s="125" t="str">
+      <c r="G86" s="108" t="str">
         <f>'Nach Mannschaften sortiert'!H86</f>
         <v>Heim</v>
       </c>
@@ -6467,7 +6473,7 @@
         <f>UPPER('Nach Mannschaften sortiert'!F87)</f>
         <v>NEUFELD</v>
       </c>
-      <c r="G87" s="125" t="str">
+      <c r="G87" s="108" t="str">
         <f>'Nach Mannschaften sortiert'!H87</f>
         <v>Heim</v>
       </c>
@@ -6496,7 +6502,7 @@
         <f>UPPER('Nach Mannschaften sortiert'!F88)</f>
         <v>NEUFELD</v>
       </c>
-      <c r="G88" s="125" t="str">
+      <c r="G88" s="108" t="str">
         <f>'Nach Mannschaften sortiert'!H88</f>
         <v>Heim</v>
       </c>
@@ -6525,7 +6531,7 @@
         <f>UPPER('Nach Mannschaften sortiert'!F89)</f>
         <v>NEUFELD</v>
       </c>
-      <c r="G89" s="125" t="str">
+      <c r="G89" s="108" t="str">
         <f>'Nach Mannschaften sortiert'!H89</f>
         <v>Heim</v>
       </c>
@@ -6559,16 +6565,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="114" t="s">
+      <c r="A1" s="115" t="s">
         <v>51</v>
       </c>
-      <c r="B1" s="115"/>
-      <c r="C1" s="115"/>
-      <c r="D1" s="115"/>
-      <c r="E1" s="115"/>
-      <c r="F1" s="115"/>
-      <c r="G1" s="115"/>
-      <c r="H1" s="115"/>
+      <c r="B1" s="116"/>
+      <c r="C1" s="116"/>
+      <c r="D1" s="116"/>
+      <c r="E1" s="116"/>
+      <c r="F1" s="116"/>
+      <c r="G1" s="116"/>
+      <c r="H1" s="116"/>
     </row>
     <row r="2" spans="1:10" ht="31.8" thickTop="1" x14ac:dyDescent="0.3">
       <c r="A2" s="42" t="s">
@@ -6595,7 +6601,7 @@
       <c r="H2" s="42" t="s">
         <v>58</v>
       </c>
-      <c r="I2" s="111" t="s">
+      <c r="I2" s="112" t="s">
         <v>80</v>
       </c>
       <c r="J2" s="50"/>
@@ -6615,7 +6621,7 @@
       <c r="F3" s="85"/>
       <c r="G3" s="85"/>
       <c r="H3" s="87"/>
-      <c r="I3" s="112"/>
+      <c r="I3" s="113"/>
       <c r="J3" s="50"/>
     </row>
     <row r="4" spans="1:10" ht="31.2" x14ac:dyDescent="0.35">
@@ -6635,7 +6641,7 @@
       </c>
       <c r="G4" s="85"/>
       <c r="H4" s="87"/>
-      <c r="I4" s="112"/>
+      <c r="I4" s="113"/>
       <c r="J4" s="50"/>
     </row>
     <row r="5" spans="1:10" ht="31.2" x14ac:dyDescent="0.35">
@@ -6655,7 +6661,7 @@
       </c>
       <c r="G5" s="85"/>
       <c r="H5" s="87"/>
-      <c r="I5" s="112"/>
+      <c r="I5" s="113"/>
       <c r="J5" s="50"/>
     </row>
     <row r="6" spans="1:10" ht="31.2" x14ac:dyDescent="0.35">
@@ -6675,7 +6681,7 @@
       </c>
       <c r="G6" s="89"/>
       <c r="H6" s="87"/>
-      <c r="I6" s="112"/>
+      <c r="I6" s="113"/>
       <c r="J6" s="50"/>
     </row>
     <row r="7" spans="1:10" ht="31.2" x14ac:dyDescent="0.35">
@@ -6697,7 +6703,7 @@
         <v>70</v>
       </c>
       <c r="H7" s="87"/>
-      <c r="I7" s="112"/>
+      <c r="I7" s="113"/>
       <c r="J7" s="50"/>
     </row>
     <row r="8" spans="1:10" ht="31.2" x14ac:dyDescent="0.35">
@@ -6719,7 +6725,7 @@
         <v>70</v>
       </c>
       <c r="H8" s="87"/>
-      <c r="I8" s="112"/>
+      <c r="I8" s="113"/>
       <c r="J8" s="50"/>
     </row>
     <row r="9" spans="1:10" ht="31.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -6743,7 +6749,7 @@
       <c r="H9" s="92" t="s">
         <v>71</v>
       </c>
-      <c r="I9" s="112"/>
+      <c r="I9" s="113"/>
       <c r="J9" s="50"/>
     </row>
     <row r="10" spans="1:10" ht="31.2" x14ac:dyDescent="0.35">
@@ -6765,7 +6771,7 @@
         <v>132</v>
       </c>
       <c r="H10" s="87"/>
-      <c r="I10" s="112"/>
+      <c r="I10" s="113"/>
       <c r="J10" s="50"/>
     </row>
     <row r="11" spans="1:10" ht="31.8" thickBot="1" x14ac:dyDescent="0.4">
@@ -6785,7 +6791,7 @@
         <v>79</v>
       </c>
       <c r="H11" s="96"/>
-      <c r="I11" s="113"/>
+      <c r="I11" s="114"/>
       <c r="J11" s="50"/>
     </row>
     <row r="12" spans="1:10" ht="18.600000000000001" thickTop="1" x14ac:dyDescent="0.35">
@@ -6843,52 +6849,52 @@
       <c r="H14" s="103"/>
     </row>
     <row r="15" spans="1:10" ht="16.8" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="116" t="s">
+      <c r="A15" s="117" t="s">
         <v>77</v>
       </c>
-      <c r="B15" s="117"/>
-      <c r="C15" s="117"/>
-      <c r="D15" s="117"/>
-      <c r="E15" s="117"/>
-      <c r="F15" s="117"/>
-      <c r="G15" s="117"/>
-      <c r="H15" s="118"/>
+      <c r="B15" s="118"/>
+      <c r="C15" s="118"/>
+      <c r="D15" s="118"/>
+      <c r="E15" s="118"/>
+      <c r="F15" s="118"/>
+      <c r="G15" s="118"/>
+      <c r="H15" s="119"/>
     </row>
     <row r="16" spans="1:10" ht="16.8" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="119" t="s">
+      <c r="A16" s="120" t="s">
         <v>76</v>
       </c>
-      <c r="B16" s="120"/>
-      <c r="C16" s="120"/>
-      <c r="D16" s="120"/>
-      <c r="E16" s="120"/>
-      <c r="F16" s="120"/>
-      <c r="G16" s="120"/>
-      <c r="H16" s="121"/>
+      <c r="B16" s="121"/>
+      <c r="C16" s="121"/>
+      <c r="D16" s="121"/>
+      <c r="E16" s="121"/>
+      <c r="F16" s="121"/>
+      <c r="G16" s="121"/>
+      <c r="H16" s="122"/>
     </row>
     <row r="17" spans="1:8" ht="16.8" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="122" t="s">
+      <c r="A17" s="123" t="s">
         <v>75</v>
       </c>
-      <c r="B17" s="123"/>
-      <c r="C17" s="123"/>
-      <c r="D17" s="123"/>
-      <c r="E17" s="123"/>
-      <c r="F17" s="123"/>
-      <c r="G17" s="123"/>
-      <c r="H17" s="124"/>
+      <c r="B17" s="124"/>
+      <c r="C17" s="124"/>
+      <c r="D17" s="124"/>
+      <c r="E17" s="124"/>
+      <c r="F17" s="124"/>
+      <c r="G17" s="124"/>
+      <c r="H17" s="125"/>
     </row>
     <row r="18" spans="1:8" ht="16.8" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="108" t="s">
+      <c r="A18" s="109" t="s">
         <v>78</v>
       </c>
-      <c r="B18" s="109"/>
-      <c r="C18" s="109"/>
-      <c r="D18" s="109"/>
-      <c r="E18" s="109"/>
-      <c r="F18" s="109"/>
-      <c r="G18" s="109"/>
-      <c r="H18" s="110"/>
+      <c r="B18" s="110"/>
+      <c r="C18" s="110"/>
+      <c r="D18" s="110"/>
+      <c r="E18" s="110"/>
+      <c r="F18" s="110"/>
+      <c r="G18" s="110"/>
+      <c r="H18" s="111"/>
     </row>
     <row r="19" spans="1:8" ht="15" thickTop="1" x14ac:dyDescent="0.3"/>
   </sheetData>

--- a/Terminefussball_2026_Frühjahr.xlsx
+++ b/Terminefussball_2026_Frühjahr.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DTB\asv-neufeld\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{332A2D47-6615-4684-9B3E-7C29891E4A78}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B77F1070-64B6-4613-86CA-9D3B87A2AE7A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3866,8 +3866,8 @@
     <col min="2" max="2" width="11.44140625" style="105"/>
     <col min="3" max="3" width="11.44140625" style="39"/>
     <col min="4" max="4" width="8.33203125" style="39" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.44140625" style="39"/>
-    <col min="6" max="6" width="14.44140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="21.6640625" style="39" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="11.5546875" style="108"/>
   </cols>
   <sheetData>

--- a/Terminefussball_2026_Frühjahr.xlsx
+++ b/Terminefussball_2026_Frühjahr.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DTB\asv-neufeld\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B77F1070-64B6-4613-86CA-9D3B87A2AE7A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D899345-8C00-4374-8205-340837328209}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="556" uniqueCount="146">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="642" uniqueCount="147">
   <si>
     <t>Mannschaft</t>
   </si>
@@ -482,6 +482,9 @@
   </si>
   <si>
     <t>STATUS</t>
+  </si>
+  <si>
+    <t>aktiv</t>
   </si>
 </sst>
 </file>
@@ -3863,16 +3866,18 @@
   <dimension ref="A1:J89"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
+    <col min="1" max="1" width="11.5546875" style="108"/>
     <col min="2" max="2" width="11.44140625" style="105"/>
     <col min="3" max="3" width="11.44140625" style="39"/>
     <col min="4" max="4" width="8.33203125" style="39" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="21.6640625" style="39" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14" style="108" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="11.5546875" style="108"/>
+    <col min="10" max="10" width="11.5546875" style="108"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
+      <c r="A1" s="108" t="s">
         <v>133</v>
       </c>
       <c r="B1" s="105" t="s">
@@ -3887,7 +3892,7 @@
       <c r="E1" s="39" t="s">
         <v>137</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="108" t="s">
         <v>141</v>
       </c>
       <c r="G1" s="108" t="s">
@@ -3899,7 +3904,7 @@
       <c r="I1" t="s">
         <v>140</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J1" s="108" t="s">
         <v>145</v>
       </c>
     </row>
@@ -3932,6 +3937,9 @@
         <f>'Nach Mannschaften sortiert'!C2</f>
         <v>KM</v>
       </c>
+      <c r="J2" s="108" t="s">
+        <v>146</v>
+      </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B3" s="105">
@@ -3962,6 +3970,9 @@
         <f>'Nach Mannschaften sortiert'!C3</f>
         <v>KM</v>
       </c>
+      <c r="J3" s="108" t="s">
+        <v>146</v>
+      </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B4" s="105">
@@ -3992,6 +4003,9 @@
         <f>'Nach Mannschaften sortiert'!C4</f>
         <v>KM</v>
       </c>
+      <c r="J4" s="108" t="s">
+        <v>146</v>
+      </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B5" s="105">
@@ -4022,6 +4036,9 @@
         <f>'Nach Mannschaften sortiert'!C5</f>
         <v>KM</v>
       </c>
+      <c r="J5" s="108" t="s">
+        <v>146</v>
+      </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B6" s="105">
@@ -4052,6 +4069,9 @@
         <f>'Nach Mannschaften sortiert'!C6</f>
         <v>KM</v>
       </c>
+      <c r="J6" s="108" t="s">
+        <v>146</v>
+      </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B7" s="105">
@@ -4082,6 +4102,9 @@
         <f>'Nach Mannschaften sortiert'!C7</f>
         <v>KM</v>
       </c>
+      <c r="J7" s="108" t="s">
+        <v>146</v>
+      </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B8" s="105">
@@ -4112,6 +4135,9 @@
         <f>'Nach Mannschaften sortiert'!C8</f>
         <v>KM</v>
       </c>
+      <c r="J8" s="108" t="s">
+        <v>146</v>
+      </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B9" s="105">
@@ -4142,6 +4168,9 @@
         <f>'Nach Mannschaften sortiert'!C9</f>
         <v>KM</v>
       </c>
+      <c r="J9" s="108" t="s">
+        <v>146</v>
+      </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B10" s="105">
@@ -4172,6 +4201,9 @@
         <f>'Nach Mannschaften sortiert'!C10</f>
         <v>KM</v>
       </c>
+      <c r="J10" s="108" t="s">
+        <v>146</v>
+      </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B11" s="105">
@@ -4202,6 +4234,9 @@
         <f>'Nach Mannschaften sortiert'!C11</f>
         <v>KM</v>
       </c>
+      <c r="J11" s="108" t="s">
+        <v>146</v>
+      </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B12" s="105">
@@ -4232,6 +4267,9 @@
         <f>'Nach Mannschaften sortiert'!C12</f>
         <v>KM</v>
       </c>
+      <c r="J12" s="108" t="s">
+        <v>146</v>
+      </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B13" s="105">
@@ -4262,6 +4300,9 @@
         <f>'Nach Mannschaften sortiert'!C13</f>
         <v>KM</v>
       </c>
+      <c r="J13" s="108" t="s">
+        <v>146</v>
+      </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B14" s="105">
@@ -4292,6 +4333,9 @@
         <f>'Nach Mannschaften sortiert'!C14</f>
         <v>KM</v>
       </c>
+      <c r="J14" s="108" t="s">
+        <v>146</v>
+      </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B15" s="105">
@@ -4322,6 +4366,9 @@
         <f>'Nach Mannschaften sortiert'!C15</f>
         <v>U23</v>
       </c>
+      <c r="J15" s="108" t="s">
+        <v>146</v>
+      </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B16" s="105">
@@ -4352,8 +4399,11 @@
         <f>'Nach Mannschaften sortiert'!C16</f>
         <v>U23</v>
       </c>
-    </row>
-    <row r="17" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="J16" s="108" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="17" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B17" s="105">
         <f>'Nach Mannschaften sortiert'!D17</f>
         <v>46109</v>
@@ -4382,8 +4432,11 @@
         <f>'Nach Mannschaften sortiert'!C17</f>
         <v>U23</v>
       </c>
-    </row>
-    <row r="18" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="J17" s="108" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="18" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B18" s="105">
         <f>'Nach Mannschaften sortiert'!D18</f>
         <v>46116</v>
@@ -4412,8 +4465,11 @@
         <f>'Nach Mannschaften sortiert'!C18</f>
         <v>U23</v>
       </c>
-    </row>
-    <row r="19" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="J18" s="108" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="19" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B19" s="105">
         <f>'Nach Mannschaften sortiert'!D19</f>
         <v>46124</v>
@@ -4442,8 +4498,11 @@
         <f>'Nach Mannschaften sortiert'!C19</f>
         <v>U23</v>
       </c>
-    </row>
-    <row r="20" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="J19" s="108" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="20" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B20" s="105">
         <f>'Nach Mannschaften sortiert'!D20</f>
         <v>46130</v>
@@ -4472,8 +4531,11 @@
         <f>'Nach Mannschaften sortiert'!C20</f>
         <v>U23</v>
       </c>
-    </row>
-    <row r="21" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="J20" s="108" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="21" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B21" s="105">
         <f>'Nach Mannschaften sortiert'!D21</f>
         <v>46136</v>
@@ -4502,8 +4564,11 @@
         <f>'Nach Mannschaften sortiert'!C21</f>
         <v>U23</v>
       </c>
-    </row>
-    <row r="22" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="J21" s="108" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="22" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B22" s="105">
         <f>'Nach Mannschaften sortiert'!D22</f>
         <v>46144</v>
@@ -4532,8 +4597,11 @@
         <f>'Nach Mannschaften sortiert'!C22</f>
         <v>U23</v>
       </c>
-    </row>
-    <row r="23" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="J22" s="108" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="23" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B23" s="105">
         <f>'Nach Mannschaften sortiert'!D23</f>
         <v>46151</v>
@@ -4562,8 +4630,11 @@
         <f>'Nach Mannschaften sortiert'!C23</f>
         <v>U23</v>
       </c>
-    </row>
-    <row r="24" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="J23" s="108" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="24" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B24" s="105">
         <f>'Nach Mannschaften sortiert'!D24</f>
         <v>46157</v>
@@ -4592,8 +4663,11 @@
         <f>'Nach Mannschaften sortiert'!C24</f>
         <v>U23</v>
       </c>
-    </row>
-    <row r="25" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="J24" s="108" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="25" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B25" s="105">
         <f>'Nach Mannschaften sortiert'!D25</f>
         <v>46166</v>
@@ -4622,8 +4696,11 @@
         <f>'Nach Mannschaften sortiert'!C25</f>
         <v>U23</v>
       </c>
-    </row>
-    <row r="26" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="J25" s="108" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="26" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B26" s="105">
         <f>'Nach Mannschaften sortiert'!D26</f>
         <v>46172</v>
@@ -4652,8 +4729,11 @@
         <f>'Nach Mannschaften sortiert'!C26</f>
         <v>U23</v>
       </c>
-    </row>
-    <row r="27" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="J26" s="108" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="27" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B27" s="105">
         <f>'Nach Mannschaften sortiert'!D27</f>
         <v>46179</v>
@@ -4682,8 +4762,11 @@
         <f>'Nach Mannschaften sortiert'!C27</f>
         <v>U23</v>
       </c>
-    </row>
-    <row r="28" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="J27" s="108" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="28" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B28" s="105">
         <f>'Nach Mannschaften sortiert'!D28</f>
         <v>46110</v>
@@ -4712,8 +4795,11 @@
         <f>'Nach Mannschaften sortiert'!C28</f>
         <v>U16</v>
       </c>
-    </row>
-    <row r="29" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="J28" s="108" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="29" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B29" s="105">
         <f>'Nach Mannschaften sortiert'!D29</f>
         <v>46124</v>
@@ -4742,8 +4828,11 @@
         <f>'Nach Mannschaften sortiert'!C29</f>
         <v>U16</v>
       </c>
-    </row>
-    <row r="30" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="J29" s="108" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="30" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B30" s="105">
         <f>'Nach Mannschaften sortiert'!D30</f>
         <v>46131</v>
@@ -4772,8 +4861,11 @@
         <f>'Nach Mannschaften sortiert'!C30</f>
         <v>U16</v>
       </c>
-    </row>
-    <row r="31" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="J30" s="108" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="31" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B31" s="105">
         <f>'Nach Mannschaften sortiert'!D31</f>
         <v>46138</v>
@@ -4802,8 +4894,11 @@
         <f>'Nach Mannschaften sortiert'!C31</f>
         <v>U16</v>
       </c>
-    </row>
-    <row r="32" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="J31" s="108" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="32" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B32" s="105">
         <f>'Nach Mannschaften sortiert'!D32</f>
         <v>46143</v>
@@ -4831,6 +4926,9 @@
       <c r="I32" t="str">
         <f>'Nach Mannschaften sortiert'!C32</f>
         <v>U16</v>
+      </c>
+      <c r="J32" s="108" t="s">
+        <v>146</v>
       </c>
     </row>
     <row r="33" spans="2:10" x14ac:dyDescent="0.3">
@@ -4862,6 +4960,9 @@
         <f>'Nach Mannschaften sortiert'!C33</f>
         <v>U16</v>
       </c>
+      <c r="J33" s="108" t="s">
+        <v>146</v>
+      </c>
     </row>
     <row r="34" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B34" s="105">
@@ -4892,6 +4993,9 @@
         <f>'Nach Mannschaften sortiert'!C34</f>
         <v>U16</v>
       </c>
+      <c r="J34" s="108" t="s">
+        <v>146</v>
+      </c>
     </row>
     <row r="35" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B35" s="105">
@@ -4922,6 +5026,9 @@
         <f>'Nach Mannschaften sortiert'!C35</f>
         <v>U16</v>
       </c>
+      <c r="J35" s="108" t="s">
+        <v>146</v>
+      </c>
     </row>
     <row r="36" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B36" s="105">
@@ -4952,6 +5059,9 @@
         <f>'Nach Mannschaften sortiert'!C36</f>
         <v>U16</v>
       </c>
+      <c r="J36" s="108" t="s">
+        <v>146</v>
+      </c>
     </row>
     <row r="37" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B37" s="105">
@@ -4982,6 +5092,9 @@
         <f>'Nach Mannschaften sortiert'!C37</f>
         <v>U16</v>
       </c>
+      <c r="J37" s="108" t="s">
+        <v>146</v>
+      </c>
     </row>
     <row r="38" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B38" s="105">
@@ -5012,6 +5125,9 @@
         <f>'Nach Mannschaften sortiert'!C38</f>
         <v>U15</v>
       </c>
+      <c r="J38" s="108" t="s">
+        <v>146</v>
+      </c>
     </row>
     <row r="39" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B39" s="105">
@@ -5042,6 +5158,9 @@
         <f>'Nach Mannschaften sortiert'!C39</f>
         <v>U15</v>
       </c>
+      <c r="J39" s="108" t="s">
+        <v>146</v>
+      </c>
     </row>
     <row r="40" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B40" s="105">
@@ -5072,6 +5191,9 @@
         <f>'Nach Mannschaften sortiert'!C40</f>
         <v>U15</v>
       </c>
+      <c r="J40" s="108" t="s">
+        <v>146</v>
+      </c>
     </row>
     <row r="41" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B41" s="105">
@@ -5102,6 +5224,9 @@
         <f>'Nach Mannschaften sortiert'!C41</f>
         <v>U15</v>
       </c>
+      <c r="J41" s="108" t="s">
+        <v>146</v>
+      </c>
     </row>
     <row r="42" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B42" s="105">
@@ -5132,6 +5257,9 @@
         <f>'Nach Mannschaften sortiert'!C42</f>
         <v>U15</v>
       </c>
+      <c r="J42" s="108" t="s">
+        <v>146</v>
+      </c>
     </row>
     <row r="43" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B43" s="105">
@@ -5162,6 +5290,9 @@
         <f>'Nach Mannschaften sortiert'!C43</f>
         <v>U15</v>
       </c>
+      <c r="J43" s="108" t="s">
+        <v>146</v>
+      </c>
     </row>
     <row r="44" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B44" s="105">
@@ -5192,6 +5323,9 @@
         <f>'Nach Mannschaften sortiert'!C44</f>
         <v>U15</v>
       </c>
+      <c r="J44" s="108" t="s">
+        <v>146</v>
+      </c>
     </row>
     <row r="45" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B45" s="105">
@@ -5222,6 +5356,9 @@
         <f>'Nach Mannschaften sortiert'!C45</f>
         <v>U15</v>
       </c>
+      <c r="J45" s="108" t="s">
+        <v>146</v>
+      </c>
     </row>
     <row r="46" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B46" s="105">
@@ -5252,7 +5389,7 @@
         <f>'Nach Mannschaften sortiert'!C46</f>
         <v>U14</v>
       </c>
-      <c r="J46" t="s">
+      <c r="J46" s="108" t="s">
         <v>144</v>
       </c>
     </row>
@@ -5285,6 +5422,9 @@
         <f>'Nach Mannschaften sortiert'!C47</f>
         <v>U14</v>
       </c>
+      <c r="J47" s="108" t="s">
+        <v>146</v>
+      </c>
     </row>
     <row r="48" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B48" s="105">
@@ -5315,6 +5455,9 @@
         <f>'Nach Mannschaften sortiert'!C48</f>
         <v>U14</v>
       </c>
+      <c r="J48" s="108" t="s">
+        <v>146</v>
+      </c>
     </row>
     <row r="49" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B49" s="105">
@@ -5345,6 +5488,9 @@
         <f>'Nach Mannschaften sortiert'!C49</f>
         <v>U14</v>
       </c>
+      <c r="J49" s="108" t="s">
+        <v>146</v>
+      </c>
     </row>
     <row r="50" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B50" s="105">
@@ -5375,6 +5521,9 @@
         <f>'Nach Mannschaften sortiert'!C50</f>
         <v>U14</v>
       </c>
+      <c r="J50" s="108" t="s">
+        <v>146</v>
+      </c>
     </row>
     <row r="51" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B51" s="105">
@@ -5405,6 +5554,9 @@
         <f>'Nach Mannschaften sortiert'!C51</f>
         <v>U14</v>
       </c>
+      <c r="J51" s="108" t="s">
+        <v>146</v>
+      </c>
     </row>
     <row r="52" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B52" s="105">
@@ -5435,6 +5587,9 @@
         <f>'Nach Mannschaften sortiert'!C52</f>
         <v>U14</v>
       </c>
+      <c r="J52" s="108" t="s">
+        <v>146</v>
+      </c>
     </row>
     <row r="53" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B53" s="105">
@@ -5465,6 +5620,9 @@
         <f>'Nach Mannschaften sortiert'!C53</f>
         <v>U14</v>
       </c>
+      <c r="J53" s="108" t="s">
+        <v>146</v>
+      </c>
     </row>
     <row r="54" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B54" s="105">
@@ -5495,7 +5653,7 @@
         <f>'Nach Mannschaften sortiert'!C54</f>
         <v>U13</v>
       </c>
-      <c r="J54" t="s">
+      <c r="J54" s="108" t="s">
         <v>144</v>
       </c>
     </row>
@@ -5528,6 +5686,9 @@
         <f>'Nach Mannschaften sortiert'!C55</f>
         <v>U13</v>
       </c>
+      <c r="J55" s="108" t="s">
+        <v>146</v>
+      </c>
     </row>
     <row r="56" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B56" s="105">
@@ -5558,6 +5719,9 @@
         <f>'Nach Mannschaften sortiert'!C56</f>
         <v>U13</v>
       </c>
+      <c r="J56" s="108" t="s">
+        <v>146</v>
+      </c>
     </row>
     <row r="57" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B57" s="105">
@@ -5588,6 +5752,9 @@
         <f>'Nach Mannschaften sortiert'!C57</f>
         <v>U13</v>
       </c>
+      <c r="J57" s="108" t="s">
+        <v>146</v>
+      </c>
     </row>
     <row r="58" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B58" s="105">
@@ -5618,6 +5785,9 @@
         <f>'Nach Mannschaften sortiert'!C58</f>
         <v>U13</v>
       </c>
+      <c r="J58" s="108" t="s">
+        <v>146</v>
+      </c>
     </row>
     <row r="59" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B59" s="105">
@@ -5648,6 +5818,9 @@
         <f>'Nach Mannschaften sortiert'!C59</f>
         <v>U13</v>
       </c>
+      <c r="J59" s="108" t="s">
+        <v>146</v>
+      </c>
     </row>
     <row r="60" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B60" s="105">
@@ -5678,6 +5851,9 @@
         <f>'Nach Mannschaften sortiert'!C60</f>
         <v>U13</v>
       </c>
+      <c r="J60" s="108" t="s">
+        <v>146</v>
+      </c>
     </row>
     <row r="61" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B61" s="105">
@@ -5708,6 +5884,9 @@
         <f>'Nach Mannschaften sortiert'!C61</f>
         <v>U13</v>
       </c>
+      <c r="J61" s="108" t="s">
+        <v>146</v>
+      </c>
     </row>
     <row r="62" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B62" s="105">
@@ -5738,6 +5917,9 @@
         <f>'Nach Mannschaften sortiert'!C62</f>
         <v>U11</v>
       </c>
+      <c r="J62" s="108" t="s">
+        <v>146</v>
+      </c>
     </row>
     <row r="63" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B63" s="105">
@@ -5768,6 +5950,9 @@
         <f>'Nach Mannschaften sortiert'!C63</f>
         <v>U11</v>
       </c>
+      <c r="J63" s="108" t="s">
+        <v>146</v>
+      </c>
     </row>
     <row r="64" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B64" s="105">
@@ -5798,8 +5983,11 @@
         <f>'Nach Mannschaften sortiert'!C64</f>
         <v>U11</v>
       </c>
-    </row>
-    <row r="65" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="J64" s="108" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="65" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B65" s="105">
         <f>'Nach Mannschaften sortiert'!D65</f>
         <v>46135</v>
@@ -5828,8 +6016,11 @@
         <f>'Nach Mannschaften sortiert'!C65</f>
         <v>U11</v>
       </c>
-    </row>
-    <row r="66" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="J65" s="108" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="66" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B66" s="105">
         <f>'Nach Mannschaften sortiert'!D66</f>
         <v>46151</v>
@@ -5858,8 +6049,11 @@
         <f>'Nach Mannschaften sortiert'!C66</f>
         <v>U11</v>
       </c>
-    </row>
-    <row r="67" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="J66" s="108" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="67" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B67" s="105">
         <f>'Nach Mannschaften sortiert'!D67</f>
         <v>46159</v>
@@ -5888,8 +6082,11 @@
         <f>'Nach Mannschaften sortiert'!C67</f>
         <v>U11</v>
       </c>
-    </row>
-    <row r="68" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="J67" s="108" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="68" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B68" s="105">
         <f>'Nach Mannschaften sortiert'!D68</f>
         <v>46164</v>
@@ -5918,8 +6115,11 @@
         <f>'Nach Mannschaften sortiert'!C68</f>
         <v>U11</v>
       </c>
-    </row>
-    <row r="69" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="J68" s="108" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="69" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B69" s="105">
         <f>'Nach Mannschaften sortiert'!D69</f>
         <v>46171</v>
@@ -5948,8 +6148,11 @@
         <f>'Nach Mannschaften sortiert'!C69</f>
         <v>U11</v>
       </c>
-    </row>
-    <row r="70" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="J69" s="108" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="70" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B70" s="105">
         <f>'Nach Mannschaften sortiert'!D70</f>
         <v>46123</v>
@@ -5978,8 +6181,11 @@
         <f>'Nach Mannschaften sortiert'!C70</f>
         <v>U9</v>
       </c>
-    </row>
-    <row r="71" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="J70" s="108" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="71" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B71" s="105">
         <f>'Nach Mannschaften sortiert'!D71</f>
         <v>46130</v>
@@ -6008,8 +6214,11 @@
         <f>'Nach Mannschaften sortiert'!C71</f>
         <v>U9</v>
       </c>
-    </row>
-    <row r="72" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="J71" s="108" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="72" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B72" s="105">
         <f>'Nach Mannschaften sortiert'!D72</f>
         <v>46137</v>
@@ -6038,8 +6247,11 @@
         <f>'Nach Mannschaften sortiert'!C72</f>
         <v>U9</v>
       </c>
-    </row>
-    <row r="73" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="J72" s="108" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="73" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B73" s="105">
         <f>'Nach Mannschaften sortiert'!D73</f>
         <v>46151</v>
@@ -6068,8 +6280,11 @@
         <f>'Nach Mannschaften sortiert'!C73</f>
         <v>U9</v>
       </c>
-    </row>
-    <row r="74" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="J73" s="108" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="74" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B74" s="105">
         <f>'Nach Mannschaften sortiert'!D74</f>
         <v>46194</v>
@@ -6098,8 +6313,11 @@
         <f>'Nach Mannschaften sortiert'!C74</f>
         <v>U9</v>
       </c>
-    </row>
-    <row r="75" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="J74" s="108" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="75" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B75" s="105">
         <f>'Nach Mannschaften sortiert'!D75</f>
         <v>46123</v>
@@ -6128,8 +6346,11 @@
         <f>'Nach Mannschaften sortiert'!C75</f>
         <v>U8</v>
       </c>
-    </row>
-    <row r="76" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="J75" s="108" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="76" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B76" s="105">
         <f>'Nach Mannschaften sortiert'!D76</f>
         <v>46137</v>
@@ -6158,8 +6379,11 @@
         <f>'Nach Mannschaften sortiert'!C76</f>
         <v>U8</v>
       </c>
-    </row>
-    <row r="77" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="J76" s="108" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="77" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B77" s="105">
         <f>'Nach Mannschaften sortiert'!D77</f>
         <v>46144</v>
@@ -6188,8 +6412,11 @@
         <f>'Nach Mannschaften sortiert'!C77</f>
         <v>U8</v>
       </c>
-    </row>
-    <row r="78" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="J77" s="108" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="78" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B78" s="105">
         <f>'Nach Mannschaften sortiert'!D78</f>
         <v>46151</v>
@@ -6218,8 +6445,11 @@
         <f>'Nach Mannschaften sortiert'!C78</f>
         <v>U8</v>
       </c>
-    </row>
-    <row r="79" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="J78" s="108" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="79" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B79" s="105">
         <f>'Nach Mannschaften sortiert'!D79</f>
         <v>46180</v>
@@ -6248,8 +6478,11 @@
         <f>'Nach Mannschaften sortiert'!C79</f>
         <v>U8</v>
       </c>
-    </row>
-    <row r="80" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="J79" s="108" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="80" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B80" s="105">
         <f>'Nach Mannschaften sortiert'!D80</f>
         <v>46123</v>
@@ -6278,8 +6511,11 @@
         <f>'Nach Mannschaften sortiert'!C80</f>
         <v>U7</v>
       </c>
-    </row>
-    <row r="81" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="J80" s="108" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="81" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B81" s="105">
         <f>'Nach Mannschaften sortiert'!D81</f>
         <v>46131</v>
@@ -6308,8 +6544,11 @@
         <f>'Nach Mannschaften sortiert'!C81</f>
         <v>U7</v>
       </c>
-    </row>
-    <row r="82" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="J81" s="108" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="82" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B82" s="105">
         <f>'Nach Mannschaften sortiert'!D82</f>
         <v>46143</v>
@@ -6338,8 +6577,11 @@
         <f>'Nach Mannschaften sortiert'!C82</f>
         <v>U7</v>
       </c>
-    </row>
-    <row r="83" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="J82" s="108" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="83" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B83" s="105">
         <f>'Nach Mannschaften sortiert'!D83</f>
         <v>46151</v>
@@ -6368,8 +6610,11 @@
         <f>'Nach Mannschaften sortiert'!C83</f>
         <v>U7</v>
       </c>
-    </row>
-    <row r="84" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="J83" s="108" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="84" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B84" s="105">
         <f>'Nach Mannschaften sortiert'!D84</f>
         <v>46187</v>
@@ -6398,8 +6643,11 @@
         <f>'Nach Mannschaften sortiert'!C84</f>
         <v>U7</v>
       </c>
-    </row>
-    <row r="85" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="J84" s="108" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="85" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B85" s="105">
         <f>'Nach Mannschaften sortiert'!D85</f>
         <v>46111</v>
@@ -6427,8 +6675,11 @@
         <f>'Nach Mannschaften sortiert'!C85</f>
         <v>Camp</v>
       </c>
-    </row>
-    <row r="86" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="J85" s="108" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="86" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B86" s="105">
         <f>'Nach Mannschaften sortiert'!D86</f>
         <v>46112</v>
@@ -6456,8 +6707,11 @@
         <f>'Nach Mannschaften sortiert'!C86</f>
         <v>Camp</v>
       </c>
-    </row>
-    <row r="87" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="J86" s="108" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="87" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B87" s="105">
         <f>'Nach Mannschaften sortiert'!D87</f>
         <v>46113</v>
@@ -6485,8 +6739,11 @@
         <f>'Nach Mannschaften sortiert'!C87</f>
         <v>Camp</v>
       </c>
-    </row>
-    <row r="88" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="J87" s="108" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="88" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B88" s="105">
         <f>'Nach Mannschaften sortiert'!D88</f>
         <v>46186</v>
@@ -6514,8 +6771,11 @@
         <f>'Nach Mannschaften sortiert'!C88</f>
         <v>GGG</v>
       </c>
-    </row>
-    <row r="89" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="J88" s="108" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="89" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B89" s="105">
         <f>'Nach Mannschaften sortiert'!D89</f>
         <v>46256</v>
@@ -6542,6 +6802,9 @@
       <c r="I89" t="str">
         <f>'Nach Mannschaften sortiert'!C89</f>
         <v>GGG</v>
+      </c>
+      <c r="J89" s="108" t="s">
+        <v>146</v>
       </c>
     </row>
   </sheetData>

--- a/Terminefussball_2026_Frühjahr.xlsx
+++ b/Terminefussball_2026_Frühjahr.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DTB\asv-neufeld\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D899345-8C00-4374-8205-340837328209}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73F61DF4-A06E-4411-B0B4-AB443A070F43}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4343,12 +4343,11 @@
         <v>46096</v>
       </c>
       <c r="C15" s="39">
-        <f>'Nach Mannschaften sortiert'!E15</f>
-        <v>0.64583333333333337</v>
+        <v>0.5625</v>
       </c>
       <c r="D15" s="39">
         <f t="shared" si="0"/>
-        <v>0.71875</v>
+        <v>0.63541666666666663</v>
       </c>
       <c r="E15" s="39" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F15)</f>
@@ -4376,12 +4375,11 @@
         <v>46102</v>
       </c>
       <c r="C16" s="39">
-        <f>'Nach Mannschaften sortiert'!E16</f>
-        <v>0.66666666666666663</v>
+        <v>0.58333333333333337</v>
       </c>
       <c r="D16" s="39">
         <f t="shared" si="0"/>
-        <v>0.73958333333333326</v>
+        <v>0.65625</v>
       </c>
       <c r="E16" s="39" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F16)</f>
@@ -4409,12 +4407,11 @@
         <v>46109</v>
       </c>
       <c r="C17" s="39">
-        <f>'Nach Mannschaften sortiert'!E17</f>
-        <v>0.64583333333333337</v>
+        <v>0.5625</v>
       </c>
       <c r="D17" s="39">
         <f t="shared" si="0"/>
-        <v>0.71875</v>
+        <v>0.63541666666666663</v>
       </c>
       <c r="E17" s="39" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F17)</f>
@@ -4442,12 +4439,11 @@
         <v>46116</v>
       </c>
       <c r="C18" s="39">
-        <f>'Nach Mannschaften sortiert'!E18</f>
-        <v>0.70833333333333337</v>
+        <v>0.625</v>
       </c>
       <c r="D18" s="39">
         <f t="shared" si="0"/>
-        <v>0.78125</v>
+        <v>0.69791666666666663</v>
       </c>
       <c r="E18" s="39" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F18)</f>
@@ -4475,12 +4471,11 @@
         <v>46124</v>
       </c>
       <c r="C19" s="39">
-        <f>'Nach Mannschaften sortiert'!E19</f>
-        <v>0.66666666666666663</v>
+        <v>0.58333333333333337</v>
       </c>
       <c r="D19" s="39">
         <f t="shared" si="0"/>
-        <v>0.73958333333333326</v>
+        <v>0.65625</v>
       </c>
       <c r="E19" s="39" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F19)</f>
@@ -4508,12 +4503,11 @@
         <v>46130</v>
       </c>
       <c r="C20" s="39">
-        <f>'Nach Mannschaften sortiert'!E20</f>
-        <v>0.72916666666666663</v>
+        <v>0.64583333333333337</v>
       </c>
       <c r="D20" s="39">
         <f t="shared" si="0"/>
-        <v>0.80208333333333326</v>
+        <v>0.71875</v>
       </c>
       <c r="E20" s="39" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F20)</f>
@@ -4541,12 +4535,11 @@
         <v>46136</v>
       </c>
       <c r="C21" s="39">
-        <f>'Nach Mannschaften sortiert'!E21</f>
-        <v>0.83333333333333337</v>
+        <v>0.75</v>
       </c>
       <c r="D21" s="39">
         <f t="shared" si="0"/>
-        <v>0.90625</v>
+        <v>0.82291666666666663</v>
       </c>
       <c r="E21" s="39" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F21)</f>
@@ -4574,12 +4567,11 @@
         <v>46144</v>
       </c>
       <c r="C22" s="39">
-        <f>'Nach Mannschaften sortiert'!E22</f>
-        <v>0.75</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="D22" s="39">
         <f t="shared" si="0"/>
-        <v>0.82291666666666663</v>
+        <v>0.73958333333333326</v>
       </c>
       <c r="E22" s="39" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F22)</f>
@@ -4607,12 +4599,11 @@
         <v>46151</v>
       </c>
       <c r="C23" s="39">
-        <f>'Nach Mannschaften sortiert'!E23</f>
-        <v>0.72916666666666663</v>
+        <v>0.64583333333333337</v>
       </c>
       <c r="D23" s="39">
         <f t="shared" si="0"/>
-        <v>0.80208333333333326</v>
+        <v>0.71875</v>
       </c>
       <c r="E23" s="39" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F23)</f>
@@ -4640,12 +4631,11 @@
         <v>46157</v>
       </c>
       <c r="C24" s="39">
-        <f>'Nach Mannschaften sortiert'!E24</f>
-        <v>0.83333333333333337</v>
+        <v>0.75</v>
       </c>
       <c r="D24" s="39">
         <f t="shared" si="0"/>
-        <v>0.90625</v>
+        <v>0.82291666666666663</v>
       </c>
       <c r="E24" s="39" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F24)</f>
@@ -4673,12 +4663,11 @@
         <v>46166</v>
       </c>
       <c r="C25" s="39">
-        <f>'Nach Mannschaften sortiert'!E25</f>
-        <v>0.77083333333333337</v>
+        <v>0.6875</v>
       </c>
       <c r="D25" s="39">
         <f t="shared" si="0"/>
-        <v>0.84375</v>
+        <v>0.76041666666666663</v>
       </c>
       <c r="E25" s="39" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F25)</f>
@@ -4706,12 +4695,11 @@
         <v>46172</v>
       </c>
       <c r="C26" s="39">
-        <f>'Nach Mannschaften sortiert'!E26</f>
-        <v>0.77083333333333337</v>
+        <v>0.6875</v>
       </c>
       <c r="D26" s="39">
         <f t="shared" si="0"/>
-        <v>0.84375</v>
+        <v>0.76041666666666663</v>
       </c>
       <c r="E26" s="39" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F26)</f>
@@ -4739,12 +4727,11 @@
         <v>46179</v>
       </c>
       <c r="C27" s="39">
-        <f>'Nach Mannschaften sortiert'!E27</f>
-        <v>0.75</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="D27" s="39">
         <f t="shared" si="0"/>
-        <v>0.82291666666666663</v>
+        <v>0.73958333333333326</v>
       </c>
       <c r="E27" s="39" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F27)</f>

--- a/Terminefussball_2026_Frühjahr.xlsx
+++ b/Terminefussball_2026_Frühjahr.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DTB\asv-neufeld\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73F61DF4-A06E-4411-B0B4-AB443A070F43}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D59280B6-1381-432F-81BC-521341DE7364}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -478,13 +478,13 @@
     <t>GGG</t>
   </si>
   <si>
-    <t>ABGESAGT!!!</t>
-  </si>
-  <si>
     <t>STATUS</t>
   </si>
   <si>
     <t>aktiv</t>
+  </si>
+  <si>
+    <t>abgesagt</t>
   </si>
 </sst>
 </file>
@@ -3905,7 +3905,7 @@
         <v>140</v>
       </c>
       <c r="J1" s="108" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.3">
@@ -3938,7 +3938,7 @@
         <v>KM</v>
       </c>
       <c r="J2" s="108" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.3">
@@ -3971,7 +3971,7 @@
         <v>KM</v>
       </c>
       <c r="J3" s="108" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.3">
@@ -4004,7 +4004,7 @@
         <v>KM</v>
       </c>
       <c r="J4" s="108" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.3">
@@ -4037,7 +4037,7 @@
         <v>KM</v>
       </c>
       <c r="J5" s="108" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.3">
@@ -4070,7 +4070,7 @@
         <v>KM</v>
       </c>
       <c r="J6" s="108" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.3">
@@ -4103,7 +4103,7 @@
         <v>KM</v>
       </c>
       <c r="J7" s="108" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.3">
@@ -4136,7 +4136,7 @@
         <v>KM</v>
       </c>
       <c r="J8" s="108" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.3">
@@ -4169,7 +4169,7 @@
         <v>KM</v>
       </c>
       <c r="J9" s="108" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.3">
@@ -4202,7 +4202,7 @@
         <v>KM</v>
       </c>
       <c r="J10" s="108" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.3">
@@ -4235,7 +4235,7 @@
         <v>KM</v>
       </c>
       <c r="J11" s="108" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.3">
@@ -4268,7 +4268,7 @@
         <v>KM</v>
       </c>
       <c r="J12" s="108" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.3">
@@ -4301,7 +4301,7 @@
         <v>KM</v>
       </c>
       <c r="J13" s="108" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.3">
@@ -4334,7 +4334,7 @@
         <v>KM</v>
       </c>
       <c r="J14" s="108" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.3">
@@ -4366,7 +4366,7 @@
         <v>U23</v>
       </c>
       <c r="J15" s="108" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.3">
@@ -4398,7 +4398,7 @@
         <v>U23</v>
       </c>
       <c r="J16" s="108" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="17" spans="2:10" x14ac:dyDescent="0.3">
@@ -4430,7 +4430,7 @@
         <v>U23</v>
       </c>
       <c r="J17" s="108" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="18" spans="2:10" x14ac:dyDescent="0.3">
@@ -4462,7 +4462,7 @@
         <v>U23</v>
       </c>
       <c r="J18" s="108" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="19" spans="2:10" x14ac:dyDescent="0.3">
@@ -4494,7 +4494,7 @@
         <v>U23</v>
       </c>
       <c r="J19" s="108" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="20" spans="2:10" x14ac:dyDescent="0.3">
@@ -4526,7 +4526,7 @@
         <v>U23</v>
       </c>
       <c r="J20" s="108" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="21" spans="2:10" x14ac:dyDescent="0.3">
@@ -4558,7 +4558,7 @@
         <v>U23</v>
       </c>
       <c r="J21" s="108" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="22" spans="2:10" x14ac:dyDescent="0.3">
@@ -4590,7 +4590,7 @@
         <v>U23</v>
       </c>
       <c r="J22" s="108" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="23" spans="2:10" x14ac:dyDescent="0.3">
@@ -4622,7 +4622,7 @@
         <v>U23</v>
       </c>
       <c r="J23" s="108" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="24" spans="2:10" x14ac:dyDescent="0.3">
@@ -4654,7 +4654,7 @@
         <v>U23</v>
       </c>
       <c r="J24" s="108" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="25" spans="2:10" x14ac:dyDescent="0.3">
@@ -4686,7 +4686,7 @@
         <v>U23</v>
       </c>
       <c r="J25" s="108" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="26" spans="2:10" x14ac:dyDescent="0.3">
@@ -4718,7 +4718,7 @@
         <v>U23</v>
       </c>
       <c r="J26" s="108" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="27" spans="2:10" x14ac:dyDescent="0.3">
@@ -4750,7 +4750,7 @@
         <v>U23</v>
       </c>
       <c r="J27" s="108" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="28" spans="2:10" x14ac:dyDescent="0.3">
@@ -4783,7 +4783,7 @@
         <v>U16</v>
       </c>
       <c r="J28" s="108" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="29" spans="2:10" x14ac:dyDescent="0.3">
@@ -4816,7 +4816,7 @@
         <v>U16</v>
       </c>
       <c r="J29" s="108" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="30" spans="2:10" x14ac:dyDescent="0.3">
@@ -4849,7 +4849,7 @@
         <v>U16</v>
       </c>
       <c r="J30" s="108" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="31" spans="2:10" x14ac:dyDescent="0.3">
@@ -4882,7 +4882,7 @@
         <v>U16</v>
       </c>
       <c r="J31" s="108" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="32" spans="2:10" x14ac:dyDescent="0.3">
@@ -4915,7 +4915,7 @@
         <v>U16</v>
       </c>
       <c r="J32" s="108" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="33" spans="2:10" x14ac:dyDescent="0.3">
@@ -4948,7 +4948,7 @@
         <v>U16</v>
       </c>
       <c r="J33" s="108" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="34" spans="2:10" x14ac:dyDescent="0.3">
@@ -4981,7 +4981,7 @@
         <v>U16</v>
       </c>
       <c r="J34" s="108" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="35" spans="2:10" x14ac:dyDescent="0.3">
@@ -5014,7 +5014,7 @@
         <v>U16</v>
       </c>
       <c r="J35" s="108" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="36" spans="2:10" x14ac:dyDescent="0.3">
@@ -5047,7 +5047,7 @@
         <v>U16</v>
       </c>
       <c r="J36" s="108" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="37" spans="2:10" x14ac:dyDescent="0.3">
@@ -5080,7 +5080,7 @@
         <v>U16</v>
       </c>
       <c r="J37" s="108" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="38" spans="2:10" x14ac:dyDescent="0.3">
@@ -5113,7 +5113,7 @@
         <v>U15</v>
       </c>
       <c r="J38" s="108" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="39" spans="2:10" x14ac:dyDescent="0.3">
@@ -5146,7 +5146,7 @@
         <v>U15</v>
       </c>
       <c r="J39" s="108" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="40" spans="2:10" x14ac:dyDescent="0.3">
@@ -5179,7 +5179,7 @@
         <v>U15</v>
       </c>
       <c r="J40" s="108" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="41" spans="2:10" x14ac:dyDescent="0.3">
@@ -5212,7 +5212,7 @@
         <v>U15</v>
       </c>
       <c r="J41" s="108" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="42" spans="2:10" x14ac:dyDescent="0.3">
@@ -5245,7 +5245,7 @@
         <v>U15</v>
       </c>
       <c r="J42" s="108" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="43" spans="2:10" x14ac:dyDescent="0.3">
@@ -5278,7 +5278,7 @@
         <v>U15</v>
       </c>
       <c r="J43" s="108" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="44" spans="2:10" x14ac:dyDescent="0.3">
@@ -5311,7 +5311,7 @@
         <v>U15</v>
       </c>
       <c r="J44" s="108" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="45" spans="2:10" x14ac:dyDescent="0.3">
@@ -5344,7 +5344,7 @@
         <v>U15</v>
       </c>
       <c r="J45" s="108" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="46" spans="2:10" x14ac:dyDescent="0.3">
@@ -5377,7 +5377,7 @@
         <v>U14</v>
       </c>
       <c r="J46" s="108" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
     </row>
     <row r="47" spans="2:10" x14ac:dyDescent="0.3">
@@ -5410,7 +5410,7 @@
         <v>U14</v>
       </c>
       <c r="J47" s="108" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="48" spans="2:10" x14ac:dyDescent="0.3">
@@ -5443,7 +5443,7 @@
         <v>U14</v>
       </c>
       <c r="J48" s="108" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="49" spans="2:10" x14ac:dyDescent="0.3">
@@ -5476,7 +5476,7 @@
         <v>U14</v>
       </c>
       <c r="J49" s="108" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="50" spans="2:10" x14ac:dyDescent="0.3">
@@ -5509,7 +5509,7 @@
         <v>U14</v>
       </c>
       <c r="J50" s="108" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="51" spans="2:10" x14ac:dyDescent="0.3">
@@ -5542,7 +5542,7 @@
         <v>U14</v>
       </c>
       <c r="J51" s="108" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="52" spans="2:10" x14ac:dyDescent="0.3">
@@ -5575,7 +5575,7 @@
         <v>U14</v>
       </c>
       <c r="J52" s="108" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="53" spans="2:10" x14ac:dyDescent="0.3">
@@ -5608,7 +5608,7 @@
         <v>U14</v>
       </c>
       <c r="J53" s="108" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="54" spans="2:10" x14ac:dyDescent="0.3">
@@ -5641,7 +5641,7 @@
         <v>U13</v>
       </c>
       <c r="J54" s="108" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
     </row>
     <row r="55" spans="2:10" x14ac:dyDescent="0.3">
@@ -5674,7 +5674,7 @@
         <v>U13</v>
       </c>
       <c r="J55" s="108" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="56" spans="2:10" x14ac:dyDescent="0.3">
@@ -5707,7 +5707,7 @@
         <v>U13</v>
       </c>
       <c r="J56" s="108" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="57" spans="2:10" x14ac:dyDescent="0.3">
@@ -5740,7 +5740,7 @@
         <v>U13</v>
       </c>
       <c r="J57" s="108" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="58" spans="2:10" x14ac:dyDescent="0.3">
@@ -5773,7 +5773,7 @@
         <v>U13</v>
       </c>
       <c r="J58" s="108" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="59" spans="2:10" x14ac:dyDescent="0.3">
@@ -5806,7 +5806,7 @@
         <v>U13</v>
       </c>
       <c r="J59" s="108" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="60" spans="2:10" x14ac:dyDescent="0.3">
@@ -5839,7 +5839,7 @@
         <v>U13</v>
       </c>
       <c r="J60" s="108" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="61" spans="2:10" x14ac:dyDescent="0.3">
@@ -5872,7 +5872,7 @@
         <v>U13</v>
       </c>
       <c r="J61" s="108" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="62" spans="2:10" x14ac:dyDescent="0.3">
@@ -5905,7 +5905,7 @@
         <v>U11</v>
       </c>
       <c r="J62" s="108" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="63" spans="2:10" x14ac:dyDescent="0.3">
@@ -5938,7 +5938,7 @@
         <v>U11</v>
       </c>
       <c r="J63" s="108" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="64" spans="2:10" x14ac:dyDescent="0.3">
@@ -5971,7 +5971,7 @@
         <v>U11</v>
       </c>
       <c r="J64" s="108" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="65" spans="2:10" x14ac:dyDescent="0.3">
@@ -6004,7 +6004,7 @@
         <v>U11</v>
       </c>
       <c r="J65" s="108" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="66" spans="2:10" x14ac:dyDescent="0.3">
@@ -6037,7 +6037,7 @@
         <v>U11</v>
       </c>
       <c r="J66" s="108" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="67" spans="2:10" x14ac:dyDescent="0.3">
@@ -6070,7 +6070,7 @@
         <v>U11</v>
       </c>
       <c r="J67" s="108" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="68" spans="2:10" x14ac:dyDescent="0.3">
@@ -6103,7 +6103,7 @@
         <v>U11</v>
       </c>
       <c r="J68" s="108" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="69" spans="2:10" x14ac:dyDescent="0.3">
@@ -6136,7 +6136,7 @@
         <v>U11</v>
       </c>
       <c r="J69" s="108" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="70" spans="2:10" x14ac:dyDescent="0.3">
@@ -6169,7 +6169,7 @@
         <v>U9</v>
       </c>
       <c r="J70" s="108" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="71" spans="2:10" x14ac:dyDescent="0.3">
@@ -6202,7 +6202,7 @@
         <v>U9</v>
       </c>
       <c r="J71" s="108" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="72" spans="2:10" x14ac:dyDescent="0.3">
@@ -6235,7 +6235,7 @@
         <v>U9</v>
       </c>
       <c r="J72" s="108" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="73" spans="2:10" x14ac:dyDescent="0.3">
@@ -6268,7 +6268,7 @@
         <v>U9</v>
       </c>
       <c r="J73" s="108" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="74" spans="2:10" x14ac:dyDescent="0.3">
@@ -6301,7 +6301,7 @@
         <v>U9</v>
       </c>
       <c r="J74" s="108" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="75" spans="2:10" x14ac:dyDescent="0.3">
@@ -6334,7 +6334,7 @@
         <v>U8</v>
       </c>
       <c r="J75" s="108" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="76" spans="2:10" x14ac:dyDescent="0.3">
@@ -6367,7 +6367,7 @@
         <v>U8</v>
       </c>
       <c r="J76" s="108" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="77" spans="2:10" x14ac:dyDescent="0.3">
@@ -6400,7 +6400,7 @@
         <v>U8</v>
       </c>
       <c r="J77" s="108" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="78" spans="2:10" x14ac:dyDescent="0.3">
@@ -6433,7 +6433,7 @@
         <v>U8</v>
       </c>
       <c r="J78" s="108" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="79" spans="2:10" x14ac:dyDescent="0.3">
@@ -6466,7 +6466,7 @@
         <v>U8</v>
       </c>
       <c r="J79" s="108" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="80" spans="2:10" x14ac:dyDescent="0.3">
@@ -6499,7 +6499,7 @@
         <v>U7</v>
       </c>
       <c r="J80" s="108" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="81" spans="2:10" x14ac:dyDescent="0.3">
@@ -6532,7 +6532,7 @@
         <v>U7</v>
       </c>
       <c r="J81" s="108" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="82" spans="2:10" x14ac:dyDescent="0.3">
@@ -6565,7 +6565,7 @@
         <v>U7</v>
       </c>
       <c r="J82" s="108" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="83" spans="2:10" x14ac:dyDescent="0.3">
@@ -6598,7 +6598,7 @@
         <v>U7</v>
       </c>
       <c r="J83" s="108" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="84" spans="2:10" x14ac:dyDescent="0.3">
@@ -6631,7 +6631,7 @@
         <v>U7</v>
       </c>
       <c r="J84" s="108" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="85" spans="2:10" x14ac:dyDescent="0.3">
@@ -6663,7 +6663,7 @@
         <v>Camp</v>
       </c>
       <c r="J85" s="108" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="86" spans="2:10" x14ac:dyDescent="0.3">
@@ -6695,7 +6695,7 @@
         <v>Camp</v>
       </c>
       <c r="J86" s="108" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="87" spans="2:10" x14ac:dyDescent="0.3">
@@ -6727,7 +6727,7 @@
         <v>Camp</v>
       </c>
       <c r="J87" s="108" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="88" spans="2:10" x14ac:dyDescent="0.3">
@@ -6759,7 +6759,7 @@
         <v>GGG</v>
       </c>
       <c r="J88" s="108" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="89" spans="2:10" x14ac:dyDescent="0.3">
@@ -6791,7 +6791,7 @@
         <v>GGG</v>
       </c>
       <c r="J89" s="108" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
   </sheetData>

--- a/Terminefussball_2026_Frühjahr.xlsx
+++ b/Terminefussball_2026_Frühjahr.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DTB\asv-neufeld\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D59280B6-1381-432F-81BC-521341DE7364}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90919E9B-23AA-40B1-9F68-898F9F8437E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="642" uniqueCount="147">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="643" uniqueCount="148">
   <si>
     <t>Mannschaft</t>
   </si>
@@ -485,6 +485,9 @@
   </si>
   <si>
     <t>abgesagt</t>
+  </si>
+  <si>
+    <t>Endstand:2:2</t>
   </si>
 </sst>
 </file>
@@ -4755,20 +4758,21 @@
     </row>
     <row r="28" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B28" s="105">
-        <f>'Nach Mannschaften sortiert'!D28</f>
-        <v>46110</v>
+        <v>46106</v>
       </c>
       <c r="C28" s="39">
-        <f>'Nach Mannschaften sortiert'!E28</f>
-        <v>0.66666666666666663</v>
+        <v>0.77083333333333337</v>
       </c>
       <c r="D28" s="39">
         <f t="shared" si="0"/>
-        <v>0.73958333333333326</v>
+        <v>0.84375</v>
       </c>
       <c r="E28" s="39" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F28)</f>
         <v>SV LEITHAPRODERSDORF</v>
+      </c>
+      <c r="F28" s="108" t="s">
+        <v>147</v>
       </c>
       <c r="G28" s="108" t="str">
         <f>'Nach Mannschaften sortiert'!H28</f>

--- a/Terminefussball_2026_Frühjahr.xlsx
+++ b/Terminefussball_2026_Frühjahr.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DTB\asv-neufeld\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90919E9B-23AA-40B1-9F68-898F9F8437E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D727DD9-7649-4E8E-AAE6-BB3C35FC326E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="643" uniqueCount="148">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="650" uniqueCount="155">
   <si>
     <t>Mannschaft</t>
   </si>
@@ -488,6 +488,27 @@
   </si>
   <si>
     <t>Endstand:2:2</t>
+  </si>
+  <si>
+    <t>Endstand:1:1</t>
+  </si>
+  <si>
+    <t>Endstand:3:3</t>
+  </si>
+  <si>
+    <t>Endstand:5:1 für Rust</t>
+  </si>
+  <si>
+    <t>Endstand:3:0 für Rust</t>
+  </si>
+  <si>
+    <t>Endstand:2:1 für Neufeld</t>
+  </si>
+  <si>
+    <t>Endstand:0:2 für Gattendorf</t>
+  </si>
+  <si>
+    <t>Endstand:4:0 für Wimpassing/Neufeld</t>
   </si>
 </sst>
 </file>
@@ -3928,6 +3949,9 @@
         <f>UPPER('Nach Mannschaften sortiert'!F2)</f>
         <v>RUST</v>
       </c>
+      <c r="F2" s="108" t="s">
+        <v>150</v>
+      </c>
       <c r="G2" s="108" t="str">
         <f>'Nach Mannschaften sortiert'!H2</f>
         <v>Auswärts</v>
@@ -3961,6 +3985,9 @@
         <f>UPPER('Nach Mannschaften sortiert'!F3)</f>
         <v>NEUFELD</v>
       </c>
+      <c r="F3" s="108" t="s">
+        <v>148</v>
+      </c>
       <c r="G3" s="108" t="str">
         <f>'Nach Mannschaften sortiert'!H3</f>
         <v>Heim</v>
@@ -3994,6 +4021,9 @@
         <f>UPPER('Nach Mannschaften sortiert'!F4)</f>
         <v>GATTENDORF</v>
       </c>
+      <c r="F4" s="108" t="s">
+        <v>149</v>
+      </c>
       <c r="G4" s="108" t="str">
         <f>'Nach Mannschaften sortiert'!H4</f>
         <v>Auswärts</v>
@@ -4356,6 +4386,9 @@
         <f>UPPER('Nach Mannschaften sortiert'!F15)</f>
         <v>RUST</v>
       </c>
+      <c r="F15" s="108" t="s">
+        <v>151</v>
+      </c>
       <c r="G15" s="108" t="str">
         <f>'Nach Mannschaften sortiert'!H15</f>
         <v>Auswärts</v>
@@ -4388,6 +4421,9 @@
         <f>UPPER('Nach Mannschaften sortiert'!F16)</f>
         <v>NEUFELD</v>
       </c>
+      <c r="F16" s="108" t="s">
+        <v>152</v>
+      </c>
       <c r="G16" s="108" t="str">
         <f>'Nach Mannschaften sortiert'!H16</f>
         <v>Heim</v>
@@ -4420,6 +4456,9 @@
         <f>UPPER('Nach Mannschaften sortiert'!F17)</f>
         <v>GATTENDORF</v>
       </c>
+      <c r="F17" s="108" t="s">
+        <v>153</v>
+      </c>
       <c r="G17" s="108" t="str">
         <f>'Nach Mannschaften sortiert'!H17</f>
         <v>Auswärts</v>
@@ -5005,6 +5044,9 @@
         <f>UPPER('Nach Mannschaften sortiert'!F35)</f>
         <v>WIMPASSING</v>
       </c>
+      <c r="F35" s="108" t="s">
+        <v>154</v>
+      </c>
       <c r="G35" s="108" t="str">
         <f>'Nach Mannschaften sortiert'!H35</f>
         <v>Heim</v>
@@ -5881,16 +5923,14 @@
     </row>
     <row r="62" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B62" s="105">
-        <f>'Nach Mannschaften sortiert'!D62</f>
-        <v>46109</v>
+        <v>46127</v>
       </c>
       <c r="C62" s="39">
-        <f>'Nach Mannschaften sortiert'!E62</f>
-        <v>0.41666666666666669</v>
+        <v>0.75</v>
       </c>
       <c r="D62" s="39">
         <f t="shared" si="0"/>
-        <v>0.46527777777777779</v>
+        <v>0.79861111111111116</v>
       </c>
       <c r="E62" s="39" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F62)</f>

--- a/Terminefussball_2026_Frühjahr.xlsx
+++ b/Terminefussball_2026_Frühjahr.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DTB\asv-neufeld\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D727DD9-7649-4E8E-AAE6-BB3C35FC326E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8A10DD4-196F-4EF1-8DD0-B81A79CFC327}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3185,7 +3185,7 @@
         <v>46123</v>
       </c>
       <c r="E63" s="28">
-        <v>0.54166666666666663</v>
+        <v>0.625</v>
       </c>
       <c r="F63" s="27" t="s">
         <v>2</v>
@@ -3367,7 +3367,7 @@
         <v>46123</v>
       </c>
       <c r="E70" s="19">
-        <v>0.39583333333333331</v>
+        <v>0.4375</v>
       </c>
       <c r="F70" s="12" t="s">
         <v>2</v>
@@ -3497,7 +3497,7 @@
         <v>46123</v>
       </c>
       <c r="E75" s="35">
-        <v>0.39583333333333331</v>
+        <v>0.4375</v>
       </c>
       <c r="F75" s="33" t="s">
         <v>2</v>
@@ -3627,7 +3627,7 @@
         <v>46123</v>
       </c>
       <c r="E80" s="55">
-        <v>0.39583333333333331</v>
+        <v>0.4375</v>
       </c>
       <c r="F80" s="53" t="s">
         <v>2</v>
@@ -5959,11 +5959,11 @@
       </c>
       <c r="C63" s="39">
         <f>'Nach Mannschaften sortiert'!E63</f>
-        <v>0.54166666666666663</v>
+        <v>0.625</v>
       </c>
       <c r="D63" s="39">
         <f t="shared" si="0"/>
-        <v>0.59027777777777779</v>
+        <v>0.67361111111111116</v>
       </c>
       <c r="E63" s="39" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F63)</f>
@@ -6190,11 +6190,11 @@
       </c>
       <c r="C70" s="39">
         <f>'Nach Mannschaften sortiert'!E70</f>
-        <v>0.39583333333333331</v>
+        <v>0.4375</v>
       </c>
       <c r="D70" s="39">
         <f t="shared" si="1"/>
-        <v>0.52083333333333326</v>
+        <v>0.5625</v>
       </c>
       <c r="E70" s="39" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F70)</f>
@@ -6355,11 +6355,11 @@
       </c>
       <c r="C75" s="39">
         <f>'Nach Mannschaften sortiert'!E75</f>
-        <v>0.39583333333333331</v>
+        <v>0.4375</v>
       </c>
       <c r="D75" s="39">
         <f t="shared" si="1"/>
-        <v>0.52083333333333326</v>
+        <v>0.5625</v>
       </c>
       <c r="E75" s="39" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F75)</f>
@@ -6520,11 +6520,11 @@
       </c>
       <c r="C80" s="39">
         <f>'Nach Mannschaften sortiert'!E80</f>
-        <v>0.39583333333333331</v>
+        <v>0.4375</v>
       </c>
       <c r="D80" s="39">
         <f t="shared" si="1"/>
-        <v>0.52083333333333326</v>
+        <v>0.5625</v>
       </c>
       <c r="E80" s="39" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F80)</f>
@@ -8023,7 +8023,7 @@
       </c>
       <c r="E24" s="65">
         <f>'Nach Mannschaften sortiert'!E70</f>
-        <v>0.39583333333333331</v>
+        <v>0.4375</v>
       </c>
       <c r="F24" s="63" t="str">
         <f>'Nach Mannschaften sortiert'!F70</f>
@@ -8091,7 +8091,7 @@
       </c>
       <c r="E26" s="65">
         <f>'Nach Mannschaften sortiert'!E75</f>
-        <v>0.39583333333333331</v>
+        <v>0.4375</v>
       </c>
       <c r="F26" s="63" t="str">
         <f>'Nach Mannschaften sortiert'!F75</f>
@@ -8193,7 +8193,7 @@
       </c>
       <c r="E29" s="65">
         <f>'Nach Mannschaften sortiert'!E80</f>
-        <v>0.39583333333333331</v>
+        <v>0.4375</v>
       </c>
       <c r="F29" s="63" t="str">
         <f>'Nach Mannschaften sortiert'!F80</f>
@@ -8397,7 +8397,7 @@
       </c>
       <c r="E35" s="65">
         <f>'Nach Mannschaften sortiert'!E63</f>
-        <v>0.54166666666666663</v>
+        <v>0.625</v>
       </c>
       <c r="F35" s="63" t="str">
         <f>'Nach Mannschaften sortiert'!F63</f>
@@ -11673,7 +11673,7 @@
       </c>
       <c r="C37" s="82">
         <f>Heimspiele!E24</f>
-        <v>0.39583333333333331</v>
+        <v>0.4375</v>
       </c>
       <c r="D37" s="80" t="str">
         <f>Heimspiele!F24</f>
@@ -11802,7 +11802,7 @@
       </c>
       <c r="C40" s="82">
         <f>Heimspiele!E26</f>
-        <v>0.39583333333333331</v>
+        <v>0.4375</v>
       </c>
       <c r="D40" s="80" t="str">
         <f>Heimspiele!F26</f>
@@ -11847,7 +11847,7 @@
       </c>
       <c r="C41" s="82">
         <f>Heimspiele!E29</f>
-        <v>0.39583333333333331</v>
+        <v>0.4375</v>
       </c>
       <c r="D41" s="80" t="str">
         <f>Heimspiele!F29</f>
@@ -11934,7 +11934,7 @@
       </c>
       <c r="C43" s="82">
         <f>Heimspiele!E35</f>
-        <v>0.54166666666666663</v>
+        <v>0.625</v>
       </c>
       <c r="D43" s="80" t="str">
         <f>Heimspiele!F35</f>

--- a/Terminefussball_2026_Frühjahr.xlsx
+++ b/Terminefussball_2026_Frühjahr.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DTB\asv-neufeld\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8A10DD4-196F-4EF1-8DD0-B81A79CFC327}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39905CF0-9457-4D1B-99AE-0F73CF4C3E32}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/Terminefussball_2026_Frühjahr.xlsx
+++ b/Terminefussball_2026_Frühjahr.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DTB\asv-neufeld\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39905CF0-9457-4D1B-99AE-0F73CF4C3E32}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A37C4FAE-6617-4559-B059-1377A5258A7E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="650" uniqueCount="155">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="656" uniqueCount="158">
   <si>
     <t>Mannschaft</t>
   </si>
@@ -509,6 +509,15 @@
   </si>
   <si>
     <t>Endstand:4:0 für Wimpassing/Neufeld</t>
+  </si>
+  <si>
+    <t>NEUFELD</t>
+  </si>
+  <si>
+    <t>Marswiese</t>
+  </si>
+  <si>
+    <t>Freundschaftsspiel</t>
   </si>
 </sst>
 </file>
@@ -3887,7 +3896,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E571BD24-40DC-4066-8BBA-CF3C23365042}">
-  <dimension ref="A1:J89"/>
+  <dimension ref="A1:J90"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11.5546875" style="108"/>
@@ -6655,7 +6664,7 @@
         <v>0.4375</v>
       </c>
       <c r="D84" s="39">
-        <f t="shared" si="1"/>
+        <f>IF(I84 = "KM",C84+"1:45",IF(I84="U23",C84+"1:45",IF(I84 = "U16",C84+"1:45",IF(I84 = "U15",C84+"1:30",IF(I84 = "U14",C84+"1:30",IF(I84 = "U13",C84+"1:35",IF(I84 = "U12",C84+"1:10",IF(I84 = "U11",C84+"1:10",IF(I84 = "U10",C84+"1:03",C84+"3:00")))))))))</f>
         <v>0.5625</v>
       </c>
       <c r="E84" s="39" t="str">
@@ -6835,6 +6844,36 @@
         <v>GGG</v>
       </c>
       <c r="J89" s="108" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="90" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B90" s="105">
+        <v>46124</v>
+      </c>
+      <c r="C90" s="39">
+        <v>0.44791666666666669</v>
+      </c>
+      <c r="D90" s="39">
+        <f>IF(I84 = "KM",C84+"1:45",IF(I84="U23",C84+"1:45",IF(I84 = "U16",C84+"1:45",IF(I84 = "U15",C84+"1:30",IF(I84 = "U14",C84+"1:30",IF(I84 = "U13",C84+"1:35",IF(I84 = "U12",C84+"1:10",IF(I84 = "U11",C84+"1:10",IF(I84 = "U10",C84+"1:03",C84+"3:00")))))))))</f>
+        <v>0.5625</v>
+      </c>
+      <c r="E90" s="39" t="s">
+        <v>155</v>
+      </c>
+      <c r="F90" s="108" t="s">
+        <v>157</v>
+      </c>
+      <c r="G90" s="108" t="s">
+        <v>12</v>
+      </c>
+      <c r="H90" t="s">
+        <v>156</v>
+      </c>
+      <c r="I90" t="s">
+        <v>18</v>
+      </c>
+      <c r="J90" s="108" t="s">
         <v>145</v>
       </c>
     </row>

--- a/Terminefussball_2026_Frühjahr.xlsx
+++ b/Terminefussball_2026_Frühjahr.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DTB\asv-neufeld\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A37C4FAE-6617-4559-B059-1377A5258A7E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56E88674-DB8C-4C4B-8CFA-D67DD68B9E9F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="656" uniqueCount="158">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="746" uniqueCount="161">
   <si>
     <t>Mannschaft</t>
   </si>
@@ -518,6 +518,15 @@
   </si>
   <si>
     <t>Freundschaftsspiel</t>
+  </si>
+  <si>
+    <t>SPIELART</t>
+  </si>
+  <si>
+    <t>Liga</t>
+  </si>
+  <si>
+    <t>Freundschaft</t>
   </si>
 </sst>
 </file>
@@ -3896,7 +3905,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E571BD24-40DC-4066-8BBA-CF3C23365042}">
-  <dimension ref="A1:J90"/>
+  <dimension ref="A1:K90"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11.5546875" style="108"/>
@@ -3909,7 +3918,7 @@
     <col min="10" max="10" width="11.5546875" style="108"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1" s="108" t="s">
         <v>133</v>
       </c>
@@ -3940,8 +3949,11 @@
       <c r="J1" s="108" t="s">
         <v>144</v>
       </c>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K1" s="108" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B2" s="105">
         <f>'Nach Mannschaften sortiert'!D2</f>
         <v>46096</v>
@@ -3976,8 +3988,11 @@
       <c r="J2" s="108" t="s">
         <v>145</v>
       </c>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K2" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B3" s="105">
         <f>'Nach Mannschaften sortiert'!D3</f>
         <v>46102</v>
@@ -4012,8 +4027,11 @@
       <c r="J3" s="108" t="s">
         <v>145</v>
       </c>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K3" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B4" s="105">
         <f>'Nach Mannschaften sortiert'!D4</f>
         <v>46109</v>
@@ -4048,8 +4066,11 @@
       <c r="J4" s="108" t="s">
         <v>145</v>
       </c>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K4" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B5" s="105">
         <f>'Nach Mannschaften sortiert'!D5</f>
         <v>46116</v>
@@ -4081,8 +4102,11 @@
       <c r="J5" s="108" t="s">
         <v>145</v>
       </c>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K5" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B6" s="105">
         <f>'Nach Mannschaften sortiert'!D6</f>
         <v>46124</v>
@@ -4114,8 +4138,11 @@
       <c r="J6" s="108" t="s">
         <v>145</v>
       </c>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K6" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B7" s="105">
         <f>'Nach Mannschaften sortiert'!D7</f>
         <v>46130</v>
@@ -4147,8 +4174,11 @@
       <c r="J7" s="108" t="s">
         <v>145</v>
       </c>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K7" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B8" s="105">
         <f>'Nach Mannschaften sortiert'!D8</f>
         <v>46136</v>
@@ -4180,8 +4210,11 @@
       <c r="J8" s="108" t="s">
         <v>145</v>
       </c>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K8" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B9" s="105">
         <f>'Nach Mannschaften sortiert'!D9</f>
         <v>46144</v>
@@ -4213,8 +4246,11 @@
       <c r="J9" s="108" t="s">
         <v>145</v>
       </c>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K9" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B10" s="105">
         <f>'Nach Mannschaften sortiert'!D10</f>
         <v>46151</v>
@@ -4246,8 +4282,11 @@
       <c r="J10" s="108" t="s">
         <v>145</v>
       </c>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K10" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B11" s="105">
         <f>'Nach Mannschaften sortiert'!D11</f>
         <v>46157</v>
@@ -4279,8 +4318,11 @@
       <c r="J11" s="108" t="s">
         <v>145</v>
       </c>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K11" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B12" s="105">
         <f>'Nach Mannschaften sortiert'!D12</f>
         <v>46166</v>
@@ -4312,8 +4354,11 @@
       <c r="J12" s="108" t="s">
         <v>145</v>
       </c>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K12" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B13" s="105">
         <f>'Nach Mannschaften sortiert'!D13</f>
         <v>46172</v>
@@ -4345,8 +4390,11 @@
       <c r="J13" s="108" t="s">
         <v>145</v>
       </c>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K13" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B14" s="105">
         <f>'Nach Mannschaften sortiert'!D14</f>
         <v>46179</v>
@@ -4378,8 +4426,11 @@
       <c r="J14" s="108" t="s">
         <v>145</v>
       </c>
-    </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K14" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B15" s="105">
         <f>'Nach Mannschaften sortiert'!D15</f>
         <v>46096</v>
@@ -4413,8 +4464,11 @@
       <c r="J15" s="108" t="s">
         <v>145</v>
       </c>
-    </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K15" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B16" s="105">
         <f>'Nach Mannschaften sortiert'!D16</f>
         <v>46102</v>
@@ -4448,8 +4502,11 @@
       <c r="J16" s="108" t="s">
         <v>145</v>
       </c>
-    </row>
-    <row r="17" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="K16" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="17" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B17" s="105">
         <f>'Nach Mannschaften sortiert'!D17</f>
         <v>46109</v>
@@ -4483,8 +4540,11 @@
       <c r="J17" s="108" t="s">
         <v>145</v>
       </c>
-    </row>
-    <row r="18" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="K17" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="18" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B18" s="105">
         <f>'Nach Mannschaften sortiert'!D18</f>
         <v>46116</v>
@@ -4515,8 +4575,11 @@
       <c r="J18" s="108" t="s">
         <v>145</v>
       </c>
-    </row>
-    <row r="19" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="K18" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="19" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B19" s="105">
         <f>'Nach Mannschaften sortiert'!D19</f>
         <v>46124</v>
@@ -4547,8 +4610,11 @@
       <c r="J19" s="108" t="s">
         <v>145</v>
       </c>
-    </row>
-    <row r="20" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="K19" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="20" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B20" s="105">
         <f>'Nach Mannschaften sortiert'!D20</f>
         <v>46130</v>
@@ -4579,8 +4645,11 @@
       <c r="J20" s="108" t="s">
         <v>145</v>
       </c>
-    </row>
-    <row r="21" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="K20" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="21" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B21" s="105">
         <f>'Nach Mannschaften sortiert'!D21</f>
         <v>46136</v>
@@ -4611,8 +4680,11 @@
       <c r="J21" s="108" t="s">
         <v>145</v>
       </c>
-    </row>
-    <row r="22" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="K21" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="22" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B22" s="105">
         <f>'Nach Mannschaften sortiert'!D22</f>
         <v>46144</v>
@@ -4643,8 +4715,11 @@
       <c r="J22" s="108" t="s">
         <v>145</v>
       </c>
-    </row>
-    <row r="23" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="K22" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="23" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B23" s="105">
         <f>'Nach Mannschaften sortiert'!D23</f>
         <v>46151</v>
@@ -4675,8 +4750,11 @@
       <c r="J23" s="108" t="s">
         <v>145</v>
       </c>
-    </row>
-    <row r="24" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="K23" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="24" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B24" s="105">
         <f>'Nach Mannschaften sortiert'!D24</f>
         <v>46157</v>
@@ -4707,8 +4785,11 @@
       <c r="J24" s="108" t="s">
         <v>145</v>
       </c>
-    </row>
-    <row r="25" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="K24" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="25" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B25" s="105">
         <f>'Nach Mannschaften sortiert'!D25</f>
         <v>46166</v>
@@ -4739,8 +4820,11 @@
       <c r="J25" s="108" t="s">
         <v>145</v>
       </c>
-    </row>
-    <row r="26" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="K25" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="26" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B26" s="105">
         <f>'Nach Mannschaften sortiert'!D26</f>
         <v>46172</v>
@@ -4771,8 +4855,11 @@
       <c r="J26" s="108" t="s">
         <v>145</v>
       </c>
-    </row>
-    <row r="27" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="K26" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="27" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B27" s="105">
         <f>'Nach Mannschaften sortiert'!D27</f>
         <v>46179</v>
@@ -4803,8 +4890,11 @@
       <c r="J27" s="108" t="s">
         <v>145</v>
       </c>
-    </row>
-    <row r="28" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="K27" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="28" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B28" s="105">
         <v>46106</v>
       </c>
@@ -4837,8 +4927,11 @@
       <c r="J28" s="108" t="s">
         <v>145</v>
       </c>
-    </row>
-    <row r="29" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="K28" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="29" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B29" s="105">
         <f>'Nach Mannschaften sortiert'!D29</f>
         <v>46124</v>
@@ -4870,8 +4963,11 @@
       <c r="J29" s="108" t="s">
         <v>145</v>
       </c>
-    </row>
-    <row r="30" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="K29" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="30" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B30" s="105">
         <f>'Nach Mannschaften sortiert'!D30</f>
         <v>46131</v>
@@ -4903,8 +4999,11 @@
       <c r="J30" s="108" t="s">
         <v>145</v>
       </c>
-    </row>
-    <row r="31" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="K30" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="31" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B31" s="105">
         <f>'Nach Mannschaften sortiert'!D31</f>
         <v>46138</v>
@@ -4936,8 +5035,11 @@
       <c r="J31" s="108" t="s">
         <v>145</v>
       </c>
-    </row>
-    <row r="32" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="K31" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="32" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B32" s="105">
         <f>'Nach Mannschaften sortiert'!D32</f>
         <v>46143</v>
@@ -4969,8 +5071,11 @@
       <c r="J32" s="108" t="s">
         <v>145</v>
       </c>
-    </row>
-    <row r="33" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="K32" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="33" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B33" s="105">
         <f>'Nach Mannschaften sortiert'!D33</f>
         <v>46151</v>
@@ -5002,8 +5107,11 @@
       <c r="J33" s="108" t="s">
         <v>145</v>
       </c>
-    </row>
-    <row r="34" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="K33" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="34" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B34" s="105">
         <f>'Nach Mannschaften sortiert'!D34</f>
         <v>46159</v>
@@ -5035,8 +5143,11 @@
       <c r="J34" s="108" t="s">
         <v>145</v>
       </c>
-    </row>
-    <row r="35" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="K34" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="35" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B35" s="105">
         <f>'Nach Mannschaften sortiert'!D35</f>
         <v>46102</v>
@@ -5071,8 +5182,11 @@
       <c r="J35" s="108" t="s">
         <v>145</v>
       </c>
-    </row>
-    <row r="36" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="K35" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="36" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B36" s="105">
         <f>'Nach Mannschaften sortiert'!D36</f>
         <v>46173</v>
@@ -5104,8 +5218,11 @@
       <c r="J36" s="108" t="s">
         <v>145</v>
       </c>
-    </row>
-    <row r="37" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="K36" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="37" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B37" s="105">
         <f>'Nach Mannschaften sortiert'!D37</f>
         <v>46180</v>
@@ -5137,8 +5254,11 @@
       <c r="J37" s="108" t="s">
         <v>145</v>
       </c>
-    </row>
-    <row r="38" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="K37" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="38" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B38" s="105">
         <f>'Nach Mannschaften sortiert'!D38</f>
         <v>46124</v>
@@ -5170,8 +5290,11 @@
       <c r="J38" s="108" t="s">
         <v>145</v>
       </c>
-    </row>
-    <row r="39" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="K38" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="39" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B39" s="105">
         <f>'Nach Mannschaften sortiert'!D39</f>
         <v>46128</v>
@@ -5203,8 +5326,11 @@
       <c r="J39" s="108" t="s">
         <v>145</v>
       </c>
-    </row>
-    <row r="40" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="K39" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="40" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B40" s="105">
         <f>'Nach Mannschaften sortiert'!D40</f>
         <v>46137</v>
@@ -5236,8 +5362,11 @@
       <c r="J40" s="108" t="s">
         <v>145</v>
       </c>
-    </row>
-    <row r="41" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="K40" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="41" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B41" s="105">
         <f>'Nach Mannschaften sortiert'!D41</f>
         <v>46145</v>
@@ -5269,8 +5398,11 @@
       <c r="J41" s="108" t="s">
         <v>145</v>
       </c>
-    </row>
-    <row r="42" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="K41" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="42" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B42" s="105">
         <f>'Nach Mannschaften sortiert'!D42</f>
         <v>46157</v>
@@ -5302,8 +5434,11 @@
       <c r="J42" s="108" t="s">
         <v>145</v>
       </c>
-    </row>
-    <row r="43" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="K42" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="43" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B43" s="105">
         <f>'Nach Mannschaften sortiert'!D43</f>
         <v>46165</v>
@@ -5335,8 +5470,11 @@
       <c r="J43" s="108" t="s">
         <v>145</v>
       </c>
-    </row>
-    <row r="44" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="K43" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="44" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B44" s="105">
         <f>'Nach Mannschaften sortiert'!D44</f>
         <v>46173</v>
@@ -5368,8 +5506,11 @@
       <c r="J44" s="108" t="s">
         <v>145</v>
       </c>
-    </row>
-    <row r="45" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="K44" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="45" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B45" s="105">
         <f>'Nach Mannschaften sortiert'!D45</f>
         <v>46179</v>
@@ -5401,8 +5542,11 @@
       <c r="J45" s="108" t="s">
         <v>145</v>
       </c>
-    </row>
-    <row r="46" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="K45" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="46" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B46" s="105">
         <f>'Nach Mannschaften sortiert'!D46</f>
         <v>46109</v>
@@ -5434,8 +5578,11 @@
       <c r="J46" s="108" t="s">
         <v>146</v>
       </c>
-    </row>
-    <row r="47" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="K46" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="47" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B47" s="105">
         <f>'Nach Mannschaften sortiert'!D47</f>
         <v>46122</v>
@@ -5467,8 +5614,11 @@
       <c r="J47" s="108" t="s">
         <v>145</v>
       </c>
-    </row>
-    <row r="48" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="K47" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="48" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B48" s="105">
         <f>'Nach Mannschaften sortiert'!D48</f>
         <v>46131</v>
@@ -5500,8 +5650,11 @@
       <c r="J48" s="108" t="s">
         <v>145</v>
       </c>
-    </row>
-    <row r="49" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="K48" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="49" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B49" s="105">
         <f>'Nach Mannschaften sortiert'!D49</f>
         <v>46137</v>
@@ -5533,8 +5686,11 @@
       <c r="J49" s="108" t="s">
         <v>145</v>
       </c>
-    </row>
-    <row r="50" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="K49" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="50" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B50" s="105">
         <f>'Nach Mannschaften sortiert'!D50</f>
         <v>46151</v>
@@ -5566,8 +5722,11 @@
       <c r="J50" s="108" t="s">
         <v>145</v>
       </c>
-    </row>
-    <row r="51" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="K50" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="51" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B51" s="105">
         <f>'Nach Mannschaften sortiert'!D51</f>
         <v>46158</v>
@@ -5599,8 +5758,11 @@
       <c r="J51" s="108" t="s">
         <v>145</v>
       </c>
-    </row>
-    <row r="52" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="K51" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="52" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B52" s="105">
         <f>'Nach Mannschaften sortiert'!D52</f>
         <v>46163</v>
@@ -5632,8 +5794,11 @@
       <c r="J52" s="108" t="s">
         <v>145</v>
       </c>
-    </row>
-    <row r="53" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="K52" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="53" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B53" s="105">
         <f>'Nach Mannschaften sortiert'!D53</f>
         <v>46171</v>
@@ -5665,8 +5830,11 @@
       <c r="J53" s="108" t="s">
         <v>145</v>
       </c>
-    </row>
-    <row r="54" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="K53" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="54" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B54" s="105">
         <f>'Nach Mannschaften sortiert'!D54</f>
         <v>46110</v>
@@ -5698,8 +5866,11 @@
       <c r="J54" s="108" t="s">
         <v>146</v>
       </c>
-    </row>
-    <row r="55" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="K54" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="55" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B55" s="105">
         <f>'Nach Mannschaften sortiert'!D55</f>
         <v>46130</v>
@@ -5731,8 +5902,11 @@
       <c r="J55" s="108" t="s">
         <v>145</v>
       </c>
-    </row>
-    <row r="56" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="K55" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="56" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B56" s="105">
         <f>'Nach Mannschaften sortiert'!D56</f>
         <v>46138</v>
@@ -5764,8 +5938,11 @@
       <c r="J56" s="108" t="s">
         <v>145</v>
       </c>
-    </row>
-    <row r="57" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="K56" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="57" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B57" s="105">
         <f>'Nach Mannschaften sortiert'!D57</f>
         <v>46145</v>
@@ -5797,8 +5974,11 @@
       <c r="J57" s="108" t="s">
         <v>145</v>
       </c>
-    </row>
-    <row r="58" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="K57" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="58" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B58" s="105">
         <f>'Nach Mannschaften sortiert'!D58</f>
         <v>46151</v>
@@ -5830,8 +6010,11 @@
       <c r="J58" s="108" t="s">
         <v>145</v>
       </c>
-    </row>
-    <row r="59" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="K58" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="59" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B59" s="105">
         <f>'Nach Mannschaften sortiert'!D59</f>
         <v>46167</v>
@@ -5863,8 +6046,11 @@
       <c r="J59" s="108" t="s">
         <v>145</v>
       </c>
-    </row>
-    <row r="60" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="K59" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="60" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B60" s="105">
         <f>'Nach Mannschaften sortiert'!D60</f>
         <v>46173</v>
@@ -5896,8 +6082,11 @@
       <c r="J60" s="108" t="s">
         <v>145</v>
       </c>
-    </row>
-    <row r="61" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="K60" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="61" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B61" s="105">
         <f>'Nach Mannschaften sortiert'!D61</f>
         <v>46180</v>
@@ -5929,8 +6118,11 @@
       <c r="J61" s="108" t="s">
         <v>145</v>
       </c>
-    </row>
-    <row r="62" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="K61" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="62" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B62" s="105">
         <v>46127</v>
       </c>
@@ -5960,8 +6152,11 @@
       <c r="J62" s="108" t="s">
         <v>145</v>
       </c>
-    </row>
-    <row r="63" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="K62" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="63" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B63" s="105">
         <f>'Nach Mannschaften sortiert'!D63</f>
         <v>46123</v>
@@ -5993,8 +6188,11 @@
       <c r="J63" s="108" t="s">
         <v>145</v>
       </c>
-    </row>
-    <row r="64" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="K63" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="64" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B64" s="105">
         <f>'Nach Mannschaften sortiert'!D64</f>
         <v>46131</v>
@@ -6026,8 +6224,11 @@
       <c r="J64" s="108" t="s">
         <v>145</v>
       </c>
-    </row>
-    <row r="65" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="K64" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="65" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B65" s="105">
         <f>'Nach Mannschaften sortiert'!D65</f>
         <v>46135</v>
@@ -6059,8 +6260,11 @@
       <c r="J65" s="108" t="s">
         <v>145</v>
       </c>
-    </row>
-    <row r="66" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="K65" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="66" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B66" s="105">
         <f>'Nach Mannschaften sortiert'!D66</f>
         <v>46151</v>
@@ -6092,8 +6296,11 @@
       <c r="J66" s="108" t="s">
         <v>145</v>
       </c>
-    </row>
-    <row r="67" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="K66" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="67" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B67" s="105">
         <f>'Nach Mannschaften sortiert'!D67</f>
         <v>46159</v>
@@ -6125,8 +6332,11 @@
       <c r="J67" s="108" t="s">
         <v>145</v>
       </c>
-    </row>
-    <row r="68" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="K67" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="68" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B68" s="105">
         <f>'Nach Mannschaften sortiert'!D68</f>
         <v>46164</v>
@@ -6158,8 +6368,11 @@
       <c r="J68" s="108" t="s">
         <v>145</v>
       </c>
-    </row>
-    <row r="69" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="K68" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="69" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B69" s="105">
         <f>'Nach Mannschaften sortiert'!D69</f>
         <v>46171</v>
@@ -6191,8 +6404,11 @@
       <c r="J69" s="108" t="s">
         <v>145</v>
       </c>
-    </row>
-    <row r="70" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="K69" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="70" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B70" s="105">
         <f>'Nach Mannschaften sortiert'!D70</f>
         <v>46123</v>
@@ -6224,8 +6440,11 @@
       <c r="J70" s="108" t="s">
         <v>145</v>
       </c>
-    </row>
-    <row r="71" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="K70" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="71" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B71" s="105">
         <f>'Nach Mannschaften sortiert'!D71</f>
         <v>46130</v>
@@ -6257,8 +6476,11 @@
       <c r="J71" s="108" t="s">
         <v>145</v>
       </c>
-    </row>
-    <row r="72" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="K71" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="72" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B72" s="105">
         <f>'Nach Mannschaften sortiert'!D72</f>
         <v>46137</v>
@@ -6290,8 +6512,11 @@
       <c r="J72" s="108" t="s">
         <v>145</v>
       </c>
-    </row>
-    <row r="73" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="K72" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="73" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B73" s="105">
         <f>'Nach Mannschaften sortiert'!D73</f>
         <v>46151</v>
@@ -6323,8 +6548,11 @@
       <c r="J73" s="108" t="s">
         <v>145</v>
       </c>
-    </row>
-    <row r="74" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="K73" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="74" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B74" s="105">
         <f>'Nach Mannschaften sortiert'!D74</f>
         <v>46194</v>
@@ -6356,8 +6584,11 @@
       <c r="J74" s="108" t="s">
         <v>145</v>
       </c>
-    </row>
-    <row r="75" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="K74" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="75" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B75" s="105">
         <f>'Nach Mannschaften sortiert'!D75</f>
         <v>46123</v>
@@ -6389,8 +6620,11 @@
       <c r="J75" s="108" t="s">
         <v>145</v>
       </c>
-    </row>
-    <row r="76" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="K75" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="76" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B76" s="105">
         <f>'Nach Mannschaften sortiert'!D76</f>
         <v>46137</v>
@@ -6422,8 +6656,11 @@
       <c r="J76" s="108" t="s">
         <v>145</v>
       </c>
-    </row>
-    <row r="77" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="K76" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="77" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B77" s="105">
         <f>'Nach Mannschaften sortiert'!D77</f>
         <v>46144</v>
@@ -6455,8 +6692,11 @@
       <c r="J77" s="108" t="s">
         <v>145</v>
       </c>
-    </row>
-    <row r="78" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="K77" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="78" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B78" s="105">
         <f>'Nach Mannschaften sortiert'!D78</f>
         <v>46151</v>
@@ -6488,8 +6728,11 @@
       <c r="J78" s="108" t="s">
         <v>145</v>
       </c>
-    </row>
-    <row r="79" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="K78" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="79" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B79" s="105">
         <f>'Nach Mannschaften sortiert'!D79</f>
         <v>46180</v>
@@ -6521,8 +6764,11 @@
       <c r="J79" s="108" t="s">
         <v>145</v>
       </c>
-    </row>
-    <row r="80" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="K79" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="80" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B80" s="105">
         <f>'Nach Mannschaften sortiert'!D80</f>
         <v>46123</v>
@@ -6554,8 +6800,11 @@
       <c r="J80" s="108" t="s">
         <v>145</v>
       </c>
-    </row>
-    <row r="81" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="K80" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="81" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B81" s="105">
         <f>'Nach Mannschaften sortiert'!D81</f>
         <v>46131</v>
@@ -6587,8 +6836,11 @@
       <c r="J81" s="108" t="s">
         <v>145</v>
       </c>
-    </row>
-    <row r="82" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="K81" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="82" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B82" s="105">
         <f>'Nach Mannschaften sortiert'!D82</f>
         <v>46143</v>
@@ -6620,8 +6872,11 @@
       <c r="J82" s="108" t="s">
         <v>145</v>
       </c>
-    </row>
-    <row r="83" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="K82" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="83" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B83" s="105">
         <f>'Nach Mannschaften sortiert'!D83</f>
         <v>46151</v>
@@ -6653,8 +6908,11 @@
       <c r="J83" s="108" t="s">
         <v>145</v>
       </c>
-    </row>
-    <row r="84" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="K83" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="84" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B84" s="105">
         <f>'Nach Mannschaften sortiert'!D84</f>
         <v>46187</v>
@@ -6686,8 +6944,11 @@
       <c r="J84" s="108" t="s">
         <v>145</v>
       </c>
-    </row>
-    <row r="85" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="K84" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="85" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B85" s="105">
         <f>'Nach Mannschaften sortiert'!D85</f>
         <v>46111</v>
@@ -6718,8 +6979,11 @@
       <c r="J85" s="108" t="s">
         <v>145</v>
       </c>
-    </row>
-    <row r="86" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="K85" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="86" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B86" s="105">
         <f>'Nach Mannschaften sortiert'!D86</f>
         <v>46112</v>
@@ -6750,8 +7014,11 @@
       <c r="J86" s="108" t="s">
         <v>145</v>
       </c>
-    </row>
-    <row r="87" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="K86" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="87" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B87" s="105">
         <f>'Nach Mannschaften sortiert'!D87</f>
         <v>46113</v>
@@ -6782,8 +7049,11 @@
       <c r="J87" s="108" t="s">
         <v>145</v>
       </c>
-    </row>
-    <row r="88" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="K87" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="88" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B88" s="105">
         <f>'Nach Mannschaften sortiert'!D88</f>
         <v>46186</v>
@@ -6814,8 +7084,11 @@
       <c r="J88" s="108" t="s">
         <v>145</v>
       </c>
-    </row>
-    <row r="89" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="K88" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="89" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B89" s="105">
         <f>'Nach Mannschaften sortiert'!D89</f>
         <v>46256</v>
@@ -6846,8 +7119,11 @@
       <c r="J89" s="108" t="s">
         <v>145</v>
       </c>
-    </row>
-    <row r="90" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="K89" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="90" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B90" s="105">
         <v>46124</v>
       </c>
@@ -6875,6 +7151,9 @@
       </c>
       <c r="J90" s="108" t="s">
         <v>145</v>
+      </c>
+      <c r="K90" t="s">
+        <v>160</v>
       </c>
     </row>
   </sheetData>

--- a/Terminefussball_2026_Frühjahr.xlsx
+++ b/Terminefussball_2026_Frühjahr.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DTB\asv-neufeld\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56E88674-DB8C-4C4B-8CFA-D67DD68B9E9F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C195120F-04BA-49F7-97D6-08CD2332C576}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3913,7 +3913,7 @@
     <col min="3" max="3" width="11.44140625" style="39"/>
     <col min="4" max="4" width="8.33203125" style="39" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="21.6640625" style="39" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14" style="108" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="32.109375" style="108" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="11.5546875" style="108"/>
     <col min="10" max="10" width="11.5546875" style="108"/>
   </cols>
@@ -7131,8 +7131,8 @@
         <v>0.44791666666666669</v>
       </c>
       <c r="D90" s="39">
-        <f>IF(I84 = "KM",C84+"1:45",IF(I84="U23",C84+"1:45",IF(I84 = "U16",C84+"1:45",IF(I84 = "U15",C84+"1:30",IF(I84 = "U14",C84+"1:30",IF(I84 = "U13",C84+"1:35",IF(I84 = "U12",C84+"1:10",IF(I84 = "U11",C84+"1:10",IF(I84 = "U10",C84+"1:03",C84+"3:00")))))))))</f>
-        <v>0.5625</v>
+        <f>IF(I90 = "KM",C90+"1:45",IF(I90="U23",C90+"1:45",IF(I90 = "U16",C90+"1:45",IF(I90 = "U15",C90+"1:30",IF(I90 = "U14",C90+"1:30",IF(I90 = "U13",C90+"1:35",IF(I90 = "U12",C90+"1:10",IF(I90 = "U11",C90+"1:10",IF(I90 = "U10",C90+"1:03",C90+"3:00")))))))))</f>
+        <v>0.51388888888888895</v>
       </c>
       <c r="E90" s="39" t="s">
         <v>155</v>

--- a/Terminefussball_2026_Frühjahr.xlsx
+++ b/Terminefussball_2026_Frühjahr.xlsx
@@ -8,23 +8,24 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DTB\asv-neufeld\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C195120F-04BA-49F7-97D6-08CD2332C576}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B159291-2A2D-4771-A164-29B02982BDE8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Nach Mannschaften sortiert" sheetId="1" r:id="rId1"/>
     <sheet name="ICS2" sheetId="21" r:id="rId2"/>
-    <sheet name="Trainingsplan" sheetId="16" r:id="rId3"/>
-    <sheet name="Heimspiele" sheetId="13" r:id="rId4"/>
-    <sheet name="Tabelle1" sheetId="18" r:id="rId5"/>
-    <sheet name="Stefans Liste 2026" sheetId="19" r:id="rId6"/>
-    <sheet name="Tabelle2" sheetId="20" r:id="rId7"/>
+    <sheet name="Kalendernamen" sheetId="22" r:id="rId3"/>
+    <sheet name="Trainingsplan" sheetId="16" r:id="rId4"/>
+    <sheet name="Heimspiele" sheetId="13" r:id="rId5"/>
+    <sheet name="Tabelle1" sheetId="18" r:id="rId6"/>
+    <sheet name="Stefans Liste 2026" sheetId="19" r:id="rId7"/>
+    <sheet name="Tabelle2" sheetId="20" r:id="rId8"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">Heimspiele!$A$1:$H$84</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">Heimspiele!$A$1:$H$84</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Nach Mannschaften sortiert'!$A$1:$H$79</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Stefans Liste 2026'!$A$1:$K$83</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Stefans Liste 2026'!$A$1:$K$83</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -44,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="746" uniqueCount="161">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="780" uniqueCount="195">
   <si>
     <t>Mannschaft</t>
   </si>
@@ -527,6 +528,108 @@
   </si>
   <si>
     <t>Freundschaft</t>
+  </si>
+  <si>
+    <t>alle_spiele.ics</t>
+  </si>
+  <si>
+    <t>heimspiele.ics</t>
+  </si>
+  <si>
+    <t>auswaertsspiele.ics</t>
+  </si>
+  <si>
+    <t>KM.ics</t>
+  </si>
+  <si>
+    <t>U23.ics</t>
+  </si>
+  <si>
+    <t>U16.ics</t>
+  </si>
+  <si>
+    <t>U15.ics</t>
+  </si>
+  <si>
+    <t>U14.ics</t>
+  </si>
+  <si>
+    <t>U13.ics</t>
+  </si>
+  <si>
+    <t>U11.ics</t>
+  </si>
+  <si>
+    <t>U9.ics</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> U8.ics</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> U7.ics</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Camp.ics</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> GGG.ics</t>
+  </si>
+  <si>
+    <t>U12.ics</t>
+  </si>
+  <si>
+    <t>U10.ics</t>
+  </si>
+  <si>
+    <t>Kategorie</t>
+  </si>
+  <si>
+    <t>Alle Spiele des ASV Neufeld</t>
+  </si>
+  <si>
+    <t>Alle Heimspiele des ASV Neufelds</t>
+  </si>
+  <si>
+    <t>Alle Auswärtsspiele des ASV Neufelds</t>
+  </si>
+  <si>
+    <t>Alle Spiele der Kampfmannschaft</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alle Spiele der U23 </t>
+  </si>
+  <si>
+    <t>Alle Spiele der U16</t>
+  </si>
+  <si>
+    <t>Alle Spiele der U7</t>
+  </si>
+  <si>
+    <t>Alle Spiele der U8</t>
+  </si>
+  <si>
+    <t>Alle Spiele der U9</t>
+  </si>
+  <si>
+    <t>Alle Spiele der U10</t>
+  </si>
+  <si>
+    <t>Alle Spiele der U15</t>
+  </si>
+  <si>
+    <t>Alle Spiele der U14</t>
+  </si>
+  <si>
+    <t>Alle Spiele der U13</t>
+  </si>
+  <si>
+    <t>Alle Spiele der U12</t>
+  </si>
+  <si>
+    <t>Alle Spiele der U11</t>
+  </si>
+  <si>
+    <t>ABOLINK</t>
   </si>
 </sst>
 </file>
@@ -539,7 +642,7 @@
     <numFmt numFmtId="166" formatCode="hh:mm;@"/>
     <numFmt numFmtId="167" formatCode="dd\.mm\.yyyy;@"/>
   </numFmts>
-  <fonts count="13" x14ac:knownFonts="1">
+  <fonts count="14" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -628,6 +731,14 @@
     </font>
     <font>
       <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -1026,10 +1137,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="126">
+  <cellXfs count="128">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1318,8 +1430,11 @@
     <xf numFmtId="0" fontId="6" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Link" xfId="1" builtinId="8"/>
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -5836,16 +5951,14 @@
     </row>
     <row r="54" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B54" s="105">
-        <f>'Nach Mannschaften sortiert'!D54</f>
-        <v>46110</v>
+        <v>46145</v>
       </c>
       <c r="C54" s="39">
-        <f>'Nach Mannschaften sortiert'!E54</f>
-        <v>0.45833333333333331</v>
+        <v>0.58333333333333337</v>
       </c>
       <c r="D54" s="39">
         <f t="shared" si="0"/>
-        <v>0.52430555555555558</v>
+        <v>0.64930555555555558</v>
       </c>
       <c r="E54" s="39" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F54)</f>
@@ -5864,7 +5977,7 @@
         <v>U13</v>
       </c>
       <c r="J54" s="108" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="K54" t="s">
         <v>159</v>
@@ -7162,6 +7275,232 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1638BD94-8334-4C49-885A-AEABEA7C434E}">
+  <dimension ref="A1:C21"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="28.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.77734375" hidden="1" customWidth="1"/>
+    <col min="3" max="3" width="48.33203125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="127" t="s">
+        <v>178</v>
+      </c>
+      <c r="B1" s="127"/>
+      <c r="C1" s="127" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="127" t="s">
+        <v>179</v>
+      </c>
+      <c r="B2" s="127" t="s">
+        <v>161</v>
+      </c>
+      <c r="C2" s="127" t="str">
+        <f>"https://dtb-asv.github.io/asv-neufeld/"&amp;B2</f>
+        <v>https://dtb-asv.github.io/asv-neufeld/alle_spiele.ics</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="127" t="s">
+        <v>180</v>
+      </c>
+      <c r="B3" s="127" t="s">
+        <v>162</v>
+      </c>
+      <c r="C3" s="127" t="str">
+        <f t="shared" ref="C3:C18" si="0">"https://dtb-asv.github.io/asv-neufeld/"&amp;B3</f>
+        <v>https://dtb-asv.github.io/asv-neufeld/heimspiele.ics</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="127" t="s">
+        <v>181</v>
+      </c>
+      <c r="B4" s="127" t="s">
+        <v>163</v>
+      </c>
+      <c r="C4" s="127" t="str">
+        <f t="shared" si="0"/>
+        <v>https://dtb-asv.github.io/asv-neufeld/auswaertsspiele.ics</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="127" t="s">
+        <v>182</v>
+      </c>
+      <c r="B5" s="127" t="s">
+        <v>164</v>
+      </c>
+      <c r="C5" s="127" t="str">
+        <f t="shared" si="0"/>
+        <v>https://dtb-asv.github.io/asv-neufeld/KM.ics</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="127" t="s">
+        <v>183</v>
+      </c>
+      <c r="B6" s="127" t="s">
+        <v>165</v>
+      </c>
+      <c r="C6" s="127" t="str">
+        <f t="shared" si="0"/>
+        <v>https://dtb-asv.github.io/asv-neufeld/U23.ics</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="127" t="s">
+        <v>184</v>
+      </c>
+      <c r="B7" s="127" t="s">
+        <v>166</v>
+      </c>
+      <c r="C7" s="127" t="str">
+        <f t="shared" si="0"/>
+        <v>https://dtb-asv.github.io/asv-neufeld/U16.ics</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="127" t="s">
+        <v>189</v>
+      </c>
+      <c r="B8" s="127" t="s">
+        <v>167</v>
+      </c>
+      <c r="C8" s="127" t="str">
+        <f t="shared" si="0"/>
+        <v>https://dtb-asv.github.io/asv-neufeld/U15.ics</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="127" t="s">
+        <v>190</v>
+      </c>
+      <c r="B9" s="127" t="s">
+        <v>168</v>
+      </c>
+      <c r="C9" s="127" t="str">
+        <f t="shared" si="0"/>
+        <v>https://dtb-asv.github.io/asv-neufeld/U14.ics</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="127" t="s">
+        <v>191</v>
+      </c>
+      <c r="B10" s="127" t="s">
+        <v>169</v>
+      </c>
+      <c r="C10" s="127" t="str">
+        <f t="shared" si="0"/>
+        <v>https://dtb-asv.github.io/asv-neufeld/U13.ics</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="127" t="s">
+        <v>192</v>
+      </c>
+      <c r="B11" s="127" t="s">
+        <v>176</v>
+      </c>
+      <c r="C11" s="127" t="str">
+        <f t="shared" si="0"/>
+        <v>https://dtb-asv.github.io/asv-neufeld/U12.ics</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="127" t="s">
+        <v>193</v>
+      </c>
+      <c r="B12" s="127" t="s">
+        <v>170</v>
+      </c>
+      <c r="C12" s="127" t="str">
+        <f t="shared" si="0"/>
+        <v>https://dtb-asv.github.io/asv-neufeld/U11.ics</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="127" t="s">
+        <v>188</v>
+      </c>
+      <c r="B13" s="127" t="s">
+        <v>177</v>
+      </c>
+      <c r="C13" s="127" t="str">
+        <f t="shared" si="0"/>
+        <v>https://dtb-asv.github.io/asv-neufeld/U10.ics</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="127" t="s">
+        <v>187</v>
+      </c>
+      <c r="B14" s="127" t="s">
+        <v>171</v>
+      </c>
+      <c r="C14" s="127" t="str">
+        <f t="shared" si="0"/>
+        <v>https://dtb-asv.github.io/asv-neufeld/U9.ics</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="127" t="s">
+        <v>186</v>
+      </c>
+      <c r="B15" s="127" t="s">
+        <v>172</v>
+      </c>
+      <c r="C15" s="127" t="str">
+        <f t="shared" si="0"/>
+        <v>https://dtb-asv.github.io/asv-neufeld/ U8.ics</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="127" t="s">
+        <v>185</v>
+      </c>
+      <c r="B16" s="127" t="s">
+        <v>173</v>
+      </c>
+      <c r="C16" s="127" t="str">
+        <f t="shared" si="0"/>
+        <v>https://dtb-asv.github.io/asv-neufeld/ U7.ics</v>
+      </c>
+    </row>
+    <row r="17" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B17" t="s">
+        <v>174</v>
+      </c>
+      <c r="C17" t="str">
+        <f t="shared" si="0"/>
+        <v>https://dtb-asv.github.io/asv-neufeld/ Camp.ics</v>
+      </c>
+    </row>
+    <row r="18" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B18" t="s">
+        <v>175</v>
+      </c>
+      <c r="C18" t="str">
+        <f t="shared" si="0"/>
+        <v>https://dtb-asv.github.io/asv-neufeld/ GGG.ics</v>
+      </c>
+    </row>
+    <row r="21" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B21" s="126"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B35835B5-0239-4B2A-9BF3-5569F1A88475}">
   <dimension ref="A1:J19"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -7524,7 +7863,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3DCAA465-B35F-48D1-A8EE-0892EAC86D5B}">
   <sheetPr filterMode="1"/>
   <dimension ref="A1:H84"/>
@@ -10415,7 +10754,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7379293C-A1E0-4DC6-BEBB-D0F5058BC12D}">
   <dimension ref="A1:C2"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -10447,7 +10786,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AB70293D-27F4-4BF1-B27D-4241A508821A}">
   <sheetPr filterMode="1">
     <pageSetUpPr fitToPage="1"/>
@@ -14210,7 +14549,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6365EA26-3DBC-4E60-A609-E8FEDD19B7F6}">
   <dimension ref="A1"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>

--- a/Terminefussball_2026_Frühjahr.xlsx
+++ b/Terminefussball_2026_Frühjahr.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DTB\asv-neufeld\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B159291-2A2D-4771-A164-29B02982BDE8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A29B4F30-2F70-44FC-9FE3-5EF6ACD97C8D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -5663,16 +5663,14 @@
     </row>
     <row r="46" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B46" s="105">
-        <f>'Nach Mannschaften sortiert'!D46</f>
-        <v>46109</v>
+        <v>46145</v>
       </c>
       <c r="C46" s="39">
-        <f>'Nach Mannschaften sortiert'!E46</f>
-        <v>0.66666666666666663</v>
+        <v>0.58333333333333337</v>
       </c>
       <c r="D46" s="39">
         <f t="shared" si="0"/>
-        <v>0.72916666666666663</v>
+        <v>0.64583333333333337</v>
       </c>
       <c r="E46" s="39" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F46)</f>
@@ -5691,7 +5689,7 @@
         <v>U14</v>
       </c>
       <c r="J46" s="108" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="K46" t="s">
         <v>159</v>
@@ -5951,14 +5949,14 @@
     </row>
     <row r="54" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B54" s="105">
-        <v>46145</v>
+        <v>46110</v>
       </c>
       <c r="C54" s="39">
-        <v>0.58333333333333337</v>
+        <v>0.4375</v>
       </c>
       <c r="D54" s="39">
         <f t="shared" si="0"/>
-        <v>0.64930555555555558</v>
+        <v>0.50347222222222221</v>
       </c>
       <c r="E54" s="39" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F54)</f>
@@ -5977,7 +5975,7 @@
         <v>U13</v>
       </c>
       <c r="J54" s="108" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="K54" t="s">
         <v>159</v>

--- a/Terminefussball_2026_Frühjahr.xlsx
+++ b/Terminefussball_2026_Frühjahr.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DTB\asv-neufeld\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A29B4F30-2F70-44FC-9FE3-5EF6ACD97C8D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7CC8829C-EBA5-470A-8CBA-86695056BE53}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Nach Mannschaften sortiert" sheetId="1" r:id="rId1"/>
@@ -1403,6 +1403,8 @@
     <xf numFmtId="20" fontId="0" fillId="11" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="20" fontId="0" fillId="15" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="13" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="6" fillId="13" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="6" fillId="13" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
@@ -1430,8 +1432,6 @@
     <xf numFmtId="0" fontId="6" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Link" xfId="1" builtinId="8"/>
@@ -2858,10 +2858,10 @@
         <v>35</v>
       </c>
       <c r="D46" s="21">
-        <v>46109</v>
+        <v>46145</v>
       </c>
       <c r="E46" s="22">
-        <v>0.66666666666666663</v>
+        <v>0.58333333333333337</v>
       </c>
       <c r="F46" s="20" t="s">
         <v>2</v>
@@ -3682,7 +3682,7 @@
         <v>46144</v>
       </c>
       <c r="E77" s="35">
-        <v>0.4375</v>
+        <v>0.41666666666666669</v>
       </c>
       <c r="F77" s="33" t="s">
         <v>113</v>
@@ -3835,7 +3835,9 @@
       <c r="D83" s="54">
         <v>46151</v>
       </c>
-      <c r="E83" s="55"/>
+      <c r="E83" s="55">
+        <v>0.39583333333333331</v>
+      </c>
       <c r="F83" s="53" t="s">
         <v>13</v>
       </c>
@@ -5663,13 +5665,15 @@
     </row>
     <row r="46" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B46" s="105">
+        <f>'Nach Mannschaften sortiert'!D46</f>
         <v>46145</v>
       </c>
       <c r="C46" s="39">
+        <f>'Nach Mannschaften sortiert'!E46</f>
         <v>0.58333333333333337</v>
       </c>
       <c r="D46" s="39">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="D46" si="1">IF(I46 = "KM",C46+"1:45",IF(I46="U23",C46+"1:45",IF(I46 = "U16",C46+"1:45",IF(I46 = "U15",C46+"1:30",IF(I46 = "U14",C46+"1:30",IF(I46 = "U13",C46+"1:35",IF(I46 = "U12",C46+"1:10",IF(I46 = "U11",C46+"1:10",IF(I46 = "U10",C46+"1:03",C46+"3:00")))))))))</f>
         <v>0.64583333333333337</v>
       </c>
       <c r="E46" s="39" t="str">
@@ -6421,7 +6425,7 @@
         <v>0.58333333333333337</v>
       </c>
       <c r="D67" s="39">
-        <f t="shared" ref="D67:D84" si="1">IF(I67 = "KM",C67+"1:45",IF(I67="U23",C67+"1:45",IF(I67 = "U16",C67+"1:45",IF(I67 = "U15",C67+"1:30",IF(I67 = "U14",C67+"1:30",IF(I67 = "U13",C67+"1:35",IF(I67 = "U12",C67+"1:10",IF(I67 = "U11",C67+"1:10",IF(I67 = "U10",C67+"1:03",C67+"3:00")))))))))</f>
+        <f t="shared" ref="D67:D83" si="2">IF(I67 = "KM",C67+"1:45",IF(I67="U23",C67+"1:45",IF(I67 = "U16",C67+"1:45",IF(I67 = "U15",C67+"1:30",IF(I67 = "U14",C67+"1:30",IF(I67 = "U13",C67+"1:35",IF(I67 = "U12",C67+"1:10",IF(I67 = "U11",C67+"1:10",IF(I67 = "U10",C67+"1:03",C67+"3:00")))))))))</f>
         <v>0.63194444444444453</v>
       </c>
       <c r="E67" s="39" t="str">
@@ -6457,7 +6461,7 @@
         <v>0.70833333333333337</v>
       </c>
       <c r="D68" s="39">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.75694444444444453</v>
       </c>
       <c r="E68" s="39" t="str">
@@ -6493,7 +6497,7 @@
         <v>0.70833333333333337</v>
       </c>
       <c r="D69" s="39">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.75694444444444453</v>
       </c>
       <c r="E69" s="39" t="str">
@@ -6529,7 +6533,7 @@
         <v>0.4375</v>
       </c>
       <c r="D70" s="39">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.5625</v>
       </c>
       <c r="E70" s="39" t="str">
@@ -6565,7 +6569,7 @@
         <v>0.39583333333333331</v>
       </c>
       <c r="D71" s="39">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.52083333333333326</v>
       </c>
       <c r="E71" s="39" t="str">
@@ -6601,7 +6605,7 @@
         <v>0.60416666666666663</v>
       </c>
       <c r="D72" s="39">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.72916666666666663</v>
       </c>
       <c r="E72" s="39" t="str">
@@ -6637,7 +6641,7 @@
         <v>0.47916666666666669</v>
       </c>
       <c r="D73" s="39">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.60416666666666674</v>
       </c>
       <c r="E73" s="39" t="str">
@@ -6673,7 +6677,7 @@
         <v>0.4375</v>
       </c>
       <c r="D74" s="39">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.5625</v>
       </c>
       <c r="E74" s="39" t="str">
@@ -6709,7 +6713,7 @@
         <v>0.4375</v>
       </c>
       <c r="D75" s="39">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.5625</v>
       </c>
       <c r="E75" s="39" t="str">
@@ -6745,7 +6749,7 @@
         <v>0.39583333333333331</v>
       </c>
       <c r="D76" s="39">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.52083333333333326</v>
       </c>
       <c r="E76" s="39" t="str">
@@ -6778,11 +6782,11 @@
       </c>
       <c r="C77" s="39">
         <f>'Nach Mannschaften sortiert'!E77</f>
-        <v>0.4375</v>
+        <v>0.41666666666666669</v>
       </c>
       <c r="D77" s="39">
-        <f t="shared" si="1"/>
-        <v>0.5625</v>
+        <f t="shared" si="2"/>
+        <v>0.54166666666666674</v>
       </c>
       <c r="E77" s="39" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F77)</f>
@@ -6817,7 +6821,7 @@
         <v>0.39583333333333331</v>
       </c>
       <c r="D78" s="39">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.52083333333333326</v>
       </c>
       <c r="E78" s="39" t="str">
@@ -6853,7 +6857,7 @@
         <v>0.4375</v>
       </c>
       <c r="D79" s="39">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.5625</v>
       </c>
       <c r="E79" s="39" t="str">
@@ -6889,7 +6893,7 @@
         <v>0.4375</v>
       </c>
       <c r="D80" s="39">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.5625</v>
       </c>
       <c r="E80" s="39" t="str">
@@ -6925,7 +6929,7 @@
         <v>0.54166666666666663</v>
       </c>
       <c r="D81" s="39">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.66666666666666663</v>
       </c>
       <c r="E81" s="39" t="str">
@@ -6961,7 +6965,7 @@
         <v>0</v>
       </c>
       <c r="D82" s="39">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.125</v>
       </c>
       <c r="E82" s="39" t="str">
@@ -6994,11 +6998,11 @@
       </c>
       <c r="C83" s="39">
         <f>'Nach Mannschaften sortiert'!E83</f>
-        <v>0</v>
+        <v>0.39583333333333331</v>
       </c>
       <c r="D83" s="39">
-        <f t="shared" si="1"/>
-        <v>0.125</v>
+        <f t="shared" si="2"/>
+        <v>0.52083333333333326</v>
       </c>
       <c r="E83" s="39" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F83)</f>
@@ -7283,190 +7287,190 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="127" t="s">
+      <c r="A1" s="110" t="s">
         <v>178</v>
       </c>
-      <c r="B1" s="127"/>
-      <c r="C1" s="127" t="s">
+      <c r="B1" s="110"/>
+      <c r="C1" s="110" t="s">
         <v>194</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="127" t="s">
+      <c r="A2" s="110" t="s">
         <v>179</v>
       </c>
-      <c r="B2" s="127" t="s">
+      <c r="B2" s="110" t="s">
         <v>161</v>
       </c>
-      <c r="C2" s="127" t="str">
+      <c r="C2" s="110" t="str">
         <f>"https://dtb-asv.github.io/asv-neufeld/"&amp;B2</f>
         <v>https://dtb-asv.github.io/asv-neufeld/alle_spiele.ics</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="127" t="s">
+      <c r="A3" s="110" t="s">
         <v>180</v>
       </c>
-      <c r="B3" s="127" t="s">
+      <c r="B3" s="110" t="s">
         <v>162</v>
       </c>
-      <c r="C3" s="127" t="str">
+      <c r="C3" s="110" t="str">
         <f t="shared" ref="C3:C18" si="0">"https://dtb-asv.github.io/asv-neufeld/"&amp;B3</f>
         <v>https://dtb-asv.github.io/asv-neufeld/heimspiele.ics</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="127" t="s">
+      <c r="A4" s="110" t="s">
         <v>181</v>
       </c>
-      <c r="B4" s="127" t="s">
+      <c r="B4" s="110" t="s">
         <v>163</v>
       </c>
-      <c r="C4" s="127" t="str">
+      <c r="C4" s="110" t="str">
         <f t="shared" si="0"/>
         <v>https://dtb-asv.github.io/asv-neufeld/auswaertsspiele.ics</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="127" t="s">
+      <c r="A5" s="110" t="s">
         <v>182</v>
       </c>
-      <c r="B5" s="127" t="s">
+      <c r="B5" s="110" t="s">
         <v>164</v>
       </c>
-      <c r="C5" s="127" t="str">
+      <c r="C5" s="110" t="str">
         <f t="shared" si="0"/>
         <v>https://dtb-asv.github.io/asv-neufeld/KM.ics</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="127" t="s">
+      <c r="A6" s="110" t="s">
         <v>183</v>
       </c>
-      <c r="B6" s="127" t="s">
+      <c r="B6" s="110" t="s">
         <v>165</v>
       </c>
-      <c r="C6" s="127" t="str">
+      <c r="C6" s="110" t="str">
         <f t="shared" si="0"/>
         <v>https://dtb-asv.github.io/asv-neufeld/U23.ics</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="127" t="s">
+      <c r="A7" s="110" t="s">
         <v>184</v>
       </c>
-      <c r="B7" s="127" t="s">
+      <c r="B7" s="110" t="s">
         <v>166</v>
       </c>
-      <c r="C7" s="127" t="str">
+      <c r="C7" s="110" t="str">
         <f t="shared" si="0"/>
         <v>https://dtb-asv.github.io/asv-neufeld/U16.ics</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="127" t="s">
+      <c r="A8" s="110" t="s">
         <v>189</v>
       </c>
-      <c r="B8" s="127" t="s">
+      <c r="B8" s="110" t="s">
         <v>167</v>
       </c>
-      <c r="C8" s="127" t="str">
+      <c r="C8" s="110" t="str">
         <f t="shared" si="0"/>
         <v>https://dtb-asv.github.io/asv-neufeld/U15.ics</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="127" t="s">
+      <c r="A9" s="110" t="s">
         <v>190</v>
       </c>
-      <c r="B9" s="127" t="s">
+      <c r="B9" s="110" t="s">
         <v>168</v>
       </c>
-      <c r="C9" s="127" t="str">
+      <c r="C9" s="110" t="str">
         <f t="shared" si="0"/>
         <v>https://dtb-asv.github.io/asv-neufeld/U14.ics</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="127" t="s">
+      <c r="A10" s="110" t="s">
         <v>191</v>
       </c>
-      <c r="B10" s="127" t="s">
+      <c r="B10" s="110" t="s">
         <v>169</v>
       </c>
-      <c r="C10" s="127" t="str">
+      <c r="C10" s="110" t="str">
         <f t="shared" si="0"/>
         <v>https://dtb-asv.github.io/asv-neufeld/U13.ics</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="127" t="s">
+      <c r="A11" s="110" t="s">
         <v>192</v>
       </c>
-      <c r="B11" s="127" t="s">
+      <c r="B11" s="110" t="s">
         <v>176</v>
       </c>
-      <c r="C11" s="127" t="str">
+      <c r="C11" s="110" t="str">
         <f t="shared" si="0"/>
         <v>https://dtb-asv.github.io/asv-neufeld/U12.ics</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="127" t="s">
+      <c r="A12" s="110" t="s">
         <v>193</v>
       </c>
-      <c r="B12" s="127" t="s">
+      <c r="B12" s="110" t="s">
         <v>170</v>
       </c>
-      <c r="C12" s="127" t="str">
+      <c r="C12" s="110" t="str">
         <f t="shared" si="0"/>
         <v>https://dtb-asv.github.io/asv-neufeld/U11.ics</v>
       </c>
     </row>
     <row r="13" spans="1:3" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="127" t="s">
+      <c r="A13" s="110" t="s">
         <v>188</v>
       </c>
-      <c r="B13" s="127" t="s">
+      <c r="B13" s="110" t="s">
         <v>177</v>
       </c>
-      <c r="C13" s="127" t="str">
+      <c r="C13" s="110" t="str">
         <f t="shared" si="0"/>
         <v>https://dtb-asv.github.io/asv-neufeld/U10.ics</v>
       </c>
     </row>
     <row r="14" spans="1:3" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="127" t="s">
+      <c r="A14" s="110" t="s">
         <v>187</v>
       </c>
-      <c r="B14" s="127" t="s">
+      <c r="B14" s="110" t="s">
         <v>171</v>
       </c>
-      <c r="C14" s="127" t="str">
+      <c r="C14" s="110" t="str">
         <f t="shared" si="0"/>
         <v>https://dtb-asv.github.io/asv-neufeld/U9.ics</v>
       </c>
     </row>
     <row r="15" spans="1:3" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="127" t="s">
+      <c r="A15" s="110" t="s">
         <v>186</v>
       </c>
-      <c r="B15" s="127" t="s">
+      <c r="B15" s="110" t="s">
         <v>172</v>
       </c>
-      <c r="C15" s="127" t="str">
+      <c r="C15" s="110" t="str">
         <f t="shared" si="0"/>
         <v>https://dtb-asv.github.io/asv-neufeld/ U8.ics</v>
       </c>
     </row>
     <row r="16" spans="1:3" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="127" t="s">
+      <c r="A16" s="110" t="s">
         <v>185</v>
       </c>
-      <c r="B16" s="127" t="s">
+      <c r="B16" s="110" t="s">
         <v>173</v>
       </c>
-      <c r="C16" s="127" t="str">
+      <c r="C16" s="110" t="str">
         <f t="shared" si="0"/>
         <v>https://dtb-asv.github.io/asv-neufeld/ U7.ics</v>
       </c>
@@ -7490,7 +7494,7 @@
       </c>
     </row>
     <row r="21" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B21" s="126"/>
+      <c r="B21" s="109"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
@@ -7514,16 +7518,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="115" t="s">
+      <c r="A1" s="117" t="s">
         <v>51</v>
       </c>
-      <c r="B1" s="116"/>
-      <c r="C1" s="116"/>
-      <c r="D1" s="116"/>
-      <c r="E1" s="116"/>
-      <c r="F1" s="116"/>
-      <c r="G1" s="116"/>
-      <c r="H1" s="116"/>
+      <c r="B1" s="118"/>
+      <c r="C1" s="118"/>
+      <c r="D1" s="118"/>
+      <c r="E1" s="118"/>
+      <c r="F1" s="118"/>
+      <c r="G1" s="118"/>
+      <c r="H1" s="118"/>
     </row>
     <row r="2" spans="1:10" ht="31.8" thickTop="1" x14ac:dyDescent="0.3">
       <c r="A2" s="42" t="s">
@@ -7550,7 +7554,7 @@
       <c r="H2" s="42" t="s">
         <v>58</v>
       </c>
-      <c r="I2" s="112" t="s">
+      <c r="I2" s="114" t="s">
         <v>80</v>
       </c>
       <c r="J2" s="50"/>
@@ -7570,7 +7574,7 @@
       <c r="F3" s="85"/>
       <c r="G3" s="85"/>
       <c r="H3" s="87"/>
-      <c r="I3" s="113"/>
+      <c r="I3" s="115"/>
       <c r="J3" s="50"/>
     </row>
     <row r="4" spans="1:10" ht="31.2" x14ac:dyDescent="0.35">
@@ -7590,7 +7594,7 @@
       </c>
       <c r="G4" s="85"/>
       <c r="H4" s="87"/>
-      <c r="I4" s="113"/>
+      <c r="I4" s="115"/>
       <c r="J4" s="50"/>
     </row>
     <row r="5" spans="1:10" ht="31.2" x14ac:dyDescent="0.35">
@@ -7610,7 +7614,7 @@
       </c>
       <c r="G5" s="85"/>
       <c r="H5" s="87"/>
-      <c r="I5" s="113"/>
+      <c r="I5" s="115"/>
       <c r="J5" s="50"/>
     </row>
     <row r="6" spans="1:10" ht="31.2" x14ac:dyDescent="0.35">
@@ -7630,7 +7634,7 @@
       </c>
       <c r="G6" s="89"/>
       <c r="H6" s="87"/>
-      <c r="I6" s="113"/>
+      <c r="I6" s="115"/>
       <c r="J6" s="50"/>
     </row>
     <row r="7" spans="1:10" ht="31.2" x14ac:dyDescent="0.35">
@@ -7652,7 +7656,7 @@
         <v>70</v>
       </c>
       <c r="H7" s="87"/>
-      <c r="I7" s="113"/>
+      <c r="I7" s="115"/>
       <c r="J7" s="50"/>
     </row>
     <row r="8" spans="1:10" ht="31.2" x14ac:dyDescent="0.35">
@@ -7674,7 +7678,7 @@
         <v>70</v>
       </c>
       <c r="H8" s="87"/>
-      <c r="I8" s="113"/>
+      <c r="I8" s="115"/>
       <c r="J8" s="50"/>
     </row>
     <row r="9" spans="1:10" ht="31.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -7698,7 +7702,7 @@
       <c r="H9" s="92" t="s">
         <v>71</v>
       </c>
-      <c r="I9" s="113"/>
+      <c r="I9" s="115"/>
       <c r="J9" s="50"/>
     </row>
     <row r="10" spans="1:10" ht="31.2" x14ac:dyDescent="0.35">
@@ -7720,7 +7724,7 @@
         <v>132</v>
       </c>
       <c r="H10" s="87"/>
-      <c r="I10" s="113"/>
+      <c r="I10" s="115"/>
       <c r="J10" s="50"/>
     </row>
     <row r="11" spans="1:10" ht="31.8" thickBot="1" x14ac:dyDescent="0.4">
@@ -7740,7 +7744,7 @@
         <v>79</v>
       </c>
       <c r="H11" s="96"/>
-      <c r="I11" s="114"/>
+      <c r="I11" s="116"/>
       <c r="J11" s="50"/>
     </row>
     <row r="12" spans="1:10" ht="18.600000000000001" thickTop="1" x14ac:dyDescent="0.35">
@@ -7798,52 +7802,52 @@
       <c r="H14" s="103"/>
     </row>
     <row r="15" spans="1:10" ht="16.8" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="117" t="s">
+      <c r="A15" s="119" t="s">
         <v>77</v>
       </c>
-      <c r="B15" s="118"/>
-      <c r="C15" s="118"/>
-      <c r="D15" s="118"/>
-      <c r="E15" s="118"/>
-      <c r="F15" s="118"/>
-      <c r="G15" s="118"/>
-      <c r="H15" s="119"/>
+      <c r="B15" s="120"/>
+      <c r="C15" s="120"/>
+      <c r="D15" s="120"/>
+      <c r="E15" s="120"/>
+      <c r="F15" s="120"/>
+      <c r="G15" s="120"/>
+      <c r="H15" s="121"/>
     </row>
     <row r="16" spans="1:10" ht="16.8" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="120" t="s">
+      <c r="A16" s="122" t="s">
         <v>76</v>
       </c>
-      <c r="B16" s="121"/>
-      <c r="C16" s="121"/>
-      <c r="D16" s="121"/>
-      <c r="E16" s="121"/>
-      <c r="F16" s="121"/>
-      <c r="G16" s="121"/>
-      <c r="H16" s="122"/>
+      <c r="B16" s="123"/>
+      <c r="C16" s="123"/>
+      <c r="D16" s="123"/>
+      <c r="E16" s="123"/>
+      <c r="F16" s="123"/>
+      <c r="G16" s="123"/>
+      <c r="H16" s="124"/>
     </row>
     <row r="17" spans="1:8" ht="16.8" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="123" t="s">
+      <c r="A17" s="125" t="s">
         <v>75</v>
       </c>
-      <c r="B17" s="124"/>
-      <c r="C17" s="124"/>
-      <c r="D17" s="124"/>
-      <c r="E17" s="124"/>
-      <c r="F17" s="124"/>
-      <c r="G17" s="124"/>
-      <c r="H17" s="125"/>
+      <c r="B17" s="126"/>
+      <c r="C17" s="126"/>
+      <c r="D17" s="126"/>
+      <c r="E17" s="126"/>
+      <c r="F17" s="126"/>
+      <c r="G17" s="126"/>
+      <c r="H17" s="127"/>
     </row>
     <row r="18" spans="1:8" ht="16.8" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="109" t="s">
+      <c r="A18" s="111" t="s">
         <v>78</v>
       </c>
-      <c r="B18" s="110"/>
-      <c r="C18" s="110"/>
-      <c r="D18" s="110"/>
-      <c r="E18" s="110"/>
-      <c r="F18" s="110"/>
-      <c r="G18" s="110"/>
-      <c r="H18" s="111"/>
+      <c r="B18" s="112"/>
+      <c r="C18" s="112"/>
+      <c r="D18" s="112"/>
+      <c r="E18" s="112"/>
+      <c r="F18" s="112"/>
+      <c r="G18" s="112"/>
+      <c r="H18" s="113"/>
     </row>
     <row r="19" spans="1:8" ht="15" thickTop="1" x14ac:dyDescent="0.3"/>
   </sheetData>
@@ -8028,11 +8032,11 @@
       </c>
       <c r="D5" s="16">
         <f>'Nach Mannschaften sortiert'!D46</f>
-        <v>46109</v>
+        <v>46145</v>
       </c>
       <c r="E5" s="38">
         <f>'Nach Mannschaften sortiert'!E46</f>
-        <v>0.66666666666666663</v>
+        <v>0.58333333333333337</v>
       </c>
       <c r="F5" s="2" t="str">
         <f>'Nach Mannschaften sortiert'!F46</f>
@@ -10308,7 +10312,7 @@
       </c>
       <c r="E72" s="38">
         <f>'Nach Mannschaften sortiert'!E77</f>
-        <v>0.4375</v>
+        <v>0.41666666666666669</v>
       </c>
       <c r="F72" s="2" t="str">
         <f>'Nach Mannschaften sortiert'!F77</f>
@@ -10512,7 +10516,7 @@
       </c>
       <c r="E78" s="38">
         <f>'Nach Mannschaften sortiert'!E83</f>
-        <v>0</v>
+        <v>0.39583333333333331</v>
       </c>
       <c r="F78" s="2" t="str">
         <f>'Nach Mannschaften sortiert'!F83</f>
@@ -11304,11 +11308,11 @@
       </c>
       <c r="B13" s="81">
         <f>Heimspiele!D5</f>
-        <v>46109</v>
+        <v>46145</v>
       </c>
       <c r="C13" s="82">
         <f>Heimspiele!E5</f>
-        <v>0.66666666666666663</v>
+        <v>0.58333333333333337</v>
       </c>
       <c r="D13" s="80" t="str">
         <f>Heimspiele!F5</f>

--- a/Terminefussball_2026_Frühjahr.xlsx
+++ b/Terminefussball_2026_Frühjahr.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DTB\asv-neufeld\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7CC8829C-EBA5-470A-8CBA-86695056BE53}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C95DB00F-C092-49A9-AD77-71EEEC64A852}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Nach Mannschaften sortiert" sheetId="1" r:id="rId1"/>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="780" uniqueCount="195">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="787" uniqueCount="195">
   <si>
     <t>Mannschaft</t>
   </si>
@@ -4022,7 +4022,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E571BD24-40DC-4066-8BBA-CF3C23365042}">
-  <dimension ref="A1:K90"/>
+  <dimension ref="A1:K91"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11.5546875" style="108"/>
@@ -7268,6 +7268,38 @@
         <v>145</v>
       </c>
       <c r="K90" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="91" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B91" s="105">
+        <v>46119</v>
+      </c>
+      <c r="C91" s="39">
+        <v>0.70833333333333337</v>
+      </c>
+      <c r="D91" s="39">
+        <v>0.75</v>
+      </c>
+      <c r="E91" s="39" t="s">
+        <v>155</v>
+      </c>
+      <c r="F91" s="108" t="s">
+        <v>157</v>
+      </c>
+      <c r="G91" s="108" t="s">
+        <v>12</v>
+      </c>
+      <c r="H91" t="s">
+        <v>31</v>
+      </c>
+      <c r="I91" t="s">
+        <v>27</v>
+      </c>
+      <c r="J91" s="108" t="s">
+        <v>145</v>
+      </c>
+      <c r="K91" t="s">
         <v>160</v>
       </c>
     </row>

--- a/Terminefussball_2026_Frühjahr.xlsx
+++ b/Terminefussball_2026_Frühjahr.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DTB\asv-neufeld\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C95DB00F-C092-49A9-AD77-71EEEC64A852}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39F3FE3F-AD2C-4E44-90B5-434498577D82}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="787" uniqueCount="195">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="789" uniqueCount="197">
   <si>
     <t>Mannschaft</t>
   </si>
@@ -630,6 +630,12 @@
   </si>
   <si>
     <t>ABOLINK</t>
+  </si>
+  <si>
+    <t>Endstand 3:1 fü Neufeld</t>
+  </si>
+  <si>
+    <t>Endstand 0:2 fr Illmitz</t>
   </si>
 </sst>
 </file>
@@ -4204,6 +4210,9 @@
         <f>UPPER('Nach Mannschaften sortiert'!F5)</f>
         <v>NEUFELD</v>
       </c>
+      <c r="F5" s="108" t="s">
+        <v>195</v>
+      </c>
       <c r="G5" s="108" t="str">
         <f>'Nach Mannschaften sortiert'!H5</f>
         <v>Heim</v>
@@ -4676,6 +4685,9 @@
       <c r="E18" s="39" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F18)</f>
         <v>NEUFELD</v>
+      </c>
+      <c r="F18" s="108" t="s">
+        <v>196</v>
       </c>
       <c r="G18" s="108" t="str">
         <f>'Nach Mannschaften sortiert'!H18</f>

--- a/Terminefussball_2026_Frühjahr.xlsx
+++ b/Terminefussball_2026_Frühjahr.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DTB\asv-neufeld\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39F3FE3F-AD2C-4E44-90B5-434498577D82}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC161EF2-7A1D-4C92-A74E-4E4A448FD2EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -632,10 +632,10 @@
     <t>ABOLINK</t>
   </si>
   <si>
-    <t>Endstand 3:1 fü Neufeld</t>
-  </si>
-  <si>
-    <t>Endstand 0:2 fr Illmitz</t>
+    <t>Endstand 3:1 für Neufeld</t>
+  </si>
+  <si>
+    <t>Endstand 0:2 für Illmitz</t>
   </si>
 </sst>
 </file>

--- a/Terminefussball_2026_Frühjahr.xlsx
+++ b/Terminefussball_2026_Frühjahr.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DTB\asv-neufeld\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC161EF2-7A1D-4C92-A74E-4E4A448FD2EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{590E5541-69DA-4125-A7AF-B4D902BCF3E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="789" uniqueCount="197">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="791" uniqueCount="199">
   <si>
     <t>Mannschaft</t>
   </si>
@@ -636,6 +636,12 @@
   </si>
   <si>
     <t>Endstand 0:2 für Illmitz</t>
+  </si>
+  <si>
+    <t>Endstand 3:2 für SK Pama</t>
+  </si>
+  <si>
+    <t>Endstand 7:2 für Neufeld</t>
   </si>
 </sst>
 </file>
@@ -5728,6 +5734,9 @@
         <f>UPPER('Nach Mannschaften sortiert'!F47)</f>
         <v>PAMA</v>
       </c>
+      <c r="F47" s="108" t="s">
+        <v>197</v>
+      </c>
       <c r="G47" s="108" t="str">
         <f>'Nach Mannschaften sortiert'!H47</f>
         <v>Auswärts</v>
@@ -6299,6 +6308,9 @@
       <c r="E63" s="39" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F63)</f>
         <v>NEUFELD</v>
+      </c>
+      <c r="F63" s="108" t="s">
+        <v>198</v>
       </c>
       <c r="G63" s="108" t="str">
         <f>'Nach Mannschaften sortiert'!H63</f>

--- a/Terminefussball_2026_Frühjahr.xlsx
+++ b/Terminefussball_2026_Frühjahr.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DTB\asv-neufeld\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{590E5541-69DA-4125-A7AF-B4D902BCF3E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6AF1D63-4154-4FC7-969B-4A07BFC45EF7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="791" uniqueCount="199">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="793" uniqueCount="202">
   <si>
     <t>Mannschaft</t>
   </si>
@@ -642,6 +642,15 @@
   </si>
   <si>
     <t>Endstand 7:2 für Neufeld</t>
+  </si>
+  <si>
+    <t>Endstand 3:1 für Edelserpentin</t>
+  </si>
+  <si>
+    <t>Endstand 3:2 für Parndorf</t>
+  </si>
+  <si>
+    <t>Endstand 2:2 Freundschaftsspiel</t>
   </si>
 </sst>
 </file>
@@ -5083,6 +5092,9 @@
         <f>UPPER('Nach Mannschaften sortiert'!F29)</f>
         <v>WIMPASSING</v>
       </c>
+      <c r="F29" s="108" t="s">
+        <v>199</v>
+      </c>
       <c r="G29" s="108" t="str">
         <f>'Nach Mannschaften sortiert'!H29</f>
         <v>Heim</v>
@@ -5410,6 +5422,9 @@
         <f>UPPER('Nach Mannschaften sortiert'!F38)</f>
         <v>NEUFELD</v>
       </c>
+      <c r="F38" s="108" t="s">
+        <v>200</v>
+      </c>
       <c r="G38" s="108" t="str">
         <f>'Nach Mannschaften sortiert'!H38</f>
         <v>Heim</v>
@@ -7277,7 +7292,7 @@
         <v>155</v>
       </c>
       <c r="F90" s="108" t="s">
-        <v>157</v>
+        <v>201</v>
       </c>
       <c r="G90" s="108" t="s">
         <v>12</v>

--- a/Terminefussball_2026_Frühjahr.xlsx
+++ b/Terminefussball_2026_Frühjahr.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DTB\asv-neufeld\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6AF1D63-4154-4FC7-969B-4A07BFC45EF7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE00884F-C9EF-444B-AB48-CA103240BAF3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="793" uniqueCount="202">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="794" uniqueCount="203">
   <si>
     <t>Mannschaft</t>
   </si>
@@ -651,6 +651,9 @@
   </si>
   <si>
     <t>Endstand 2:2 Freundschaftsspiel</t>
+  </si>
+  <si>
+    <t>Endstand 1:1</t>
   </si>
 </sst>
 </file>
@@ -4264,6 +4267,9 @@
         <f>UPPER('Nach Mannschaften sortiert'!F6)</f>
         <v>ANDAU</v>
       </c>
+      <c r="F6" s="108" t="s">
+        <v>202</v>
+      </c>
       <c r="G6" s="108" t="str">
         <f>'Nach Mannschaften sortiert'!H6</f>
         <v>Auswärts</v>

--- a/Terminefussball_2026_Frühjahr.xlsx
+++ b/Terminefussball_2026_Frühjahr.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DTB\asv-neufeld\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE00884F-C9EF-444B-AB48-CA103240BAF3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B8811A8-2230-473B-A748-B954777FA82A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="794" uniqueCount="203">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="795" uniqueCount="204">
   <si>
     <t>Mannschaft</t>
   </si>
@@ -654,6 +654,9 @@
   </si>
   <si>
     <t>Endstand 1:1</t>
+  </si>
+  <si>
+    <t>Endstand 5:0 für Andau</t>
   </si>
 </sst>
 </file>
@@ -4745,6 +4748,9 @@
         <f>UPPER('Nach Mannschaften sortiert'!F19)</f>
         <v>ANDAU</v>
       </c>
+      <c r="F19" s="108" t="s">
+        <v>203</v>
+      </c>
       <c r="G19" s="108" t="str">
         <f>'Nach Mannschaften sortiert'!H19</f>
         <v>Auswärts</v>

--- a/Terminefussball_2026_Frühjahr.xlsx
+++ b/Terminefussball_2026_Frühjahr.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DTB\asv-neufeld\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B8811A8-2230-473B-A748-B954777FA82A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B570ED7D-1329-4D5A-A874-3F1C875E7A94}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3316,19 +3316,19 @@
         <v>61</v>
       </c>
       <c r="D62" s="32">
-        <v>46109</v>
+        <v>46127</v>
       </c>
       <c r="E62" s="28">
-        <v>0.41666666666666669</v>
+        <v>0.72916666666666663</v>
       </c>
       <c r="F62" s="27" t="s">
-        <v>31</v>
+        <v>2</v>
       </c>
       <c r="G62" s="27" t="s">
         <v>31</v>
       </c>
       <c r="H62" s="27" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="63" spans="1:10" x14ac:dyDescent="0.3">
@@ -3838,7 +3838,9 @@
       <c r="D82" s="54">
         <v>46143</v>
       </c>
-      <c r="E82" s="55"/>
+      <c r="E82" s="55">
+        <v>0.4375</v>
+      </c>
       <c r="F82" s="53" t="s">
         <v>45</v>
       </c>
@@ -6298,11 +6300,11 @@
       </c>
       <c r="E62" s="39" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F62)</f>
-        <v>STEINBRUNN</v>
+        <v>NEUFELD</v>
       </c>
       <c r="G62" s="108" t="str">
         <f>'Nach Mannschaften sortiert'!H62</f>
-        <v>Auswärts</v>
+        <v>Heim</v>
       </c>
       <c r="H62" t="str">
         <f>'Nach Mannschaften sortiert'!G62</f>
@@ -7013,11 +7015,11 @@
       </c>
       <c r="C82" s="39">
         <f>'Nach Mannschaften sortiert'!E82</f>
-        <v>0</v>
+        <v>0.4375</v>
       </c>
       <c r="D82" s="39">
         <f t="shared" si="2"/>
-        <v>0.125</v>
+        <v>0.5625</v>
       </c>
       <c r="E82" s="39" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F82)</f>
@@ -9815,15 +9817,15 @@
       </c>
       <c r="D55" s="16">
         <f>'Nach Mannschaften sortiert'!D62</f>
-        <v>46109</v>
+        <v>46127</v>
       </c>
       <c r="E55" s="38">
         <f>'Nach Mannschaften sortiert'!E62</f>
-        <v>0.41666666666666669</v>
+        <v>0.72916666666666663</v>
       </c>
       <c r="F55" s="2" t="str">
         <f>'Nach Mannschaften sortiert'!F62</f>
-        <v>Steinbrunn</v>
+        <v>Neufeld</v>
       </c>
       <c r="G55" s="2" t="str">
         <f>'Nach Mannschaften sortiert'!G62</f>
@@ -9831,7 +9833,7 @@
       </c>
       <c r="H55" s="2" t="str">
         <f>'Nach Mannschaften sortiert'!H62</f>
-        <v>Auswärts</v>
+        <v>Heim</v>
       </c>
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.3">
@@ -10565,7 +10567,7 @@
       </c>
       <c r="E77" s="38">
         <f>'Nach Mannschaften sortiert'!E82</f>
-        <v>0</v>
+        <v>0.4375</v>
       </c>
       <c r="F77" s="2" t="str">
         <f>'Nach Mannschaften sortiert'!F82</f>
@@ -13149,12 +13151,12 @@
       </c>
       <c r="B54" s="72">
         <f>Heimspiele!D55</f>
-        <v>46109</v>
+        <v>46127</v>
       </c>
       <c r="C54" s="72"/>
       <c r="D54" t="str">
         <f>Heimspiele!F55</f>
-        <v>Steinbrunn</v>
+        <v>Neufeld</v>
       </c>
       <c r="E54" t="str">
         <f>Heimspiele!G55</f>

--- a/Terminefussball_2026_Frühjahr.xlsx
+++ b/Terminefussball_2026_Frühjahr.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DTB\asv-neufeld\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B570ED7D-1329-4D5A-A874-3F1C875E7A94}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53FC9526-5ED0-4B51-8BCE-A51869922731}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="795" uniqueCount="204">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="796" uniqueCount="205">
   <si>
     <t>Mannschaft</t>
   </si>
@@ -657,6 +657,9 @@
   </si>
   <si>
     <t>Endstand 5:0 für Andau</t>
+  </si>
+  <si>
+    <t>Endstand 5:1 für Steinbrunn</t>
   </si>
 </sst>
 </file>
@@ -6292,15 +6295,19 @@
         <v>46127</v>
       </c>
       <c r="C62" s="39">
-        <v>0.75</v>
+        <f>'Nach Mannschaften sortiert'!E62</f>
+        <v>0.72916666666666663</v>
       </c>
       <c r="D62" s="39">
         <f t="shared" si="0"/>
-        <v>0.79861111111111116</v>
+        <v>0.77777777777777779</v>
       </c>
       <c r="E62" s="39" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F62)</f>
         <v>NEUFELD</v>
+      </c>
+      <c r="F62" s="108" t="s">
+        <v>204</v>
       </c>
       <c r="G62" s="108" t="str">
         <f>'Nach Mannschaften sortiert'!H62</f>

--- a/Terminefussball_2026_Frühjahr.xlsx
+++ b/Terminefussball_2026_Frühjahr.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DTB\asv-neufeld\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53FC9526-5ED0-4B51-8BCE-A51869922731}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42A1634D-AD67-4AC9-BFD2-27DD132B3DCC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="796" uniqueCount="205">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="797" uniqueCount="206">
   <si>
     <t>Mannschaft</t>
   </si>
@@ -660,6 +660,9 @@
   </si>
   <si>
     <t>Endstand 5:1 für Steinbrunn</t>
+  </si>
+  <si>
+    <t>Endstand 1:0 für Großhöflein</t>
   </si>
 </sst>
 </file>
@@ -5478,6 +5481,9 @@
         <f>UPPER('Nach Mannschaften sortiert'!F39)</f>
         <v>WIMPASSING</v>
       </c>
+      <c r="F39" s="108" t="s">
+        <v>205</v>
+      </c>
       <c r="G39" s="108" t="str">
         <f>'Nach Mannschaften sortiert'!H39</f>
         <v>Heim</v>

--- a/Terminefussball_2026_Frühjahr.xlsx
+++ b/Terminefussball_2026_Frühjahr.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DTB\asv-neufeld\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42A1634D-AD67-4AC9-BFD2-27DD132B3DCC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE94388F-470C-4BC0-8925-72BCACEDB30C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="797" uniqueCount="206">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="800" uniqueCount="208">
   <si>
     <t>Mannschaft</t>
   </si>
@@ -663,6 +663,12 @@
   </si>
   <si>
     <t>Endstand 1:0 für Großhöflein</t>
+  </si>
+  <si>
+    <t>Endstand 3:3</t>
+  </si>
+  <si>
+    <t>Endstand 2:2</t>
   </si>
 </sst>
 </file>
@@ -4317,6 +4323,9 @@
         <f>UPPER('Nach Mannschaften sortiert'!F7)</f>
         <v>NEUFELD</v>
       </c>
+      <c r="F7" s="108" t="s">
+        <v>195</v>
+      </c>
       <c r="G7" s="108" t="str">
         <f>'Nach Mannschaften sortiert'!H7</f>
         <v>Heim</v>
@@ -4794,6 +4803,9 @@
         <f>UPPER('Nach Mannschaften sortiert'!F20)</f>
         <v>NEUFELD</v>
       </c>
+      <c r="F20" s="108" t="s">
+        <v>206</v>
+      </c>
       <c r="G20" s="108" t="str">
         <f>'Nach Mannschaften sortiert'!H20</f>
         <v>Heim</v>
@@ -6060,6 +6072,9 @@
       <c r="E55" s="39" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F55)</f>
         <v>RUST</v>
+      </c>
+      <c r="F55" s="108" t="s">
+        <v>207</v>
       </c>
       <c r="G55" s="108" t="str">
         <f>'Nach Mannschaften sortiert'!H55</f>

--- a/Terminefussball_2026_Frühjahr.xlsx
+++ b/Terminefussball_2026_Frühjahr.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DTB\asv-neufeld\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE94388F-470C-4BC0-8925-72BCACEDB30C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4378E9C1-416C-46EA-BFD6-2B0C42A20AE9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="800" uniqueCount="208">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="803" uniqueCount="210">
   <si>
     <t>Mannschaft</t>
   </si>
@@ -669,6 +669,12 @@
   </si>
   <si>
     <t>Endstand 2:2</t>
+  </si>
+  <si>
+    <t>Endstand 5:1 für Wolfau</t>
+  </si>
+  <si>
+    <t>Endstand 4:2 für Klingenbach</t>
   </si>
 </sst>
 </file>
@@ -5163,6 +5169,9 @@
         <f>UPPER('Nach Mannschaften sortiert'!F30)</f>
         <v>WOLFAU</v>
       </c>
+      <c r="F30" s="108" t="s">
+        <v>208</v>
+      </c>
       <c r="G30" s="108" t="str">
         <f>'Nach Mannschaften sortiert'!H30</f>
         <v>Auswärts</v>
@@ -5823,6 +5832,9 @@
         <f>UPPER('Nach Mannschaften sortiert'!F48)</f>
         <v>KITTSEE</v>
       </c>
+      <c r="F48" s="108" t="s">
+        <v>206</v>
+      </c>
       <c r="G48" s="108" t="str">
         <f>'Nach Mannschaften sortiert'!H48</f>
         <v>Auswärts</v>
@@ -6404,6 +6416,9 @@
       <c r="E64" s="39" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F64)</f>
         <v>KLINGENBACH</v>
+      </c>
+      <c r="F64" s="108" t="s">
+        <v>209</v>
       </c>
       <c r="G64" s="108" t="str">
         <f>'Nach Mannschaften sortiert'!H64</f>

--- a/Terminefussball_2026_Frühjahr.xlsx
+++ b/Terminefussball_2026_Frühjahr.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DTB\asv-neufeld\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4378E9C1-416C-46EA-BFD6-2B0C42A20AE9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17C0C917-DEB9-47AE-B8AE-FB720DC93C05}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="803" uniqueCount="210">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="804" uniqueCount="211">
   <si>
     <t>Mannschaft</t>
   </si>
@@ -675,6 +675,9 @@
   </si>
   <si>
     <t>Endstand 4:2 für Klingenbach</t>
+  </si>
+  <si>
+    <t>Endstand 4:2 für Neufeld</t>
   </si>
 </sst>
 </file>
@@ -6456,6 +6459,9 @@
         <f>UPPER('Nach Mannschaften sortiert'!F65)</f>
         <v>NEUFELD</v>
       </c>
+      <c r="F65" s="108" t="s">
+        <v>210</v>
+      </c>
       <c r="G65" s="108" t="str">
         <f>'Nach Mannschaften sortiert'!H65</f>
         <v>Heim</v>

--- a/Terminefussball_2026_Frühjahr.xlsx
+++ b/Terminefussball_2026_Frühjahr.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DTB\asv-neufeld\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17C0C917-DEB9-47AE-B8AE-FB720DC93C05}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E478F90D-5A2F-4939-8BDB-C175E25B477A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="804" uniqueCount="211">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="806" uniqueCount="212">
   <si>
     <t>Mannschaft</t>
   </si>
@@ -678,6 +678,9 @@
   </si>
   <si>
     <t>Endstand 4:2 für Neufeld</t>
+  </si>
+  <si>
+    <t>Endstand 3:0 für Deutsch Jahrndorf</t>
   </si>
 </sst>
 </file>
@@ -4371,6 +4374,9 @@
         <f>UPPER('Nach Mannschaften sortiert'!F8)</f>
         <v>DEUTSCH JAHRNDORF</v>
       </c>
+      <c r="F8" s="108" t="s">
+        <v>202</v>
+      </c>
       <c r="G8" s="108" t="str">
         <f>'Nach Mannschaften sortiert'!H8</f>
         <v>Auswärts</v>
@@ -4849,6 +4855,9 @@
       <c r="E21" s="39" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F21)</f>
         <v>DEUTSCH JAHRNDORF</v>
+      </c>
+      <c r="F21" s="108" t="s">
+        <v>211</v>
       </c>
       <c r="G21" s="108" t="str">
         <f>'Nach Mannschaften sortiert'!H21</f>

--- a/Terminefussball_2026_Frühjahr.xlsx
+++ b/Terminefussball_2026_Frühjahr.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DTB\asv-neufeld\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E478F90D-5A2F-4939-8BDB-C175E25B477A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64BC4A65-C21C-455F-B219-F19A105F2D5E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="806" uniqueCount="212">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="807" uniqueCount="213">
   <si>
     <t>Mannschaft</t>
   </si>
@@ -681,6 +681,9 @@
   </si>
   <si>
     <t>Endstand 3:0 für Deutsch Jahrndorf</t>
+  </si>
+  <si>
+    <t>Endstand 6:2 für Neufeld</t>
   </si>
 </sst>
 </file>
@@ -5883,6 +5886,9 @@
         <f>UPPER('Nach Mannschaften sortiert'!F49)</f>
         <v>NEUFELD</v>
       </c>
+      <c r="F49" s="108" t="s">
+        <v>212</v>
+      </c>
       <c r="G49" s="108" t="str">
         <f>'Nach Mannschaften sortiert'!H49</f>
         <v>Heim</v>

--- a/Terminefussball_2026_Frühjahr.xlsx
+++ b/Terminefussball_2026_Frühjahr.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DTB\asv-neufeld\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64BC4A65-C21C-455F-B219-F19A105F2D5E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A1DD70C-558F-48EA-98DB-060FBEA347BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="807" uniqueCount="213">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="809" uniqueCount="214">
   <si>
     <t>Mannschaft</t>
   </si>
@@ -684,6 +684,9 @@
   </si>
   <si>
     <t>Endstand 6:2 für Neufeld</t>
+  </si>
+  <si>
+    <t>Endstand 7:2 für Breitenbrunn</t>
   </si>
 </sst>
 </file>
@@ -5556,6 +5559,9 @@
         <f>UPPER('Nach Mannschaften sortiert'!F40)</f>
         <v>NEUSIEDL</v>
       </c>
+      <c r="F40" s="108" t="s">
+        <v>207</v>
+      </c>
       <c r="G40" s="108" t="str">
         <f>'Nach Mannschaften sortiert'!H40</f>
         <v>Auswärts</v>
@@ -6141,6 +6147,9 @@
       <c r="E56" s="39" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F56)</f>
         <v>NEUFELD</v>
+      </c>
+      <c r="F56" s="108" t="s">
+        <v>213</v>
       </c>
       <c r="G56" s="108" t="str">
         <f>'Nach Mannschaften sortiert'!H56</f>

--- a/Terminefussball_2026_Frühjahr.xlsx
+++ b/Terminefussball_2026_Frühjahr.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DTB\asv-neufeld\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A1DD70C-558F-48EA-98DB-060FBEA347BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75256A68-B590-4A2B-9D63-10BB7A83AAF3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -686,7 +686,7 @@
     <t>Endstand 6:2 für Neufeld</t>
   </si>
   <si>
-    <t>Endstand 7:2 für Breitenbrunn</t>
+    <t>Endstand 7:1 für Breitenbrunn</t>
   </si>
 </sst>
 </file>

--- a/Terminefussball_2026_Frühjahr.xlsx
+++ b/Terminefussball_2026_Frühjahr.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DTB\asv-neufeld\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75256A68-B590-4A2B-9D63-10BB7A83AAF3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{631B02E1-9933-4295-AB41-C0932A2F9A42}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="809" uniqueCount="214">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="810" uniqueCount="214">
   <si>
     <t>Mannschaft</t>
   </si>
@@ -5226,6 +5226,9 @@
         <f>UPPER('Nach Mannschaften sortiert'!F31)</f>
         <v>NEUFELD</v>
       </c>
+      <c r="F31" s="108" t="s">
+        <v>206</v>
+      </c>
       <c r="G31" s="108" t="str">
         <f>'Nach Mannschaften sortiert'!H31</f>
         <v>Heim</v>

--- a/Terminefussball_2026_Frühjahr.xlsx
+++ b/Terminefussball_2026_Frühjahr.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DTB\asv-neufeld\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{631B02E1-9933-4295-AB41-C0932A2F9A42}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE557585-E467-4278-84FB-661F105F51F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="810" uniqueCount="214">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="816" uniqueCount="218">
   <si>
     <t>Mannschaft</t>
   </si>
@@ -687,6 +687,18 @@
   </si>
   <si>
     <t>Endstand 7:1 für Breitenbrunn</t>
+  </si>
+  <si>
+    <t>Endstand 6:0 für Neufeld</t>
+  </si>
+  <si>
+    <t>Endstand 3:0 für Hornstein</t>
+  </si>
+  <si>
+    <t>Endstand 5:0 für Neufeld</t>
+  </si>
+  <si>
+    <t>Endstand 5:3 für Leithaprodersdorf</t>
   </si>
 </sst>
 </file>
@@ -3026,10 +3038,10 @@
         <v>35</v>
       </c>
       <c r="D50" s="21">
-        <v>46151</v>
+        <v>46145</v>
       </c>
       <c r="E50" s="22">
-        <v>0.75</v>
+        <v>0.58333333333333337</v>
       </c>
       <c r="F50" s="20" t="s">
         <v>45</v>
@@ -4419,6 +4431,9 @@
         <f>UPPER('Nach Mannschaften sortiert'!F9)</f>
         <v>NEUFELD</v>
       </c>
+      <c r="F9" s="108" t="s">
+        <v>215</v>
+      </c>
       <c r="G9" s="108" t="str">
         <f>'Nach Mannschaften sortiert'!H9</f>
         <v>Heim</v>
@@ -4900,6 +4915,9 @@
         <f>UPPER('Nach Mannschaften sortiert'!F22)</f>
         <v>NEUFELD</v>
       </c>
+      <c r="F22" s="108" t="s">
+        <v>214</v>
+      </c>
       <c r="G22" s="108" t="str">
         <f>'Nach Mannschaften sortiert'!H22</f>
         <v>Heim</v>
@@ -5265,6 +5283,9 @@
         <f>UPPER('Nach Mannschaften sortiert'!F32)</f>
         <v>ST. GEORGEN</v>
       </c>
+      <c r="F32" s="108" t="s">
+        <v>207</v>
+      </c>
       <c r="G32" s="108" t="str">
         <f>'Nach Mannschaften sortiert'!H32</f>
         <v>Auswärts</v>
@@ -5601,6 +5622,9 @@
         <f>UPPER('Nach Mannschaften sortiert'!F41)</f>
         <v>NEUFELD</v>
       </c>
+      <c r="F41" s="108" t="s">
+        <v>207</v>
+      </c>
       <c r="G41" s="108" t="str">
         <f>'Nach Mannschaften sortiert'!H41</f>
         <v>Heim</v>
@@ -5781,6 +5805,9 @@
         <f>UPPER('Nach Mannschaften sortiert'!F46)</f>
         <v>NEUFELD</v>
       </c>
+      <c r="F46" s="108" t="s">
+        <v>216</v>
+      </c>
       <c r="G46" s="108" t="str">
         <f>'Nach Mannschaften sortiert'!H46</f>
         <v>Heim</v>
@@ -5919,16 +5946,15 @@
     </row>
     <row r="50" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B50" s="105">
-        <f>'Nach Mannschaften sortiert'!D50</f>
         <v>46151</v>
       </c>
       <c r="C50" s="39">
         <f>'Nach Mannschaften sortiert'!E50</f>
-        <v>0.75</v>
+        <v>0.58333333333333337</v>
       </c>
       <c r="D50" s="39">
         <f t="shared" si="0"/>
-        <v>0.8125</v>
+        <v>0.64583333333333337</v>
       </c>
       <c r="E50" s="39" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F50)</f>
@@ -6189,6 +6215,9 @@
       <c r="E57" s="39" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F57)</f>
         <v>LEITHAPRODERSDORF</v>
+      </c>
+      <c r="F57" s="108" t="s">
+        <v>217</v>
       </c>
       <c r="G57" s="108" t="str">
         <f>'Nach Mannschaften sortiert'!H57</f>
@@ -9383,11 +9412,11 @@
       </c>
       <c r="D40" s="16">
         <f>'Nach Mannschaften sortiert'!D50</f>
-        <v>46151</v>
+        <v>46145</v>
       </c>
       <c r="E40" s="38">
         <f>'Nach Mannschaften sortiert'!E50</f>
-        <v>0.75</v>
+        <v>0.58333333333333337</v>
       </c>
       <c r="F40" s="2" t="str">
         <f>'Nach Mannschaften sortiert'!F50</f>
@@ -12576,7 +12605,7 @@
       </c>
       <c r="B39" s="72">
         <f>Heimspiele!D40</f>
-        <v>46151</v>
+        <v>46145</v>
       </c>
       <c r="C39" s="72"/>
       <c r="D39" t="str">

--- a/Terminefussball_2026_Frühjahr.xlsx
+++ b/Terminefussball_2026_Frühjahr.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DTB\asv-neufeld\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE557585-E467-4278-84FB-661F105F51F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0007DDE4-23D1-4538-8E1B-0C4B9E818999}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="816" uniqueCount="218">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="816" uniqueCount="217">
   <si>
     <t>Mannschaft</t>
   </si>
@@ -483,9 +483,6 @@
   </si>
   <si>
     <t>aktiv</t>
-  </si>
-  <si>
-    <t>abgesagt</t>
   </si>
   <si>
     <t>Endstand:2:2</t>
@@ -3041,7 +3038,7 @@
         <v>46145</v>
       </c>
       <c r="E50" s="22">
-        <v>0.58333333333333337</v>
+        <v>0.75</v>
       </c>
       <c r="F50" s="20" t="s">
         <v>45</v>
@@ -3150,10 +3147,10 @@
         <v>18</v>
       </c>
       <c r="D54" s="31">
-        <v>46110</v>
+        <v>46188</v>
       </c>
       <c r="E54" s="11">
-        <v>0.45833333333333331</v>
+        <v>0.75</v>
       </c>
       <c r="F54" s="10" t="s">
         <v>2</v>
@@ -4138,7 +4135,7 @@
         <v>144</v>
       </c>
       <c r="K1" s="108" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.3">
@@ -4159,7 +4156,7 @@
         <v>RUST</v>
       </c>
       <c r="F2" s="108" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="G2" s="108" t="str">
         <f>'Nach Mannschaften sortiert'!H2</f>
@@ -4177,7 +4174,7 @@
         <v>145</v>
       </c>
       <c r="K2" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.3">
@@ -4198,7 +4195,7 @@
         <v>NEUFELD</v>
       </c>
       <c r="F3" s="108" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="G3" s="108" t="str">
         <f>'Nach Mannschaften sortiert'!H3</f>
@@ -4216,7 +4213,7 @@
         <v>145</v>
       </c>
       <c r="K3" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.3">
@@ -4237,7 +4234,7 @@
         <v>GATTENDORF</v>
       </c>
       <c r="F4" s="108" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="G4" s="108" t="str">
         <f>'Nach Mannschaften sortiert'!H4</f>
@@ -4255,7 +4252,7 @@
         <v>145</v>
       </c>
       <c r="K4" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.3">
@@ -4276,7 +4273,7 @@
         <v>NEUFELD</v>
       </c>
       <c r="F5" s="108" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="G5" s="108" t="str">
         <f>'Nach Mannschaften sortiert'!H5</f>
@@ -4294,7 +4291,7 @@
         <v>145</v>
       </c>
       <c r="K5" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.3">
@@ -4315,7 +4312,7 @@
         <v>ANDAU</v>
       </c>
       <c r="F6" s="108" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="G6" s="108" t="str">
         <f>'Nach Mannschaften sortiert'!H6</f>
@@ -4333,7 +4330,7 @@
         <v>145</v>
       </c>
       <c r="K6" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.3">
@@ -4354,7 +4351,7 @@
         <v>NEUFELD</v>
       </c>
       <c r="F7" s="108" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="G7" s="108" t="str">
         <f>'Nach Mannschaften sortiert'!H7</f>
@@ -4372,7 +4369,7 @@
         <v>145</v>
       </c>
       <c r="K7" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.3">
@@ -4393,7 +4390,7 @@
         <v>DEUTSCH JAHRNDORF</v>
       </c>
       <c r="F8" s="108" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="G8" s="108" t="str">
         <f>'Nach Mannschaften sortiert'!H8</f>
@@ -4411,7 +4408,7 @@
         <v>145</v>
       </c>
       <c r="K8" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.3">
@@ -4432,7 +4429,7 @@
         <v>NEUFELD</v>
       </c>
       <c r="F9" s="108" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="G9" s="108" t="str">
         <f>'Nach Mannschaften sortiert'!H9</f>
@@ -4450,7 +4447,7 @@
         <v>145</v>
       </c>
       <c r="K9" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.3">
@@ -4486,7 +4483,7 @@
         <v>145</v>
       </c>
       <c r="K10" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.3">
@@ -4522,7 +4519,7 @@
         <v>145</v>
       </c>
       <c r="K11" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.3">
@@ -4558,7 +4555,7 @@
         <v>145</v>
       </c>
       <c r="K12" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.3">
@@ -4594,7 +4591,7 @@
         <v>145</v>
       </c>
       <c r="K13" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.3">
@@ -4630,7 +4627,7 @@
         <v>145</v>
       </c>
       <c r="K14" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.3">
@@ -4650,7 +4647,7 @@
         <v>RUST</v>
       </c>
       <c r="F15" s="108" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="G15" s="108" t="str">
         <f>'Nach Mannschaften sortiert'!H15</f>
@@ -4668,7 +4665,7 @@
         <v>145</v>
       </c>
       <c r="K15" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.3">
@@ -4688,7 +4685,7 @@
         <v>NEUFELD</v>
       </c>
       <c r="F16" s="108" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="G16" s="108" t="str">
         <f>'Nach Mannschaften sortiert'!H16</f>
@@ -4706,7 +4703,7 @@
         <v>145</v>
       </c>
       <c r="K16" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="17" spans="2:11" x14ac:dyDescent="0.3">
@@ -4726,7 +4723,7 @@
         <v>GATTENDORF</v>
       </c>
       <c r="F17" s="108" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="G17" s="108" t="str">
         <f>'Nach Mannschaften sortiert'!H17</f>
@@ -4744,7 +4741,7 @@
         <v>145</v>
       </c>
       <c r="K17" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="18" spans="2:11" x14ac:dyDescent="0.3">
@@ -4764,7 +4761,7 @@
         <v>NEUFELD</v>
       </c>
       <c r="F18" s="108" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="G18" s="108" t="str">
         <f>'Nach Mannschaften sortiert'!H18</f>
@@ -4782,7 +4779,7 @@
         <v>145</v>
       </c>
       <c r="K18" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="19" spans="2:11" x14ac:dyDescent="0.3">
@@ -4802,7 +4799,7 @@
         <v>ANDAU</v>
       </c>
       <c r="F19" s="108" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="G19" s="108" t="str">
         <f>'Nach Mannschaften sortiert'!H19</f>
@@ -4820,7 +4817,7 @@
         <v>145</v>
       </c>
       <c r="K19" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="20" spans="2:11" x14ac:dyDescent="0.3">
@@ -4840,7 +4837,7 @@
         <v>NEUFELD</v>
       </c>
       <c r="F20" s="108" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="G20" s="108" t="str">
         <f>'Nach Mannschaften sortiert'!H20</f>
@@ -4858,7 +4855,7 @@
         <v>145</v>
       </c>
       <c r="K20" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="21" spans="2:11" x14ac:dyDescent="0.3">
@@ -4878,7 +4875,7 @@
         <v>DEUTSCH JAHRNDORF</v>
       </c>
       <c r="F21" s="108" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="G21" s="108" t="str">
         <f>'Nach Mannschaften sortiert'!H21</f>
@@ -4896,7 +4893,7 @@
         <v>145</v>
       </c>
       <c r="K21" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="22" spans="2:11" x14ac:dyDescent="0.3">
@@ -4916,7 +4913,7 @@
         <v>NEUFELD</v>
       </c>
       <c r="F22" s="108" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="G22" s="108" t="str">
         <f>'Nach Mannschaften sortiert'!H22</f>
@@ -4934,7 +4931,7 @@
         <v>145</v>
       </c>
       <c r="K22" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="23" spans="2:11" x14ac:dyDescent="0.3">
@@ -4969,7 +4966,7 @@
         <v>145</v>
       </c>
       <c r="K23" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="24" spans="2:11" x14ac:dyDescent="0.3">
@@ -5004,7 +5001,7 @@
         <v>145</v>
       </c>
       <c r="K24" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="25" spans="2:11" x14ac:dyDescent="0.3">
@@ -5039,7 +5036,7 @@
         <v>145</v>
       </c>
       <c r="K25" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="26" spans="2:11" x14ac:dyDescent="0.3">
@@ -5074,7 +5071,7 @@
         <v>145</v>
       </c>
       <c r="K26" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="27" spans="2:11" x14ac:dyDescent="0.3">
@@ -5109,7 +5106,7 @@
         <v>145</v>
       </c>
       <c r="K27" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="28" spans="2:11" x14ac:dyDescent="0.3">
@@ -5128,7 +5125,7 @@
         <v>SV LEITHAPRODERSDORF</v>
       </c>
       <c r="F28" s="108" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="G28" s="108" t="str">
         <f>'Nach Mannschaften sortiert'!H28</f>
@@ -5146,7 +5143,7 @@
         <v>145</v>
       </c>
       <c r="K28" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="29" spans="2:11" x14ac:dyDescent="0.3">
@@ -5167,7 +5164,7 @@
         <v>WIMPASSING</v>
       </c>
       <c r="F29" s="108" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="G29" s="108" t="str">
         <f>'Nach Mannschaften sortiert'!H29</f>
@@ -5185,7 +5182,7 @@
         <v>145</v>
       </c>
       <c r="K29" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="30" spans="2:11" x14ac:dyDescent="0.3">
@@ -5206,7 +5203,7 @@
         <v>WOLFAU</v>
       </c>
       <c r="F30" s="108" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="G30" s="108" t="str">
         <f>'Nach Mannschaften sortiert'!H30</f>
@@ -5224,7 +5221,7 @@
         <v>145</v>
       </c>
       <c r="K30" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="31" spans="2:11" x14ac:dyDescent="0.3">
@@ -5245,7 +5242,7 @@
         <v>NEUFELD</v>
       </c>
       <c r="F31" s="108" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="G31" s="108" t="str">
         <f>'Nach Mannschaften sortiert'!H31</f>
@@ -5263,7 +5260,7 @@
         <v>145</v>
       </c>
       <c r="K31" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="32" spans="2:11" x14ac:dyDescent="0.3">
@@ -5284,7 +5281,7 @@
         <v>ST. GEORGEN</v>
       </c>
       <c r="F32" s="108" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="G32" s="108" t="str">
         <f>'Nach Mannschaften sortiert'!H32</f>
@@ -5302,7 +5299,7 @@
         <v>145</v>
       </c>
       <c r="K32" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="33" spans="2:11" x14ac:dyDescent="0.3">
@@ -5338,7 +5335,7 @@
         <v>145</v>
       </c>
       <c r="K33" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="34" spans="2:11" x14ac:dyDescent="0.3">
@@ -5374,7 +5371,7 @@
         <v>145</v>
       </c>
       <c r="K34" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="35" spans="2:11" x14ac:dyDescent="0.3">
@@ -5395,7 +5392,7 @@
         <v>WIMPASSING</v>
       </c>
       <c r="F35" s="108" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="G35" s="108" t="str">
         <f>'Nach Mannschaften sortiert'!H35</f>
@@ -5413,7 +5410,7 @@
         <v>145</v>
       </c>
       <c r="K35" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="36" spans="2:11" x14ac:dyDescent="0.3">
@@ -5449,7 +5446,7 @@
         <v>145</v>
       </c>
       <c r="K36" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="37" spans="2:11" x14ac:dyDescent="0.3">
@@ -5485,7 +5482,7 @@
         <v>145</v>
       </c>
       <c r="K37" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="38" spans="2:11" x14ac:dyDescent="0.3">
@@ -5506,7 +5503,7 @@
         <v>NEUFELD</v>
       </c>
       <c r="F38" s="108" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="G38" s="108" t="str">
         <f>'Nach Mannschaften sortiert'!H38</f>
@@ -5524,7 +5521,7 @@
         <v>145</v>
       </c>
       <c r="K38" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="39" spans="2:11" x14ac:dyDescent="0.3">
@@ -5545,7 +5542,7 @@
         <v>WIMPASSING</v>
       </c>
       <c r="F39" s="108" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="G39" s="108" t="str">
         <f>'Nach Mannschaften sortiert'!H39</f>
@@ -5563,7 +5560,7 @@
         <v>145</v>
       </c>
       <c r="K39" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="40" spans="2:11" x14ac:dyDescent="0.3">
@@ -5584,7 +5581,7 @@
         <v>NEUSIEDL</v>
       </c>
       <c r="F40" s="108" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="G40" s="108" t="str">
         <f>'Nach Mannschaften sortiert'!H40</f>
@@ -5602,7 +5599,7 @@
         <v>145</v>
       </c>
       <c r="K40" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="41" spans="2:11" x14ac:dyDescent="0.3">
@@ -5623,7 +5620,7 @@
         <v>NEUFELD</v>
       </c>
       <c r="F41" s="108" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="G41" s="108" t="str">
         <f>'Nach Mannschaften sortiert'!H41</f>
@@ -5641,7 +5638,7 @@
         <v>145</v>
       </c>
       <c r="K41" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="42" spans="2:11" x14ac:dyDescent="0.3">
@@ -5677,7 +5674,7 @@
         <v>145</v>
       </c>
       <c r="K42" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="43" spans="2:11" x14ac:dyDescent="0.3">
@@ -5713,7 +5710,7 @@
         <v>145</v>
       </c>
       <c r="K43" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="44" spans="2:11" x14ac:dyDescent="0.3">
@@ -5749,7 +5746,7 @@
         <v>145</v>
       </c>
       <c r="K44" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="45" spans="2:11" x14ac:dyDescent="0.3">
@@ -5785,7 +5782,7 @@
         <v>145</v>
       </c>
       <c r="K45" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="46" spans="2:11" x14ac:dyDescent="0.3">
@@ -5806,7 +5803,7 @@
         <v>NEUFELD</v>
       </c>
       <c r="F46" s="108" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="G46" s="108" t="str">
         <f>'Nach Mannschaften sortiert'!H46</f>
@@ -5824,7 +5821,7 @@
         <v>145</v>
       </c>
       <c r="K46" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="47" spans="2:11" x14ac:dyDescent="0.3">
@@ -5845,7 +5842,7 @@
         <v>PAMA</v>
       </c>
       <c r="F47" s="108" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="G47" s="108" t="str">
         <f>'Nach Mannschaften sortiert'!H47</f>
@@ -5863,7 +5860,7 @@
         <v>145</v>
       </c>
       <c r="K47" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="48" spans="2:11" x14ac:dyDescent="0.3">
@@ -5884,7 +5881,7 @@
         <v>KITTSEE</v>
       </c>
       <c r="F48" s="108" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="G48" s="108" t="str">
         <f>'Nach Mannschaften sortiert'!H48</f>
@@ -5902,7 +5899,7 @@
         <v>145</v>
       </c>
       <c r="K48" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="49" spans="2:11" x14ac:dyDescent="0.3">
@@ -5923,7 +5920,7 @@
         <v>NEUFELD</v>
       </c>
       <c r="F49" s="108" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="G49" s="108" t="str">
         <f>'Nach Mannschaften sortiert'!H49</f>
@@ -5941,7 +5938,7 @@
         <v>145</v>
       </c>
       <c r="K49" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="50" spans="2:11" x14ac:dyDescent="0.3">
@@ -5950,11 +5947,11 @@
       </c>
       <c r="C50" s="39">
         <f>'Nach Mannschaften sortiert'!E50</f>
-        <v>0.58333333333333337</v>
+        <v>0.75</v>
       </c>
       <c r="D50" s="39">
         <f t="shared" si="0"/>
-        <v>0.64583333333333337</v>
+        <v>0.8125</v>
       </c>
       <c r="E50" s="39" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F50)</f>
@@ -5976,7 +5973,7 @@
         <v>145</v>
       </c>
       <c r="K50" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="51" spans="2:11" x14ac:dyDescent="0.3">
@@ -6012,7 +6009,7 @@
         <v>145</v>
       </c>
       <c r="K51" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="52" spans="2:11" x14ac:dyDescent="0.3">
@@ -6048,7 +6045,7 @@
         <v>145</v>
       </c>
       <c r="K52" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="53" spans="2:11" x14ac:dyDescent="0.3">
@@ -6084,19 +6081,21 @@
         <v>145</v>
       </c>
       <c r="K53" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="54" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B54" s="105">
-        <v>46110</v>
+        <f>'Nach Mannschaften sortiert'!D54</f>
+        <v>46188</v>
       </c>
       <c r="C54" s="39">
-        <v>0.4375</v>
+        <f>'Nach Mannschaften sortiert'!E54</f>
+        <v>0.75</v>
       </c>
       <c r="D54" s="39">
         <f t="shared" si="0"/>
-        <v>0.50347222222222221</v>
+        <v>0.81597222222222221</v>
       </c>
       <c r="E54" s="39" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F54)</f>
@@ -6115,10 +6114,10 @@
         <v>U13</v>
       </c>
       <c r="J54" s="108" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="K54" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="55" spans="2:11" x14ac:dyDescent="0.3">
@@ -6139,7 +6138,7 @@
         <v>RUST</v>
       </c>
       <c r="F55" s="108" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="G55" s="108" t="str">
         <f>'Nach Mannschaften sortiert'!H55</f>
@@ -6157,7 +6156,7 @@
         <v>145</v>
       </c>
       <c r="K55" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="56" spans="2:11" x14ac:dyDescent="0.3">
@@ -6178,7 +6177,7 @@
         <v>NEUFELD</v>
       </c>
       <c r="F56" s="108" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="G56" s="108" t="str">
         <f>'Nach Mannschaften sortiert'!H56</f>
@@ -6196,7 +6195,7 @@
         <v>145</v>
       </c>
       <c r="K56" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="57" spans="2:11" x14ac:dyDescent="0.3">
@@ -6217,7 +6216,7 @@
         <v>LEITHAPRODERSDORF</v>
       </c>
       <c r="F57" s="108" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="G57" s="108" t="str">
         <f>'Nach Mannschaften sortiert'!H57</f>
@@ -6235,7 +6234,7 @@
         <v>145</v>
       </c>
       <c r="K57" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="58" spans="2:11" x14ac:dyDescent="0.3">
@@ -6271,7 +6270,7 @@
         <v>145</v>
       </c>
       <c r="K58" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="59" spans="2:11" x14ac:dyDescent="0.3">
@@ -6307,7 +6306,7 @@
         <v>145</v>
       </c>
       <c r="K59" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="60" spans="2:11" x14ac:dyDescent="0.3">
@@ -6343,7 +6342,7 @@
         <v>145</v>
       </c>
       <c r="K60" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="61" spans="2:11" x14ac:dyDescent="0.3">
@@ -6379,7 +6378,7 @@
         <v>145</v>
       </c>
       <c r="K61" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="62" spans="2:11" x14ac:dyDescent="0.3">
@@ -6399,7 +6398,7 @@
         <v>NEUFELD</v>
       </c>
       <c r="F62" s="108" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="G62" s="108" t="str">
         <f>'Nach Mannschaften sortiert'!H62</f>
@@ -6417,7 +6416,7 @@
         <v>145</v>
       </c>
       <c r="K62" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="63" spans="2:11" x14ac:dyDescent="0.3">
@@ -6438,7 +6437,7 @@
         <v>NEUFELD</v>
       </c>
       <c r="F63" s="108" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="G63" s="108" t="str">
         <f>'Nach Mannschaften sortiert'!H63</f>
@@ -6456,7 +6455,7 @@
         <v>145</v>
       </c>
       <c r="K63" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="64" spans="2:11" x14ac:dyDescent="0.3">
@@ -6477,7 +6476,7 @@
         <v>KLINGENBACH</v>
       </c>
       <c r="F64" s="108" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="G64" s="108" t="str">
         <f>'Nach Mannschaften sortiert'!H64</f>
@@ -6495,7 +6494,7 @@
         <v>145</v>
       </c>
       <c r="K64" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="65" spans="2:11" x14ac:dyDescent="0.3">
@@ -6516,7 +6515,7 @@
         <v>NEUFELD</v>
       </c>
       <c r="F65" s="108" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="G65" s="108" t="str">
         <f>'Nach Mannschaften sortiert'!H65</f>
@@ -6534,7 +6533,7 @@
         <v>145</v>
       </c>
       <c r="K65" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="66" spans="2:11" x14ac:dyDescent="0.3">
@@ -6570,7 +6569,7 @@
         <v>145</v>
       </c>
       <c r="K66" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="67" spans="2:11" x14ac:dyDescent="0.3">
@@ -6606,7 +6605,7 @@
         <v>145</v>
       </c>
       <c r="K67" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="68" spans="2:11" x14ac:dyDescent="0.3">
@@ -6642,7 +6641,7 @@
         <v>145</v>
       </c>
       <c r="K68" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="69" spans="2:11" x14ac:dyDescent="0.3">
@@ -6678,7 +6677,7 @@
         <v>145</v>
       </c>
       <c r="K69" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="70" spans="2:11" x14ac:dyDescent="0.3">
@@ -6714,7 +6713,7 @@
         <v>145</v>
       </c>
       <c r="K70" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="71" spans="2:11" x14ac:dyDescent="0.3">
@@ -6750,7 +6749,7 @@
         <v>145</v>
       </c>
       <c r="K71" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="72" spans="2:11" x14ac:dyDescent="0.3">
@@ -6786,7 +6785,7 @@
         <v>145</v>
       </c>
       <c r="K72" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="73" spans="2:11" x14ac:dyDescent="0.3">
@@ -6822,7 +6821,7 @@
         <v>145</v>
       </c>
       <c r="K73" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="74" spans="2:11" x14ac:dyDescent="0.3">
@@ -6858,7 +6857,7 @@
         <v>145</v>
       </c>
       <c r="K74" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="75" spans="2:11" x14ac:dyDescent="0.3">
@@ -6894,7 +6893,7 @@
         <v>145</v>
       </c>
       <c r="K75" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="76" spans="2:11" x14ac:dyDescent="0.3">
@@ -6930,7 +6929,7 @@
         <v>145</v>
       </c>
       <c r="K76" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="77" spans="2:11" x14ac:dyDescent="0.3">
@@ -6966,7 +6965,7 @@
         <v>145</v>
       </c>
       <c r="K77" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="78" spans="2:11" x14ac:dyDescent="0.3">
@@ -7002,7 +7001,7 @@
         <v>145</v>
       </c>
       <c r="K78" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="79" spans="2:11" x14ac:dyDescent="0.3">
@@ -7038,7 +7037,7 @@
         <v>145</v>
       </c>
       <c r="K79" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="80" spans="2:11" x14ac:dyDescent="0.3">
@@ -7074,7 +7073,7 @@
         <v>145</v>
       </c>
       <c r="K80" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="81" spans="2:11" x14ac:dyDescent="0.3">
@@ -7110,7 +7109,7 @@
         <v>145</v>
       </c>
       <c r="K81" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="82" spans="2:11" x14ac:dyDescent="0.3">
@@ -7146,7 +7145,7 @@
         <v>145</v>
       </c>
       <c r="K82" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="83" spans="2:11" x14ac:dyDescent="0.3">
@@ -7182,7 +7181,7 @@
         <v>145</v>
       </c>
       <c r="K83" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="84" spans="2:11" x14ac:dyDescent="0.3">
@@ -7218,7 +7217,7 @@
         <v>145</v>
       </c>
       <c r="K84" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="85" spans="2:11" x14ac:dyDescent="0.3">
@@ -7408,16 +7407,16 @@
         <v>0.51388888888888895</v>
       </c>
       <c r="E90" s="39" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="F90" s="108" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="G90" s="108" t="s">
         <v>12</v>
       </c>
       <c r="H90" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="I90" t="s">
         <v>18</v>
@@ -7426,7 +7425,7 @@
         <v>145</v>
       </c>
       <c r="K90" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="91" spans="2:11" x14ac:dyDescent="0.3">
@@ -7440,10 +7439,10 @@
         <v>0.75</v>
       </c>
       <c r="E91" s="39" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="F91" s="108" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="G91" s="108" t="s">
         <v>12</v>
@@ -7458,7 +7457,7 @@
         <v>145</v>
       </c>
       <c r="K91" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
   </sheetData>
@@ -7478,19 +7477,19 @@
   <sheetData>
     <row r="1" spans="1:3" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="110" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B1" s="110"/>
       <c r="C1" s="110" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="110" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B2" s="110" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C2" s="110" t="str">
         <f>"https://dtb-asv.github.io/asv-neufeld/"&amp;B2</f>
@@ -7499,10 +7498,10 @@
     </row>
     <row r="3" spans="1:3" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="110" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B3" s="110" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C3" s="110" t="str">
         <f t="shared" ref="C3:C18" si="0">"https://dtb-asv.github.io/asv-neufeld/"&amp;B3</f>
@@ -7511,10 +7510,10 @@
     </row>
     <row r="4" spans="1:3" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="110" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B4" s="110" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C4" s="110" t="str">
         <f t="shared" si="0"/>
@@ -7523,10 +7522,10 @@
     </row>
     <row r="5" spans="1:3" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="110" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B5" s="110" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C5" s="110" t="str">
         <f t="shared" si="0"/>
@@ -7535,10 +7534,10 @@
     </row>
     <row r="6" spans="1:3" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="110" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B6" s="110" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C6" s="110" t="str">
         <f t="shared" si="0"/>
@@ -7547,10 +7546,10 @@
     </row>
     <row r="7" spans="1:3" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="110" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B7" s="110" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C7" s="110" t="str">
         <f t="shared" si="0"/>
@@ -7559,10 +7558,10 @@
     </row>
     <row r="8" spans="1:3" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="110" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B8" s="110" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C8" s="110" t="str">
         <f t="shared" si="0"/>
@@ -7571,10 +7570,10 @@
     </row>
     <row r="9" spans="1:3" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="110" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B9" s="110" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C9" s="110" t="str">
         <f t="shared" si="0"/>
@@ -7583,10 +7582,10 @@
     </row>
     <row r="10" spans="1:3" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="110" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B10" s="110" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C10" s="110" t="str">
         <f t="shared" si="0"/>
@@ -7595,10 +7594,10 @@
     </row>
     <row r="11" spans="1:3" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="110" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B11" s="110" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="C11" s="110" t="str">
         <f t="shared" si="0"/>
@@ -7607,10 +7606,10 @@
     </row>
     <row r="12" spans="1:3" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="110" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B12" s="110" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C12" s="110" t="str">
         <f t="shared" si="0"/>
@@ -7619,10 +7618,10 @@
     </row>
     <row r="13" spans="1:3" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="110" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B13" s="110" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C13" s="110" t="str">
         <f t="shared" si="0"/>
@@ -7631,10 +7630,10 @@
     </row>
     <row r="14" spans="1:3" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="110" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B14" s="110" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C14" s="110" t="str">
         <f t="shared" si="0"/>
@@ -7643,10 +7642,10 @@
     </row>
     <row r="15" spans="1:3" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="110" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B15" s="110" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C15" s="110" t="str">
         <f t="shared" si="0"/>
@@ -7655,10 +7654,10 @@
     </row>
     <row r="16" spans="1:3" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="110" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B16" s="110" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C16" s="110" t="str">
         <f t="shared" si="0"/>
@@ -7667,7 +7666,7 @@
     </row>
     <row r="17" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B17" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C17" t="str">
         <f t="shared" si="0"/>
@@ -7676,7 +7675,7 @@
     </row>
     <row r="18" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B18" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C18" t="str">
         <f t="shared" si="0"/>
@@ -8290,11 +8289,11 @@
       </c>
       <c r="D7" s="16">
         <f>'Nach Mannschaften sortiert'!D54</f>
-        <v>46110</v>
+        <v>46188</v>
       </c>
       <c r="E7" s="38">
         <f>'Nach Mannschaften sortiert'!E54</f>
-        <v>0.45833333333333331</v>
+        <v>0.75</v>
       </c>
       <c r="F7" s="2" t="str">
         <f>'Nach Mannschaften sortiert'!F54</f>
@@ -9416,7 +9415,7 @@
       </c>
       <c r="E40" s="38">
         <f>'Nach Mannschaften sortiert'!E50</f>
-        <v>0.58333333333333337</v>
+        <v>0.75</v>
       </c>
       <c r="F40" s="2" t="str">
         <f>'Nach Mannschaften sortiert'!F50</f>
@@ -11669,11 +11668,11 @@
       </c>
       <c r="B17" s="81">
         <f>Heimspiele!D7</f>
-        <v>46110</v>
+        <v>46188</v>
       </c>
       <c r="C17" s="82">
         <f>Heimspiele!E7</f>
-        <v>0.45833333333333331</v>
+        <v>0.75</v>
       </c>
       <c r="D17" s="80" t="str">
         <f>Heimspiele!F7</f>

--- a/Terminefussball_2026_Frühjahr.xlsx
+++ b/Terminefussball_2026_Frühjahr.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DTB\asv-neufeld\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0007DDE4-23D1-4538-8E1B-0C4B9E818999}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0F3BEA5-B4AD-4AD9-B476-FA4027468A16}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="816" uniqueCount="217">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="821" uniqueCount="221">
   <si>
     <t>Mannschaft</t>
   </si>
@@ -696,6 +696,18 @@
   </si>
   <si>
     <t>Endstand 5:3 für Leithaprodersdorf</t>
+  </si>
+  <si>
+    <t>Endstand 7:3 für Kittsee</t>
+  </si>
+  <si>
+    <t>Endstand 3:1 für Gols</t>
+  </si>
+  <si>
+    <t>Endstand 5:3 für Wimpassing/Neufeld</t>
+  </si>
+  <si>
+    <t>Endstand 3:0 für Neufeld</t>
   </si>
 </sst>
 </file>
@@ -4467,6 +4479,9 @@
         <f>UPPER('Nach Mannschaften sortiert'!F10)</f>
         <v>GOLS</v>
       </c>
+      <c r="F10" s="108" t="s">
+        <v>220</v>
+      </c>
       <c r="G10" s="108" t="str">
         <f>'Nach Mannschaften sortiert'!H10</f>
         <v>Auswärts</v>
@@ -4950,6 +4965,9 @@
         <f>UPPER('Nach Mannschaften sortiert'!F23)</f>
         <v>GOLS</v>
       </c>
+      <c r="F23" s="108" t="s">
+        <v>218</v>
+      </c>
       <c r="G23" s="108" t="str">
         <f>'Nach Mannschaften sortiert'!H23</f>
         <v>Auswärts</v>
@@ -5319,6 +5337,9 @@
         <f>UPPER('Nach Mannschaften sortiert'!F33)</f>
         <v>WIMPASSING</v>
       </c>
+      <c r="F33" s="108" t="s">
+        <v>219</v>
+      </c>
       <c r="G33" s="108" t="str">
         <f>'Nach Mannschaften sortiert'!H33</f>
         <v>Heim</v>
@@ -5957,6 +5978,9 @@
         <f>UPPER('Nach Mannschaften sortiert'!F50)</f>
         <v>WULKAPRODERSDORF</v>
       </c>
+      <c r="F50" s="108" t="s">
+        <v>215</v>
+      </c>
       <c r="G50" s="108" t="str">
         <f>'Nach Mannschaften sortiert'!H50</f>
         <v>Auswärts</v>
@@ -6254,6 +6278,9 @@
         <f>UPPER('Nach Mannschaften sortiert'!F58)</f>
         <v>KITTSEE</v>
       </c>
+      <c r="F58" s="108" t="s">
+        <v>217</v>
+      </c>
       <c r="G58" s="108" t="str">
         <f>'Nach Mannschaften sortiert'!H58</f>
         <v>Auswärts</v>
@@ -6538,16 +6565,14 @@
     </row>
     <row r="66" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B66" s="105">
-        <f>'Nach Mannschaften sortiert'!D66</f>
-        <v>46151</v>
+        <v>46160</v>
       </c>
       <c r="C66" s="39">
-        <f>'Nach Mannschaften sortiert'!E66</f>
-        <v>0.41666666666666669</v>
+        <v>0.72916666666666663</v>
       </c>
       <c r="D66" s="39">
         <f t="shared" si="0"/>
-        <v>0.46527777777777779</v>
+        <v>0.77777777777777779</v>
       </c>
       <c r="E66" s="39" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F66)</f>

--- a/Terminefussball_2026_Frühjahr.xlsx
+++ b/Terminefussball_2026_Frühjahr.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DTB\asv-neufeld\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0F3BEA5-B4AD-4AD9-B476-FA4027468A16}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C768B8CF-AC45-46EE-8C7A-22D8DD2B2BC5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="821" uniqueCount="221">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="822" uniqueCount="222">
   <si>
     <t>Mannschaft</t>
   </si>
@@ -708,6 +708,9 @@
   </si>
   <si>
     <t>Endstand 3:0 für Neufeld</t>
+  </si>
+  <si>
+    <t>Endstand 4:3 für Neufeld</t>
   </si>
 </sst>
 </file>
@@ -6565,7 +6568,7 @@
     </row>
     <row r="66" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B66" s="105">
-        <v>46160</v>
+        <v>46155</v>
       </c>
       <c r="C66" s="39">
         <v>0.72916666666666663</v>
@@ -6577,6 +6580,9 @@
       <c r="E66" s="39" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F66)</f>
         <v>NEUFELD</v>
+      </c>
+      <c r="F66" s="108" t="s">
+        <v>221</v>
       </c>
       <c r="G66" s="108" t="str">
         <f>'Nach Mannschaften sortiert'!H66</f>

--- a/Terminefussball_2026_Frühjahr.xlsx
+++ b/Terminefussball_2026_Frühjahr.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DTB\asv-neufeld\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C768B8CF-AC45-46EE-8C7A-22D8DD2B2BC5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8724CA08-875E-4306-9C4F-E9180E84B4D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="822" uniqueCount="222">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="822" uniqueCount="223">
   <si>
     <t>Mannschaft</t>
   </si>
@@ -711,6 +711,9 @@
   </si>
   <si>
     <t>Endstand 4:3 für Neufeld</t>
+  </si>
+  <si>
+    <t>abgesagt</t>
   </si>
 </sst>
 </file>
@@ -6033,7 +6036,7 @@
         <v>U14</v>
       </c>
       <c r="J51" s="108" t="s">
-        <v>145</v>
+        <v>222</v>
       </c>
       <c r="K51" t="s">
         <v>158</v>

--- a/Terminefussball_2026_Frühjahr.xlsx
+++ b/Terminefussball_2026_Frühjahr.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DTB\asv-neufeld\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8724CA08-875E-4306-9C4F-E9180E84B4D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86332F2D-5D44-4D54-B6E4-C2256FB5F1DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="822" uniqueCount="223">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="825" uniqueCount="226">
   <si>
     <t>Mannschaft</t>
   </si>
@@ -714,6 +714,15 @@
   </si>
   <si>
     <t>abgesagt</t>
+  </si>
+  <si>
+    <t>Endstand 4:0 für Parndorf</t>
+  </si>
+  <si>
+    <t>Endstand 1:0 für Pama</t>
+  </si>
+  <si>
+    <t>Endstand 4:1 für Neufeld</t>
   </si>
 </sst>
 </file>
@@ -4524,6 +4533,9 @@
         <f>UPPER('Nach Mannschaften sortiert'!F11)</f>
         <v>NEUFELD</v>
       </c>
+      <c r="F11" s="108" t="s">
+        <v>225</v>
+      </c>
       <c r="G11" s="108" t="str">
         <f>'Nach Mannschaften sortiert'!H11</f>
         <v>Heim</v>
@@ -5009,6 +5021,9 @@
         <f>UPPER('Nach Mannschaften sortiert'!F24)</f>
         <v>NEUFELD</v>
       </c>
+      <c r="F24" s="108" t="s">
+        <v>224</v>
+      </c>
       <c r="G24" s="108" t="str">
         <f>'Nach Mannschaften sortiert'!H24</f>
         <v>Heim</v>
@@ -5684,6 +5699,9 @@
       <c r="E42" s="39" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F42)</f>
         <v>PARNDORF</v>
+      </c>
+      <c r="F42" s="108" t="s">
+        <v>223</v>
       </c>
       <c r="G42" s="108" t="str">
         <f>'Nach Mannschaften sortiert'!H42</f>

--- a/Terminefussball_2026_Frühjahr.xlsx
+++ b/Terminefussball_2026_Frühjahr.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DTB\asv-neufeld\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86332F2D-5D44-4D54-B6E4-C2256FB5F1DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97A06EE8-D07B-4D2F-9795-A289A59676DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="825" uniqueCount="226">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="826" uniqueCount="227">
   <si>
     <t>Mannschaft</t>
   </si>
@@ -335,9 +335,6 @@
     <t>SV BB1 Wolfau</t>
   </si>
   <si>
-    <t>Bernstein</t>
-  </si>
-  <si>
     <t>U15 LL Nord</t>
   </si>
   <si>
@@ -723,6 +720,12 @@
   </si>
   <si>
     <t>Endstand 4:1 für Neufeld</t>
+  </si>
+  <si>
+    <t>Endstand 6:1 für SPG SVO</t>
+  </si>
+  <si>
+    <t>Oberwart</t>
   </si>
 </sst>
 </file>
@@ -2518,7 +2521,7 @@
         <v>13</v>
       </c>
       <c r="G29" s="29" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H29" s="29" t="s">
         <v>12</v>
@@ -2570,7 +2573,7 @@
         <v>2</v>
       </c>
       <c r="G31" s="29" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="H31" s="29" t="s">
         <v>12</v>
@@ -2645,10 +2648,10 @@
         <v>0.72916666666666663</v>
       </c>
       <c r="F34" s="29" t="s">
-        <v>96</v>
+        <v>226</v>
       </c>
       <c r="G34" s="29" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H34" s="29" t="s">
         <v>11</v>
@@ -2697,10 +2700,10 @@
         <v>0.52083333333333337</v>
       </c>
       <c r="F36" s="29" t="s">
+        <v>122</v>
+      </c>
+      <c r="G36" s="29" t="s">
         <v>123</v>
-      </c>
-      <c r="G36" s="29" t="s">
-        <v>124</v>
       </c>
       <c r="H36" s="29" t="s">
         <v>11</v>
@@ -2752,7 +2755,7 @@
         <v>2</v>
       </c>
       <c r="G38" s="8" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="H38" s="8" t="s">
         <v>12</v>
@@ -2778,7 +2781,7 @@
         <v>13</v>
       </c>
       <c r="G39" s="8" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H39" s="8" t="s">
         <v>12</v>
@@ -2801,10 +2804,10 @@
         <v>0.77083333333333337</v>
       </c>
       <c r="F40" s="8" t="s">
+        <v>99</v>
+      </c>
+      <c r="G40" s="8" t="s">
         <v>100</v>
-      </c>
-      <c r="G40" s="8" t="s">
-        <v>101</v>
       </c>
       <c r="H40" s="8" t="s">
         <v>11</v>
@@ -2830,7 +2833,7 @@
         <v>2</v>
       </c>
       <c r="G41" s="8" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="H41" s="8" t="s">
         <v>12</v>
@@ -2853,10 +2856,10 @@
         <v>0.72916666666666663</v>
       </c>
       <c r="F42" s="8" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="G42" s="8" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="H42" s="8" t="s">
         <v>11</v>
@@ -2882,7 +2885,7 @@
         <v>6</v>
       </c>
       <c r="G43" s="8" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H43" s="8" t="s">
         <v>11</v>
@@ -2908,7 +2911,7 @@
         <v>13</v>
       </c>
       <c r="G44" s="8" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="H44" s="8" t="s">
         <v>12</v>
@@ -2931,10 +2934,10 @@
         <v>0.58333333333333337</v>
       </c>
       <c r="F45" s="8" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="G45" s="8" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="H45" s="8" t="s">
         <v>11</v>
@@ -2960,7 +2963,7 @@
         <v>2</v>
       </c>
       <c r="G46" s="20" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="H46" s="20" t="s">
         <v>12</v>
@@ -2987,7 +2990,7 @@
         <v>43</v>
       </c>
       <c r="G47" s="20" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="H47" s="20" t="s">
         <v>11</v>
@@ -3015,7 +3018,7 @@
         <v>30</v>
       </c>
       <c r="G48" s="20" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="H48" s="20" t="s">
         <v>11</v>
@@ -3071,7 +3074,7 @@
         <v>45</v>
       </c>
       <c r="G50" s="20" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="H50" s="20" t="s">
         <v>11</v>
@@ -3099,7 +3102,7 @@
         <v>2</v>
       </c>
       <c r="G51" s="20" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="H51" s="20" t="s">
         <v>12</v>
@@ -3127,7 +3130,7 @@
         <v>2</v>
       </c>
       <c r="G52" s="20" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="H52" s="20" t="s">
         <v>12</v>
@@ -3183,7 +3186,7 @@
         <v>2</v>
       </c>
       <c r="G54" s="10" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="H54" s="10" t="s">
         <v>12</v>
@@ -3209,7 +3212,7 @@
         <v>39</v>
       </c>
       <c r="G55" s="10" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="H55" s="10" t="s">
         <v>11</v>
@@ -3235,7 +3238,7 @@
         <v>2</v>
       </c>
       <c r="G56" s="10" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="H56" s="10" t="s">
         <v>12</v>
@@ -3287,7 +3290,7 @@
         <v>30</v>
       </c>
       <c r="G58" s="10" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="H58" s="10" t="s">
         <v>11</v>
@@ -3313,7 +3316,7 @@
         <v>2</v>
       </c>
       <c r="G59" s="10" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="H59" s="10" t="s">
         <v>12</v>
@@ -3339,7 +3342,7 @@
         <v>29</v>
       </c>
       <c r="G60" s="10" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="H60" s="10" t="s">
         <v>11</v>
@@ -3417,7 +3420,7 @@
         <v>2</v>
       </c>
       <c r="G63" s="27" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="H63" s="27" t="s">
         <v>12</v>
@@ -3469,7 +3472,7 @@
         <v>2</v>
       </c>
       <c r="G65" s="27" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="H65" s="27" t="s">
         <v>12</v>
@@ -3521,7 +3524,7 @@
         <v>17</v>
       </c>
       <c r="G67" s="27" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="H67" s="27" t="s">
         <v>11</v>
@@ -3570,10 +3573,10 @@
         <v>0.70833333333333337</v>
       </c>
       <c r="F69" s="27" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="G69" s="27" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="H69" s="27" t="s">
         <v>11</v>
@@ -3599,7 +3602,7 @@
         <v>2</v>
       </c>
       <c r="G70" s="12" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="H70" s="12" t="s">
         <v>12</v>
@@ -3625,7 +3628,7 @@
         <v>31</v>
       </c>
       <c r="G71" s="12" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="H71" s="12" t="s">
         <v>11</v>
@@ -3648,10 +3651,10 @@
         <v>0.60416666666666663</v>
       </c>
       <c r="F72" s="12" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="G72" s="12" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="H72" s="12" t="s">
         <v>11</v>
@@ -3677,7 +3680,7 @@
         <v>14</v>
       </c>
       <c r="G73" s="12" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="H73" s="12" t="s">
         <v>11</v>
@@ -3703,7 +3706,7 @@
         <v>26</v>
       </c>
       <c r="G74" s="12" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="H74" s="12" t="s">
         <v>11</v>
@@ -3729,7 +3732,7 @@
         <v>2</v>
       </c>
       <c r="G75" s="12" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="H75" s="33" t="s">
         <v>12</v>
@@ -3752,10 +3755,10 @@
         <v>0.39583333333333331</v>
       </c>
       <c r="F76" s="33" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="G76" s="12" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="H76" s="33" t="s">
         <v>11</v>
@@ -3778,10 +3781,10 @@
         <v>0.41666666666666669</v>
       </c>
       <c r="F77" s="33" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="G77" s="12" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="H77" s="33" t="s">
         <v>11</v>
@@ -3807,7 +3810,7 @@
         <v>14</v>
       </c>
       <c r="G78" s="12" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="H78" s="33" t="s">
         <v>11</v>
@@ -3833,7 +3836,7 @@
         <v>26</v>
       </c>
       <c r="G79" s="12" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="H79" s="33" t="s">
         <v>11</v>
@@ -3859,7 +3862,7 @@
         <v>2</v>
       </c>
       <c r="G80" s="12" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="H80" s="53" t="s">
         <v>12</v>
@@ -3885,7 +3888,7 @@
         <v>19</v>
       </c>
       <c r="G81" s="12" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="H81" s="53" t="s">
         <v>11</v>
@@ -3911,7 +3914,7 @@
         <v>45</v>
       </c>
       <c r="G82" s="12" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="H82" s="53" t="s">
         <v>11</v>
@@ -3937,7 +3940,7 @@
         <v>13</v>
       </c>
       <c r="G83" s="12" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="H83" s="53" t="s">
         <v>11</v>
@@ -3963,7 +3966,7 @@
         <v>26</v>
       </c>
       <c r="G84" s="12" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="H84" s="53" t="s">
         <v>11</v>
@@ -4055,7 +4058,7 @@
         <v>1</v>
       </c>
       <c r="C88" s="51" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="D88" s="84">
         <v>46186</v>
@@ -4067,7 +4070,7 @@
         <v>2</v>
       </c>
       <c r="G88" s="12" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="H88" s="52" t="s">
         <v>12</v>
@@ -4081,7 +4084,7 @@
         <v>2</v>
       </c>
       <c r="C89" s="51" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="D89" s="84">
         <v>46256</v>
@@ -4093,7 +4096,7 @@
         <v>2</v>
       </c>
       <c r="G89" s="12" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="H89" s="52" t="s">
         <v>12</v>
@@ -4132,37 +4135,37 @@
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1" s="108" t="s">
+        <v>132</v>
+      </c>
+      <c r="B1" s="105" t="s">
         <v>133</v>
       </c>
-      <c r="B1" s="105" t="s">
+      <c r="C1" s="39" t="s">
+        <v>138</v>
+      </c>
+      <c r="D1" s="39" t="s">
+        <v>137</v>
+      </c>
+      <c r="E1" s="39" t="s">
+        <v>136</v>
+      </c>
+      <c r="F1" s="108" t="s">
+        <v>140</v>
+      </c>
+      <c r="G1" s="108" t="s">
         <v>134</v>
       </c>
-      <c r="C1" s="39" t="s">
+      <c r="H1" t="s">
+        <v>135</v>
+      </c>
+      <c r="I1" t="s">
         <v>139</v>
       </c>
-      <c r="D1" s="39" t="s">
-        <v>138</v>
-      </c>
-      <c r="E1" s="39" t="s">
-        <v>137</v>
-      </c>
-      <c r="F1" s="108" t="s">
-        <v>141</v>
-      </c>
-      <c r="G1" s="108" t="s">
-        <v>135</v>
-      </c>
-      <c r="H1" t="s">
-        <v>136</v>
-      </c>
-      <c r="I1" t="s">
-        <v>140</v>
-      </c>
       <c r="J1" s="108" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="K1" s="108" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.3">
@@ -4183,7 +4186,7 @@
         <v>RUST</v>
       </c>
       <c r="F2" s="108" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="G2" s="108" t="str">
         <f>'Nach Mannschaften sortiert'!H2</f>
@@ -4198,10 +4201,10 @@
         <v>KM</v>
       </c>
       <c r="J2" s="108" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="K2" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.3">
@@ -4222,7 +4225,7 @@
         <v>NEUFELD</v>
       </c>
       <c r="F3" s="108" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="G3" s="108" t="str">
         <f>'Nach Mannschaften sortiert'!H3</f>
@@ -4237,10 +4240,10 @@
         <v>KM</v>
       </c>
       <c r="J3" s="108" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="K3" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.3">
@@ -4261,7 +4264,7 @@
         <v>GATTENDORF</v>
       </c>
       <c r="F4" s="108" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="G4" s="108" t="str">
         <f>'Nach Mannschaften sortiert'!H4</f>
@@ -4276,10 +4279,10 @@
         <v>KM</v>
       </c>
       <c r="J4" s="108" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="K4" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.3">
@@ -4300,7 +4303,7 @@
         <v>NEUFELD</v>
       </c>
       <c r="F5" s="108" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="G5" s="108" t="str">
         <f>'Nach Mannschaften sortiert'!H5</f>
@@ -4315,10 +4318,10 @@
         <v>KM</v>
       </c>
       <c r="J5" s="108" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="K5" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.3">
@@ -4339,7 +4342,7 @@
         <v>ANDAU</v>
       </c>
       <c r="F6" s="108" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="G6" s="108" t="str">
         <f>'Nach Mannschaften sortiert'!H6</f>
@@ -4354,10 +4357,10 @@
         <v>KM</v>
       </c>
       <c r="J6" s="108" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="K6" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.3">
@@ -4378,7 +4381,7 @@
         <v>NEUFELD</v>
       </c>
       <c r="F7" s="108" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="G7" s="108" t="str">
         <f>'Nach Mannschaften sortiert'!H7</f>
@@ -4393,10 +4396,10 @@
         <v>KM</v>
       </c>
       <c r="J7" s="108" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="K7" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.3">
@@ -4417,7 +4420,7 @@
         <v>DEUTSCH JAHRNDORF</v>
       </c>
       <c r="F8" s="108" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="G8" s="108" t="str">
         <f>'Nach Mannschaften sortiert'!H8</f>
@@ -4432,10 +4435,10 @@
         <v>KM</v>
       </c>
       <c r="J8" s="108" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="K8" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.3">
@@ -4456,7 +4459,7 @@
         <v>NEUFELD</v>
       </c>
       <c r="F9" s="108" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="G9" s="108" t="str">
         <f>'Nach Mannschaften sortiert'!H9</f>
@@ -4471,10 +4474,10 @@
         <v>KM</v>
       </c>
       <c r="J9" s="108" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="K9" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.3">
@@ -4495,7 +4498,7 @@
         <v>GOLS</v>
       </c>
       <c r="F10" s="108" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="G10" s="108" t="str">
         <f>'Nach Mannschaften sortiert'!H10</f>
@@ -4510,10 +4513,10 @@
         <v>KM</v>
       </c>
       <c r="J10" s="108" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="K10" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.3">
@@ -4534,7 +4537,7 @@
         <v>NEUFELD</v>
       </c>
       <c r="F11" s="108" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="G11" s="108" t="str">
         <f>'Nach Mannschaften sortiert'!H11</f>
@@ -4549,10 +4552,10 @@
         <v>KM</v>
       </c>
       <c r="J11" s="108" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="K11" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.3">
@@ -4585,10 +4588,10 @@
         <v>KM</v>
       </c>
       <c r="J12" s="108" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="K12" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.3">
@@ -4621,10 +4624,10 @@
         <v>KM</v>
       </c>
       <c r="J13" s="108" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="K13" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.3">
@@ -4657,10 +4660,10 @@
         <v>KM</v>
       </c>
       <c r="J14" s="108" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="K14" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.3">
@@ -4680,7 +4683,7 @@
         <v>RUST</v>
       </c>
       <c r="F15" s="108" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="G15" s="108" t="str">
         <f>'Nach Mannschaften sortiert'!H15</f>
@@ -4695,10 +4698,10 @@
         <v>U23</v>
       </c>
       <c r="J15" s="108" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="K15" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.3">
@@ -4718,7 +4721,7 @@
         <v>NEUFELD</v>
       </c>
       <c r="F16" s="108" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="G16" s="108" t="str">
         <f>'Nach Mannschaften sortiert'!H16</f>
@@ -4733,10 +4736,10 @@
         <v>U23</v>
       </c>
       <c r="J16" s="108" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="K16" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="17" spans="2:11" x14ac:dyDescent="0.3">
@@ -4756,7 +4759,7 @@
         <v>GATTENDORF</v>
       </c>
       <c r="F17" s="108" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="G17" s="108" t="str">
         <f>'Nach Mannschaften sortiert'!H17</f>
@@ -4771,10 +4774,10 @@
         <v>U23</v>
       </c>
       <c r="J17" s="108" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="K17" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="18" spans="2:11" x14ac:dyDescent="0.3">
@@ -4794,7 +4797,7 @@
         <v>NEUFELD</v>
       </c>
       <c r="F18" s="108" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="G18" s="108" t="str">
         <f>'Nach Mannschaften sortiert'!H18</f>
@@ -4809,10 +4812,10 @@
         <v>U23</v>
       </c>
       <c r="J18" s="108" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="K18" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="19" spans="2:11" x14ac:dyDescent="0.3">
@@ -4832,7 +4835,7 @@
         <v>ANDAU</v>
       </c>
       <c r="F19" s="108" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="G19" s="108" t="str">
         <f>'Nach Mannschaften sortiert'!H19</f>
@@ -4847,10 +4850,10 @@
         <v>U23</v>
       </c>
       <c r="J19" s="108" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="K19" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="20" spans="2:11" x14ac:dyDescent="0.3">
@@ -4870,7 +4873,7 @@
         <v>NEUFELD</v>
       </c>
       <c r="F20" s="108" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="G20" s="108" t="str">
         <f>'Nach Mannschaften sortiert'!H20</f>
@@ -4885,10 +4888,10 @@
         <v>U23</v>
       </c>
       <c r="J20" s="108" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="K20" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="21" spans="2:11" x14ac:dyDescent="0.3">
@@ -4908,7 +4911,7 @@
         <v>DEUTSCH JAHRNDORF</v>
       </c>
       <c r="F21" s="108" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="G21" s="108" t="str">
         <f>'Nach Mannschaften sortiert'!H21</f>
@@ -4923,10 +4926,10 @@
         <v>U23</v>
       </c>
       <c r="J21" s="108" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="K21" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="22" spans="2:11" x14ac:dyDescent="0.3">
@@ -4946,7 +4949,7 @@
         <v>NEUFELD</v>
       </c>
       <c r="F22" s="108" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="G22" s="108" t="str">
         <f>'Nach Mannschaften sortiert'!H22</f>
@@ -4961,10 +4964,10 @@
         <v>U23</v>
       </c>
       <c r="J22" s="108" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="K22" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="23" spans="2:11" x14ac:dyDescent="0.3">
@@ -4984,7 +4987,7 @@
         <v>GOLS</v>
       </c>
       <c r="F23" s="108" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="G23" s="108" t="str">
         <f>'Nach Mannschaften sortiert'!H23</f>
@@ -4999,10 +5002,10 @@
         <v>U23</v>
       </c>
       <c r="J23" s="108" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="K23" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="24" spans="2:11" x14ac:dyDescent="0.3">
@@ -5022,7 +5025,7 @@
         <v>NEUFELD</v>
       </c>
       <c r="F24" s="108" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="G24" s="108" t="str">
         <f>'Nach Mannschaften sortiert'!H24</f>
@@ -5037,10 +5040,10 @@
         <v>U23</v>
       </c>
       <c r="J24" s="108" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="K24" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="25" spans="2:11" x14ac:dyDescent="0.3">
@@ -5072,10 +5075,10 @@
         <v>U23</v>
       </c>
       <c r="J25" s="108" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="K25" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="26" spans="2:11" x14ac:dyDescent="0.3">
@@ -5107,10 +5110,10 @@
         <v>U23</v>
       </c>
       <c r="J26" s="108" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="K26" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="27" spans="2:11" x14ac:dyDescent="0.3">
@@ -5142,10 +5145,10 @@
         <v>U23</v>
       </c>
       <c r="J27" s="108" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="K27" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="28" spans="2:11" x14ac:dyDescent="0.3">
@@ -5164,7 +5167,7 @@
         <v>SV LEITHAPRODERSDORF</v>
       </c>
       <c r="F28" s="108" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="G28" s="108" t="str">
         <f>'Nach Mannschaften sortiert'!H28</f>
@@ -5179,10 +5182,10 @@
         <v>U16</v>
       </c>
       <c r="J28" s="108" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="K28" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="29" spans="2:11" x14ac:dyDescent="0.3">
@@ -5203,7 +5206,7 @@
         <v>WIMPASSING</v>
       </c>
       <c r="F29" s="108" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="G29" s="108" t="str">
         <f>'Nach Mannschaften sortiert'!H29</f>
@@ -5218,10 +5221,10 @@
         <v>U16</v>
       </c>
       <c r="J29" s="108" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="K29" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="30" spans="2:11" x14ac:dyDescent="0.3">
@@ -5242,7 +5245,7 @@
         <v>WOLFAU</v>
       </c>
       <c r="F30" s="108" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="G30" s="108" t="str">
         <f>'Nach Mannschaften sortiert'!H30</f>
@@ -5257,10 +5260,10 @@
         <v>U16</v>
       </c>
       <c r="J30" s="108" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="K30" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="31" spans="2:11" x14ac:dyDescent="0.3">
@@ -5281,7 +5284,7 @@
         <v>NEUFELD</v>
       </c>
       <c r="F31" s="108" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="G31" s="108" t="str">
         <f>'Nach Mannschaften sortiert'!H31</f>
@@ -5296,10 +5299,10 @@
         <v>U16</v>
       </c>
       <c r="J31" s="108" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="K31" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="32" spans="2:11" x14ac:dyDescent="0.3">
@@ -5320,7 +5323,7 @@
         <v>ST. GEORGEN</v>
       </c>
       <c r="F32" s="108" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="G32" s="108" t="str">
         <f>'Nach Mannschaften sortiert'!H32</f>
@@ -5335,10 +5338,10 @@
         <v>U16</v>
       </c>
       <c r="J32" s="108" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="K32" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="33" spans="2:11" x14ac:dyDescent="0.3">
@@ -5359,7 +5362,7 @@
         <v>WIMPASSING</v>
       </c>
       <c r="F33" s="108" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="G33" s="108" t="str">
         <f>'Nach Mannschaften sortiert'!H33</f>
@@ -5374,10 +5377,10 @@
         <v>U16</v>
       </c>
       <c r="J33" s="108" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="K33" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="34" spans="2:11" x14ac:dyDescent="0.3">
@@ -5395,7 +5398,10 @@
       </c>
       <c r="E34" s="39" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F34)</f>
-        <v>BERNSTEIN</v>
+        <v>OBERWART</v>
+      </c>
+      <c r="F34" s="108" t="s">
+        <v>225</v>
       </c>
       <c r="G34" s="108" t="str">
         <f>'Nach Mannschaften sortiert'!H34</f>
@@ -5410,10 +5416,10 @@
         <v>U16</v>
       </c>
       <c r="J34" s="108" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="K34" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="35" spans="2:11" x14ac:dyDescent="0.3">
@@ -5434,7 +5440,7 @@
         <v>WIMPASSING</v>
       </c>
       <c r="F35" s="108" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="G35" s="108" t="str">
         <f>'Nach Mannschaften sortiert'!H35</f>
@@ -5449,10 +5455,10 @@
         <v>U16</v>
       </c>
       <c r="J35" s="108" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="K35" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="36" spans="2:11" x14ac:dyDescent="0.3">
@@ -5485,10 +5491,10 @@
         <v>U16</v>
       </c>
       <c r="J36" s="108" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="K36" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="37" spans="2:11" x14ac:dyDescent="0.3">
@@ -5521,10 +5527,10 @@
         <v>U16</v>
       </c>
       <c r="J37" s="108" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="K37" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="38" spans="2:11" x14ac:dyDescent="0.3">
@@ -5545,7 +5551,7 @@
         <v>NEUFELD</v>
       </c>
       <c r="F38" s="108" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="G38" s="108" t="str">
         <f>'Nach Mannschaften sortiert'!H38</f>
@@ -5560,10 +5566,10 @@
         <v>U15</v>
       </c>
       <c r="J38" s="108" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="K38" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="39" spans="2:11" x14ac:dyDescent="0.3">
@@ -5584,7 +5590,7 @@
         <v>WIMPASSING</v>
       </c>
       <c r="F39" s="108" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="G39" s="108" t="str">
         <f>'Nach Mannschaften sortiert'!H39</f>
@@ -5599,10 +5605,10 @@
         <v>U15</v>
       </c>
       <c r="J39" s="108" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="K39" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="40" spans="2:11" x14ac:dyDescent="0.3">
@@ -5623,7 +5629,7 @@
         <v>NEUSIEDL</v>
       </c>
       <c r="F40" s="108" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="G40" s="108" t="str">
         <f>'Nach Mannschaften sortiert'!H40</f>
@@ -5638,10 +5644,10 @@
         <v>U15</v>
       </c>
       <c r="J40" s="108" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="K40" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="41" spans="2:11" x14ac:dyDescent="0.3">
@@ -5662,7 +5668,7 @@
         <v>NEUFELD</v>
       </c>
       <c r="F41" s="108" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="G41" s="108" t="str">
         <f>'Nach Mannschaften sortiert'!H41</f>
@@ -5677,10 +5683,10 @@
         <v>U15</v>
       </c>
       <c r="J41" s="108" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="K41" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="42" spans="2:11" x14ac:dyDescent="0.3">
@@ -5701,7 +5707,7 @@
         <v>PARNDORF</v>
       </c>
       <c r="F42" s="108" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="G42" s="108" t="str">
         <f>'Nach Mannschaften sortiert'!H42</f>
@@ -5716,10 +5722,10 @@
         <v>U15</v>
       </c>
       <c r="J42" s="108" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="K42" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="43" spans="2:11" x14ac:dyDescent="0.3">
@@ -5752,10 +5758,10 @@
         <v>U15</v>
       </c>
       <c r="J43" s="108" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="K43" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="44" spans="2:11" x14ac:dyDescent="0.3">
@@ -5788,10 +5794,10 @@
         <v>U15</v>
       </c>
       <c r="J44" s="108" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="K44" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="45" spans="2:11" x14ac:dyDescent="0.3">
@@ -5824,10 +5830,10 @@
         <v>U15</v>
       </c>
       <c r="J45" s="108" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="K45" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="46" spans="2:11" x14ac:dyDescent="0.3">
@@ -5848,7 +5854,7 @@
         <v>NEUFELD</v>
       </c>
       <c r="F46" s="108" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="G46" s="108" t="str">
         <f>'Nach Mannschaften sortiert'!H46</f>
@@ -5863,10 +5869,10 @@
         <v>U14</v>
       </c>
       <c r="J46" s="108" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="K46" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="47" spans="2:11" x14ac:dyDescent="0.3">
@@ -5887,7 +5893,7 @@
         <v>PAMA</v>
       </c>
       <c r="F47" s="108" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="G47" s="108" t="str">
         <f>'Nach Mannschaften sortiert'!H47</f>
@@ -5902,10 +5908,10 @@
         <v>U14</v>
       </c>
       <c r="J47" s="108" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="K47" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="48" spans="2:11" x14ac:dyDescent="0.3">
@@ -5926,7 +5932,7 @@
         <v>KITTSEE</v>
       </c>
       <c r="F48" s="108" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="G48" s="108" t="str">
         <f>'Nach Mannschaften sortiert'!H48</f>
@@ -5941,10 +5947,10 @@
         <v>U14</v>
       </c>
       <c r="J48" s="108" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="K48" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="49" spans="2:11" x14ac:dyDescent="0.3">
@@ -5965,7 +5971,7 @@
         <v>NEUFELD</v>
       </c>
       <c r="F49" s="108" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="G49" s="108" t="str">
         <f>'Nach Mannschaften sortiert'!H49</f>
@@ -5980,10 +5986,10 @@
         <v>U14</v>
       </c>
       <c r="J49" s="108" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="K49" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="50" spans="2:11" x14ac:dyDescent="0.3">
@@ -6003,7 +6009,7 @@
         <v>WULKAPRODERSDORF</v>
       </c>
       <c r="F50" s="108" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="G50" s="108" t="str">
         <f>'Nach Mannschaften sortiert'!H50</f>
@@ -6018,10 +6024,10 @@
         <v>U14</v>
       </c>
       <c r="J50" s="108" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="K50" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="51" spans="2:11" x14ac:dyDescent="0.3">
@@ -6054,10 +6060,10 @@
         <v>U14</v>
       </c>
       <c r="J51" s="108" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="K51" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="52" spans="2:11" x14ac:dyDescent="0.3">
@@ -6090,10 +6096,10 @@
         <v>U14</v>
       </c>
       <c r="J52" s="108" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="K52" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="53" spans="2:11" x14ac:dyDescent="0.3">
@@ -6126,10 +6132,10 @@
         <v>U14</v>
       </c>
       <c r="J53" s="108" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="K53" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="54" spans="2:11" x14ac:dyDescent="0.3">
@@ -6162,10 +6168,10 @@
         <v>U13</v>
       </c>
       <c r="J54" s="108" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="K54" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="55" spans="2:11" x14ac:dyDescent="0.3">
@@ -6186,7 +6192,7 @@
         <v>RUST</v>
       </c>
       <c r="F55" s="108" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="G55" s="108" t="str">
         <f>'Nach Mannschaften sortiert'!H55</f>
@@ -6201,10 +6207,10 @@
         <v>U13</v>
       </c>
       <c r="J55" s="108" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="K55" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="56" spans="2:11" x14ac:dyDescent="0.3">
@@ -6225,7 +6231,7 @@
         <v>NEUFELD</v>
       </c>
       <c r="F56" s="108" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="G56" s="108" t="str">
         <f>'Nach Mannschaften sortiert'!H56</f>
@@ -6240,10 +6246,10 @@
         <v>U13</v>
       </c>
       <c r="J56" s="108" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="K56" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="57" spans="2:11" x14ac:dyDescent="0.3">
@@ -6264,7 +6270,7 @@
         <v>LEITHAPRODERSDORF</v>
       </c>
       <c r="F57" s="108" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="G57" s="108" t="str">
         <f>'Nach Mannschaften sortiert'!H57</f>
@@ -6279,10 +6285,10 @@
         <v>U13</v>
       </c>
       <c r="J57" s="108" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="K57" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="58" spans="2:11" x14ac:dyDescent="0.3">
@@ -6303,7 +6309,7 @@
         <v>KITTSEE</v>
       </c>
       <c r="F58" s="108" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="G58" s="108" t="str">
         <f>'Nach Mannschaften sortiert'!H58</f>
@@ -6318,10 +6324,10 @@
         <v>U13</v>
       </c>
       <c r="J58" s="108" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="K58" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="59" spans="2:11" x14ac:dyDescent="0.3">
@@ -6354,10 +6360,10 @@
         <v>U13</v>
       </c>
       <c r="J59" s="108" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="K59" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="60" spans="2:11" x14ac:dyDescent="0.3">
@@ -6390,10 +6396,10 @@
         <v>U13</v>
       </c>
       <c r="J60" s="108" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="K60" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="61" spans="2:11" x14ac:dyDescent="0.3">
@@ -6426,10 +6432,10 @@
         <v>U13</v>
       </c>
       <c r="J61" s="108" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="K61" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="62" spans="2:11" x14ac:dyDescent="0.3">
@@ -6449,7 +6455,7 @@
         <v>NEUFELD</v>
       </c>
       <c r="F62" s="108" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="G62" s="108" t="str">
         <f>'Nach Mannschaften sortiert'!H62</f>
@@ -6464,10 +6470,10 @@
         <v>U11</v>
       </c>
       <c r="J62" s="108" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="K62" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="63" spans="2:11" x14ac:dyDescent="0.3">
@@ -6488,7 +6494,7 @@
         <v>NEUFELD</v>
       </c>
       <c r="F63" s="108" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="G63" s="108" t="str">
         <f>'Nach Mannschaften sortiert'!H63</f>
@@ -6503,10 +6509,10 @@
         <v>U11</v>
       </c>
       <c r="J63" s="108" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="K63" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="64" spans="2:11" x14ac:dyDescent="0.3">
@@ -6527,7 +6533,7 @@
         <v>KLINGENBACH</v>
       </c>
       <c r="F64" s="108" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="G64" s="108" t="str">
         <f>'Nach Mannschaften sortiert'!H64</f>
@@ -6542,10 +6548,10 @@
         <v>U11</v>
       </c>
       <c r="J64" s="108" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="K64" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="65" spans="2:11" x14ac:dyDescent="0.3">
@@ -6566,7 +6572,7 @@
         <v>NEUFELD</v>
       </c>
       <c r="F65" s="108" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="G65" s="108" t="str">
         <f>'Nach Mannschaften sortiert'!H65</f>
@@ -6581,10 +6587,10 @@
         <v>U11</v>
       </c>
       <c r="J65" s="108" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="K65" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="66" spans="2:11" x14ac:dyDescent="0.3">
@@ -6603,7 +6609,7 @@
         <v>NEUFELD</v>
       </c>
       <c r="F66" s="108" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="G66" s="108" t="str">
         <f>'Nach Mannschaften sortiert'!H66</f>
@@ -6618,10 +6624,10 @@
         <v>U11</v>
       </c>
       <c r="J66" s="108" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="K66" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="67" spans="2:11" x14ac:dyDescent="0.3">
@@ -6654,10 +6660,10 @@
         <v>U11</v>
       </c>
       <c r="J67" s="108" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="K67" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="68" spans="2:11" x14ac:dyDescent="0.3">
@@ -6690,10 +6696,10 @@
         <v>U11</v>
       </c>
       <c r="J68" s="108" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="K68" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="69" spans="2:11" x14ac:dyDescent="0.3">
@@ -6726,10 +6732,10 @@
         <v>U11</v>
       </c>
       <c r="J69" s="108" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="K69" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="70" spans="2:11" x14ac:dyDescent="0.3">
@@ -6762,10 +6768,10 @@
         <v>U9</v>
       </c>
       <c r="J70" s="108" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="K70" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="71" spans="2:11" x14ac:dyDescent="0.3">
@@ -6798,10 +6804,10 @@
         <v>U9</v>
       </c>
       <c r="J71" s="108" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="K71" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="72" spans="2:11" x14ac:dyDescent="0.3">
@@ -6834,10 +6840,10 @@
         <v>U9</v>
       </c>
       <c r="J72" s="108" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="K72" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="73" spans="2:11" x14ac:dyDescent="0.3">
@@ -6870,10 +6876,10 @@
         <v>U9</v>
       </c>
       <c r="J73" s="108" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="K73" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="74" spans="2:11" x14ac:dyDescent="0.3">
@@ -6906,10 +6912,10 @@
         <v>U9</v>
       </c>
       <c r="J74" s="108" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="K74" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="75" spans="2:11" x14ac:dyDescent="0.3">
@@ -6942,10 +6948,10 @@
         <v>U8</v>
       </c>
       <c r="J75" s="108" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="K75" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="76" spans="2:11" x14ac:dyDescent="0.3">
@@ -6978,10 +6984,10 @@
         <v>U8</v>
       </c>
       <c r="J76" s="108" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="K76" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="77" spans="2:11" x14ac:dyDescent="0.3">
@@ -7014,10 +7020,10 @@
         <v>U8</v>
       </c>
       <c r="J77" s="108" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="K77" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="78" spans="2:11" x14ac:dyDescent="0.3">
@@ -7050,10 +7056,10 @@
         <v>U8</v>
       </c>
       <c r="J78" s="108" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="K78" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="79" spans="2:11" x14ac:dyDescent="0.3">
@@ -7086,10 +7092,10 @@
         <v>U8</v>
       </c>
       <c r="J79" s="108" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="K79" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="80" spans="2:11" x14ac:dyDescent="0.3">
@@ -7122,10 +7128,10 @@
         <v>U7</v>
       </c>
       <c r="J80" s="108" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="K80" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="81" spans="2:11" x14ac:dyDescent="0.3">
@@ -7158,10 +7164,10 @@
         <v>U7</v>
       </c>
       <c r="J81" s="108" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="K81" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="82" spans="2:11" x14ac:dyDescent="0.3">
@@ -7194,10 +7200,10 @@
         <v>U7</v>
       </c>
       <c r="J82" s="108" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="K82" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="83" spans="2:11" x14ac:dyDescent="0.3">
@@ -7230,10 +7236,10 @@
         <v>U7</v>
       </c>
       <c r="J83" s="108" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="K83" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="84" spans="2:11" x14ac:dyDescent="0.3">
@@ -7266,10 +7272,10 @@
         <v>U7</v>
       </c>
       <c r="J84" s="108" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="K84" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="85" spans="2:11" x14ac:dyDescent="0.3">
@@ -7301,7 +7307,7 @@
         <v>Camp</v>
       </c>
       <c r="J85" s="108" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="K85" t="s">
         <v>49</v>
@@ -7336,7 +7342,7 @@
         <v>Camp</v>
       </c>
       <c r="J86" s="108" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="K86" t="s">
         <v>49</v>
@@ -7371,7 +7377,7 @@
         <v>Camp</v>
       </c>
       <c r="J87" s="108" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="K87" t="s">
         <v>49</v>
@@ -7406,10 +7412,10 @@
         <v>GGG</v>
       </c>
       <c r="J88" s="108" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="K88" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="89" spans="2:11" x14ac:dyDescent="0.3">
@@ -7441,10 +7447,10 @@
         <v>GGG</v>
       </c>
       <c r="J89" s="108" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="K89" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="90" spans="2:11" x14ac:dyDescent="0.3">
@@ -7459,25 +7465,25 @@
         <v>0.51388888888888895</v>
       </c>
       <c r="E90" s="39" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="F90" s="108" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="G90" s="108" t="s">
         <v>12</v>
       </c>
       <c r="H90" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="I90" t="s">
         <v>18</v>
       </c>
       <c r="J90" s="108" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="K90" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="91" spans="2:11" x14ac:dyDescent="0.3">
@@ -7491,10 +7497,10 @@
         <v>0.75</v>
       </c>
       <c r="E91" s="39" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="F91" s="108" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="G91" s="108" t="s">
         <v>12</v>
@@ -7506,10 +7512,10 @@
         <v>27</v>
       </c>
       <c r="J91" s="108" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="K91" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
   </sheetData>
@@ -7529,19 +7535,19 @@
   <sheetData>
     <row r="1" spans="1:3" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="110" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B1" s="110"/>
       <c r="C1" s="110" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="110" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B2" s="110" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C2" s="110" t="str">
         <f>"https://dtb-asv.github.io/asv-neufeld/"&amp;B2</f>
@@ -7550,10 +7556,10 @@
     </row>
     <row r="3" spans="1:3" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="110" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B3" s="110" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C3" s="110" t="str">
         <f t="shared" ref="C3:C18" si="0">"https://dtb-asv.github.io/asv-neufeld/"&amp;B3</f>
@@ -7562,10 +7568,10 @@
     </row>
     <row r="4" spans="1:3" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="110" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B4" s="110" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C4" s="110" t="str">
         <f t="shared" si="0"/>
@@ -7574,10 +7580,10 @@
     </row>
     <row r="5" spans="1:3" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="110" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B5" s="110" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C5" s="110" t="str">
         <f t="shared" si="0"/>
@@ -7586,10 +7592,10 @@
     </row>
     <row r="6" spans="1:3" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="110" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B6" s="110" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C6" s="110" t="str">
         <f t="shared" si="0"/>
@@ -7598,10 +7604,10 @@
     </row>
     <row r="7" spans="1:3" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="110" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B7" s="110" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C7" s="110" t="str">
         <f t="shared" si="0"/>
@@ -7610,10 +7616,10 @@
     </row>
     <row r="8" spans="1:3" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="110" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B8" s="110" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C8" s="110" t="str">
         <f t="shared" si="0"/>
@@ -7622,10 +7628,10 @@
     </row>
     <row r="9" spans="1:3" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="110" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B9" s="110" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C9" s="110" t="str">
         <f t="shared" si="0"/>
@@ -7634,10 +7640,10 @@
     </row>
     <row r="10" spans="1:3" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="110" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B10" s="110" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C10" s="110" t="str">
         <f t="shared" si="0"/>
@@ -7646,10 +7652,10 @@
     </row>
     <row r="11" spans="1:3" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="110" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B11" s="110" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C11" s="110" t="str">
         <f t="shared" si="0"/>
@@ -7658,10 +7664,10 @@
     </row>
     <row r="12" spans="1:3" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="110" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B12" s="110" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C12" s="110" t="str">
         <f t="shared" si="0"/>
@@ -7670,10 +7676,10 @@
     </row>
     <row r="13" spans="1:3" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="110" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B13" s="110" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="C13" s="110" t="str">
         <f t="shared" si="0"/>
@@ -7682,10 +7688,10 @@
     </row>
     <row r="14" spans="1:3" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="110" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B14" s="110" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C14" s="110" t="str">
         <f t="shared" si="0"/>
@@ -7694,10 +7700,10 @@
     </row>
     <row r="15" spans="1:3" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="110" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B15" s="110" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C15" s="110" t="str">
         <f t="shared" si="0"/>
@@ -7706,10 +7712,10 @@
     </row>
     <row r="16" spans="1:3" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="110" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B16" s="110" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C16" s="110" t="str">
         <f t="shared" si="0"/>
@@ -7718,7 +7724,7 @@
     </row>
     <row r="17" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B17" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C17" t="str">
         <f t="shared" si="0"/>
@@ -7727,7 +7733,7 @@
     </row>
     <row r="18" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B18" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C18" t="str">
         <f t="shared" si="0"/>
@@ -7810,7 +7816,7 @@
       <c r="C3" s="85"/>
       <c r="D3" s="85"/>
       <c r="E3" s="86" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="F3" s="85"/>
       <c r="G3" s="85"/>
@@ -7823,15 +7829,15 @@
         <v>87</v>
       </c>
       <c r="B4" s="46" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C4" s="85"/>
       <c r="D4" s="88" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="E4" s="85"/>
       <c r="F4" s="88" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="G4" s="85"/>
       <c r="H4" s="87"/>
@@ -7863,7 +7869,7 @@
         <v>36</v>
       </c>
       <c r="B6" s="46" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C6" s="89"/>
       <c r="D6" s="90" t="s">
@@ -7955,14 +7961,14 @@
       </c>
       <c r="C10" s="85"/>
       <c r="D10" s="91" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E10" s="85"/>
       <c r="F10" s="90" t="s">
+        <v>130</v>
+      </c>
+      <c r="G10" s="90" t="s">
         <v>131</v>
-      </c>
-      <c r="G10" s="90" t="s">
-        <v>132</v>
       </c>
       <c r="H10" s="87"/>
       <c r="I10" s="115"/>
@@ -7993,7 +7999,7 @@
         <v>72</v>
       </c>
       <c r="B12" s="48" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C12" s="97" t="s">
         <v>73</v>
@@ -8013,7 +8019,7 @@
         <v>38</v>
       </c>
       <c r="B13" s="49" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C13" s="100" t="s">
         <v>73</v>
@@ -8825,7 +8831,7 @@
       </c>
       <c r="F21" s="2" t="str">
         <f>'Nach Mannschaften sortiert'!F34</f>
-        <v>Bernstein</v>
+        <v>Oberwart</v>
       </c>
       <c r="G21" s="2" t="str">
         <f>'Nach Mannschaften sortiert'!G34</f>
@@ -11058,7 +11064,7 @@
         <v>8</v>
       </c>
       <c r="C1" s="76" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D1" s="74" t="s">
         <v>1</v>
@@ -11099,7 +11105,7 @@
         <v>2</v>
       </c>
       <c r="E2" s="77" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="F2" s="77" t="s">
         <v>27</v>
@@ -11181,7 +11187,7 @@
         <v>2</v>
       </c>
       <c r="E4" s="77" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="F4" s="77" t="s">
         <v>62</v>
@@ -11251,7 +11257,7 @@
     </row>
     <row r="6" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A6" s="77" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B6" s="78">
         <v>46096</v>
@@ -11263,7 +11269,7 @@
         <v>2</v>
       </c>
       <c r="E6" s="77" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="F6" s="77" t="s">
         <v>34</v>
@@ -11345,7 +11351,7 @@
         <v>2</v>
       </c>
       <c r="E8" s="77" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="F8" s="77" t="s">
         <v>24</v>
@@ -11854,7 +11860,7 @@
       <c r="C20" s="72"/>
       <c r="D20" t="str">
         <f>Heimspiele!F21</f>
-        <v>Bernstein</v>
+        <v>Oberwart</v>
       </c>
       <c r="E20" t="str">
         <f>Heimspiele!G21</f>
@@ -11997,7 +12003,7 @@
         <v>Großfeld</v>
       </c>
       <c r="H23" s="77" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="I23" s="77">
         <v>3</v>
@@ -12082,7 +12088,7 @@
         <v>Großfeld</v>
       </c>
       <c r="H25" s="77" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="I25" s="77">
         <v>3</v>
@@ -12209,7 +12215,7 @@
         <v>Großfeld</v>
       </c>
       <c r="H28" s="77" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="I28" s="77">
         <v>3</v>
@@ -14708,7 +14714,7 @@
         <v>viele Gegner</v>
       </c>
       <c r="F86" s="77" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="G86" s="77" t="str">
         <f t="shared" si="8"/>
@@ -14753,7 +14759,7 @@
         <v>viele Gegner</v>
       </c>
       <c r="F87" s="77" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="G87" s="77" t="str">
         <f t="shared" si="8"/>

--- a/Terminefussball_2026_Frühjahr.xlsx
+++ b/Terminefussball_2026_Frühjahr.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DTB\asv-neufeld\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97A06EE8-D07B-4D2F-9795-A289A59676DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7296229-E290-42CE-ABDC-D7A6BCA8F022}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="826" uniqueCount="227">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="827" uniqueCount="227">
   <si>
     <t>Mannschaft</t>
   </si>
@@ -710,9 +710,6 @@
     <t>Endstand 4:3 für Neufeld</t>
   </si>
   <si>
-    <t>abgesagt</t>
-  </si>
-  <si>
     <t>Endstand 4:0 für Parndorf</t>
   </si>
   <si>
@@ -726,6 +723,9 @@
   </si>
   <si>
     <t>Oberwart</t>
+  </si>
+  <si>
+    <t>Endstand 4:0 für Kittsee</t>
   </si>
 </sst>
 </file>
@@ -2648,7 +2648,7 @@
         <v>0.72916666666666663</v>
       </c>
       <c r="F34" s="29" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="G34" s="29" t="s">
         <v>124</v>
@@ -3093,10 +3093,10 @@
         <v>35</v>
       </c>
       <c r="D51" s="21">
-        <v>46158</v>
+        <v>46173</v>
       </c>
       <c r="E51" s="22">
-        <v>0.625</v>
+        <v>0.58333333333333337</v>
       </c>
       <c r="F51" s="20" t="s">
         <v>2</v>
@@ -3152,7 +3152,7 @@
         <v>46171</v>
       </c>
       <c r="E53" s="22">
-        <v>0.79166666666666663</v>
+        <v>0.8125</v>
       </c>
       <c r="F53" s="20" t="s">
         <v>14</v>
@@ -3515,10 +3515,10 @@
         <v>61</v>
       </c>
       <c r="D67" s="32">
-        <v>46159</v>
+        <v>46169</v>
       </c>
       <c r="E67" s="28">
-        <v>0.58333333333333337</v>
+        <v>0.75</v>
       </c>
       <c r="F67" s="27" t="s">
         <v>17</v>
@@ -4537,7 +4537,7 @@
         <v>NEUFELD</v>
       </c>
       <c r="F11" s="108" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="G11" s="108" t="str">
         <f>'Nach Mannschaften sortiert'!H11</f>
@@ -5025,7 +5025,7 @@
         <v>NEUFELD</v>
       </c>
       <c r="F24" s="108" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="G24" s="108" t="str">
         <f>'Nach Mannschaften sortiert'!H24</f>
@@ -5401,7 +5401,7 @@
         <v>OBERWART</v>
       </c>
       <c r="F34" s="108" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="G34" s="108" t="str">
         <f>'Nach Mannschaften sortiert'!H34</f>
@@ -5707,7 +5707,7 @@
         <v>PARNDORF</v>
       </c>
       <c r="F42" s="108" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="G42" s="108" t="str">
         <f>'Nach Mannschaften sortiert'!H42</f>
@@ -6033,15 +6033,15 @@
     <row r="51" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B51" s="105">
         <f>'Nach Mannschaften sortiert'!D51</f>
-        <v>46158</v>
+        <v>46173</v>
       </c>
       <c r="C51" s="39">
         <f>'Nach Mannschaften sortiert'!E51</f>
-        <v>0.625</v>
+        <v>0.58333333333333337</v>
       </c>
       <c r="D51" s="39">
         <f t="shared" si="0"/>
-        <v>0.6875</v>
+        <v>0.64583333333333337</v>
       </c>
       <c r="E51" s="39" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F51)</f>
@@ -6060,7 +6060,7 @@
         <v>U14</v>
       </c>
       <c r="J51" s="108" t="s">
-        <v>221</v>
+        <v>144</v>
       </c>
       <c r="K51" t="s">
         <v>157</v>
@@ -6083,6 +6083,9 @@
         <f>UPPER('Nach Mannschaften sortiert'!F52)</f>
         <v>NEUFELD</v>
       </c>
+      <c r="F52" s="108" t="s">
+        <v>226</v>
+      </c>
       <c r="G52" s="108" t="str">
         <f>'Nach Mannschaften sortiert'!H52</f>
         <v>Heim</v>
@@ -6109,11 +6112,11 @@
       </c>
       <c r="C53" s="39">
         <f>'Nach Mannschaften sortiert'!E53</f>
-        <v>0.79166666666666663</v>
+        <v>0.8125</v>
       </c>
       <c r="D53" s="39">
         <f t="shared" si="0"/>
-        <v>0.85416666666666663</v>
+        <v>0.875</v>
       </c>
       <c r="E53" s="39" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F53)</f>
@@ -6633,15 +6636,15 @@
     <row r="67" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B67" s="105">
         <f>'Nach Mannschaften sortiert'!D67</f>
-        <v>46159</v>
+        <v>46169</v>
       </c>
       <c r="C67" s="39">
         <f>'Nach Mannschaften sortiert'!E67</f>
-        <v>0.58333333333333337</v>
+        <v>0.75</v>
       </c>
       <c r="D67" s="39">
         <f t="shared" ref="D67:D83" si="2">IF(I67 = "KM",C67+"1:45",IF(I67="U23",C67+"1:45",IF(I67 = "U16",C67+"1:45",IF(I67 = "U15",C67+"1:30",IF(I67 = "U14",C67+"1:30",IF(I67 = "U13",C67+"1:35",IF(I67 = "U12",C67+"1:10",IF(I67 = "U11",C67+"1:10",IF(I67 = "U10",C67+"1:03",C67+"3:00")))))))))</f>
-        <v>0.63194444444444453</v>
+        <v>0.79861111111111116</v>
       </c>
       <c r="E67" s="39" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F67)</f>
@@ -9575,7 +9578,7 @@
       </c>
       <c r="E43" s="38">
         <f>'Nach Mannschaften sortiert'!E53</f>
-        <v>0.79166666666666663</v>
+        <v>0.8125</v>
       </c>
       <c r="F43" s="2" t="str">
         <f>'Nach Mannschaften sortiert'!F53</f>
@@ -10149,11 +10152,11 @@
       </c>
       <c r="D60" s="61">
         <f>'Nach Mannschaften sortiert'!D51</f>
-        <v>46158</v>
+        <v>46173</v>
       </c>
       <c r="E60" s="62">
         <f>'Nach Mannschaften sortiert'!E51</f>
-        <v>0.625</v>
+        <v>0.58333333333333337</v>
       </c>
       <c r="F60" s="60" t="str">
         <f>'Nach Mannschaften sortiert'!F51</f>
@@ -10183,11 +10186,11 @@
       </c>
       <c r="D61" s="16">
         <f>'Nach Mannschaften sortiert'!D67</f>
-        <v>46159</v>
+        <v>46169</v>
       </c>
       <c r="E61" s="38">
         <f>'Nach Mannschaften sortiert'!E67</f>
-        <v>0.58333333333333337</v>
+        <v>0.75</v>
       </c>
       <c r="F61" s="2" t="str">
         <f>'Nach Mannschaften sortiert'!F67</f>
@@ -13574,7 +13577,7 @@
       </c>
       <c r="B60" s="72">
         <f>Heimspiele!D61</f>
-        <v>46159</v>
+        <v>46169</v>
       </c>
       <c r="C60" s="72"/>
       <c r="D60" t="str">
@@ -14171,11 +14174,11 @@
       </c>
       <c r="B74" s="81">
         <f>Heimspiele!D60</f>
-        <v>46158</v>
+        <v>46173</v>
       </c>
       <c r="C74" s="82">
         <f>Heimspiele!E60</f>
-        <v>0.625</v>
+        <v>0.58333333333333337</v>
       </c>
       <c r="D74" s="80" t="str">
         <f>Heimspiele!F60</f>

--- a/Terminefussball_2026_Frühjahr.xlsx
+++ b/Terminefussball_2026_Frühjahr.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DTB\asv-neufeld\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7296229-E290-42CE-ABDC-D7A6BCA8F022}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3D354CD-7940-4823-A223-78127EC56A0C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="827" uniqueCount="227">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="832" uniqueCount="231">
   <si>
     <t>Mannschaft</t>
   </si>
@@ -726,6 +726,18 @@
   </si>
   <si>
     <t>Endstand 4:0 für Kittsee</t>
+  </si>
+  <si>
+    <t>Endstand 3:1 für Wimpassing</t>
+  </si>
+  <si>
+    <t>Großhöflein wollte nicht verschieben - daher 3:0 für Großhöflein, wir hatten zu wenige Spieler. (Verletzungen und Turniere der U14 und U16)</t>
+  </si>
+  <si>
+    <t>5:0 für Eisenstadt</t>
+  </si>
+  <si>
+    <t>12:4 für Klimpuh Juniors</t>
   </si>
 </sst>
 </file>
@@ -4575,6 +4587,9 @@
         <f>UPPER('Nach Mannschaften sortiert'!F12)</f>
         <v>WIMPASSING</v>
       </c>
+      <c r="F12" s="108" t="s">
+        <v>200</v>
+      </c>
       <c r="G12" s="108" t="str">
         <f>'Nach Mannschaften sortiert'!H12</f>
         <v>Auswärts</v>
@@ -5062,6 +5077,9 @@
         <f>UPPER('Nach Mannschaften sortiert'!F25)</f>
         <v>WIMPASSING</v>
       </c>
+      <c r="F25" s="108" t="s">
+        <v>227</v>
+      </c>
       <c r="G25" s="108" t="str">
         <f>'Nach Mannschaften sortiert'!H25</f>
         <v>Auswärts</v>
@@ -5745,6 +5763,9 @@
         <f>UPPER('Nach Mannschaften sortiert'!F43)</f>
         <v>GROßHÖFLEIN</v>
       </c>
+      <c r="F43" s="108" t="s">
+        <v>228</v>
+      </c>
       <c r="G43" s="108" t="str">
         <f>'Nach Mannschaften sortiert'!H43</f>
         <v>Auswärts</v>
@@ -6350,6 +6371,9 @@
         <f>UPPER('Nach Mannschaften sortiert'!F59)</f>
         <v>NEUFELD</v>
       </c>
+      <c r="F59" s="108" t="s">
+        <v>229</v>
+      </c>
       <c r="G59" s="108" t="str">
         <f>'Nach Mannschaften sortiert'!H59</f>
         <v>Heim</v>
@@ -6685,6 +6709,9 @@
       <c r="E68" s="39" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F68)</f>
         <v>NEUFELD</v>
+      </c>
+      <c r="F68" s="108" t="s">
+        <v>230</v>
       </c>
       <c r="G68" s="108" t="str">
         <f>'Nach Mannschaften sortiert'!H68</f>

--- a/Terminefussball_2026_Frühjahr.xlsx
+++ b/Terminefussball_2026_Frühjahr.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DTB\asv-neufeld\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3D354CD-7940-4823-A223-78127EC56A0C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F860A76-E005-48DD-96B5-E3A887C9E486}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="832" uniqueCount="231">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="835" uniqueCount="233">
   <si>
     <t>Mannschaft</t>
   </si>
@@ -737,7 +737,13 @@
     <t>5:0 für Eisenstadt</t>
   </si>
   <si>
-    <t>12:4 für Klimpuh Juniors</t>
+    <t>Endstand 6:2 für Margarethen</t>
+  </si>
+  <si>
+    <t>Endstand 12:4 für Klimpuh Juniors</t>
+  </si>
+  <si>
+    <t>Endstand 3:2 für Neufeld</t>
   </si>
 </sst>
 </file>
@@ -6143,6 +6149,9 @@
         <f>UPPER('Nach Mannschaften sortiert'!F53)</f>
         <v>LEITHAPRODERSDORF</v>
       </c>
+      <c r="F53" s="108" t="s">
+        <v>204</v>
+      </c>
       <c r="G53" s="108" t="str">
         <f>'Nach Mannschaften sortiert'!H53</f>
         <v>Auswärts</v>
@@ -6674,6 +6683,9 @@
         <f>UPPER('Nach Mannschaften sortiert'!F67)</f>
         <v>ST. MARGARETHEN</v>
       </c>
+      <c r="F67" s="108" t="s">
+        <v>230</v>
+      </c>
       <c r="G67" s="108" t="str">
         <f>'Nach Mannschaften sortiert'!H67</f>
         <v>Auswärts</v>
@@ -6711,7 +6723,7 @@
         <v>NEUFELD</v>
       </c>
       <c r="F68" s="108" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="G68" s="108" t="str">
         <f>'Nach Mannschaften sortiert'!H68</f>
@@ -6748,6 +6760,9 @@
       <c r="E69" s="39" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F69)</f>
         <v>STOTZING</v>
+      </c>
+      <c r="F69" s="108" t="s">
+        <v>232</v>
       </c>
       <c r="G69" s="108" t="str">
         <f>'Nach Mannschaften sortiert'!H69</f>

--- a/Terminefussball_2026_Frühjahr.xlsx
+++ b/Terminefussball_2026_Frühjahr.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DTB\asv-neufeld\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F860A76-E005-48DD-96B5-E3A887C9E486}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F9D8138-69CD-4B31-956C-9886F8954F78}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="835" uniqueCount="233">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="837" uniqueCount="233">
   <si>
     <t>Mannschaft</t>
   </si>
@@ -4632,6 +4632,9 @@
         <f>UPPER('Nach Mannschaften sortiert'!F13)</f>
         <v>WINDEN</v>
       </c>
+      <c r="F13" s="108" t="s">
+        <v>219</v>
+      </c>
       <c r="G13" s="108" t="str">
         <f>'Nach Mannschaften sortiert'!H13</f>
         <v>Auswärts</v>
@@ -5120,6 +5123,9 @@
       <c r="E26" s="39" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F26)</f>
         <v>WINDEN</v>
+      </c>
+      <c r="F26" s="108" t="s">
+        <v>232</v>
       </c>
       <c r="G26" s="108" t="str">
         <f>'Nach Mannschaften sortiert'!H26</f>

--- a/Terminefussball_2026_Frühjahr.xlsx
+++ b/Terminefussball_2026_Frühjahr.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DTB\asv-neufeld\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F9D8138-69CD-4B31-956C-9886F8954F78}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4DAACE6F-4099-4B90-A12C-7BB3F2B1913A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="837" uniqueCount="233">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="841" uniqueCount="235">
   <si>
     <t>Mannschaft</t>
   </si>
@@ -734,9 +734,6 @@
     <t>Großhöflein wollte nicht verschieben - daher 3:0 für Großhöflein, wir hatten zu wenige Spieler. (Verletzungen und Turniere der U14 und U16)</t>
   </si>
   <si>
-    <t>5:0 für Eisenstadt</t>
-  </si>
-  <si>
     <t>Endstand 6:2 für Margarethen</t>
   </si>
   <si>
@@ -744,6 +741,15 @@
   </si>
   <si>
     <t>Endstand 3:2 für Neufeld</t>
+  </si>
+  <si>
+    <t>Endstand 5:0 für Eisenstadt</t>
+  </si>
+  <si>
+    <t>Endstand 2:0 für Neusiedl</t>
+  </si>
+  <si>
+    <t>Endstand 5:2 für SPG DER CLUB</t>
   </si>
 </sst>
 </file>
@@ -5125,7 +5131,7 @@
         <v>WINDEN</v>
       </c>
       <c r="F26" s="108" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="G26" s="108" t="str">
         <f>'Nach Mannschaften sortiert'!H26</f>
@@ -5508,6 +5514,9 @@
         <f>UPPER('Nach Mannschaften sortiert'!F36)</f>
         <v>KIRCHSCHLAG</v>
       </c>
+      <c r="F36" s="108" t="s">
+        <v>234</v>
+      </c>
       <c r="G36" s="108" t="str">
         <f>'Nach Mannschaften sortiert'!H36</f>
         <v>Auswärts</v>
@@ -5814,6 +5823,9 @@
         <f>UPPER('Nach Mannschaften sortiert'!F44)</f>
         <v>WIMPASSING</v>
       </c>
+      <c r="F44" s="108" t="s">
+        <v>233</v>
+      </c>
       <c r="G44" s="108" t="str">
         <f>'Nach Mannschaften sortiert'!H44</f>
         <v>Heim</v>
@@ -6080,6 +6092,9 @@
         <f>UPPER('Nach Mannschaften sortiert'!F51)</f>
         <v>NEUFELD</v>
       </c>
+      <c r="F51" s="108" t="s">
+        <v>193</v>
+      </c>
       <c r="G51" s="108" t="str">
         <f>'Nach Mannschaften sortiert'!H51</f>
         <v>Heim</v>
@@ -6387,7 +6402,7 @@
         <v>NEUFELD</v>
       </c>
       <c r="F59" s="108" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="G59" s="108" t="str">
         <f>'Nach Mannschaften sortiert'!H59</f>
@@ -6425,6 +6440,9 @@
         <f>UPPER('Nach Mannschaften sortiert'!F60)</f>
         <v>BREITENBRUNN</v>
       </c>
+      <c r="F60" s="108" t="s">
+        <v>205</v>
+      </c>
       <c r="G60" s="108" t="str">
         <f>'Nach Mannschaften sortiert'!H60</f>
         <v>Auswärts</v>
@@ -6690,7 +6708,7 @@
         <v>ST. MARGARETHEN</v>
       </c>
       <c r="F67" s="108" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="G67" s="108" t="str">
         <f>'Nach Mannschaften sortiert'!H67</f>
@@ -6729,7 +6747,7 @@
         <v>NEUFELD</v>
       </c>
       <c r="F68" s="108" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="G68" s="108" t="str">
         <f>'Nach Mannschaften sortiert'!H68</f>
@@ -6768,7 +6786,7 @@
         <v>STOTZING</v>
       </c>
       <c r="F69" s="108" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="G69" s="108" t="str">
         <f>'Nach Mannschaften sortiert'!H69</f>

--- a/Terminefussball_2026_Frühjahr.xlsx
+++ b/Terminefussball_2026_Frühjahr.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DTB\asv-neufeld\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4DAACE6F-4099-4B90-A12C-7BB3F2B1913A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EDAAD00C-D181-4BF6-8BA5-D8976024A8CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="841" uniqueCount="235">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="846" uniqueCount="239">
   <si>
     <t>Mannschaft</t>
   </si>
@@ -750,6 +750,18 @@
   </si>
   <si>
     <t>Endstand 5:2 für SPG DER CLUB</t>
+  </si>
+  <si>
+    <t>Endstand 2:1 für Neufeld</t>
+  </si>
+  <si>
+    <t>Endstand 6:2 für St. Georgen</t>
+  </si>
+  <si>
+    <t>Endstand 4:0 für Neufeld</t>
+  </si>
+  <si>
+    <t>Endstand 2:0 für Leithaprodersdorf</t>
   </si>
 </sst>
 </file>
@@ -4677,6 +4689,9 @@
         <f>UPPER('Nach Mannschaften sortiert'!F14)</f>
         <v>NEUFELD</v>
       </c>
+      <c r="F14" s="108" t="s">
+        <v>235</v>
+      </c>
       <c r="G14" s="108" t="str">
         <f>'Nach Mannschaften sortiert'!H14</f>
         <v>Heim</v>
@@ -5168,6 +5183,9 @@
         <f>UPPER('Nach Mannschaften sortiert'!F27)</f>
         <v>NEUFELD</v>
       </c>
+      <c r="F27" s="108" t="s">
+        <v>226</v>
+      </c>
       <c r="G27" s="108" t="str">
         <f>'Nach Mannschaften sortiert'!H27</f>
         <v>Heim</v>
@@ -5553,6 +5571,9 @@
         <f>UPPER('Nach Mannschaften sortiert'!F37)</f>
         <v>NEUFELD</v>
       </c>
+      <c r="F37" s="108" t="s">
+        <v>236</v>
+      </c>
       <c r="G37" s="108" t="str">
         <f>'Nach Mannschaften sortiert'!H37</f>
         <v>Heim</v>
@@ -5862,6 +5883,9 @@
         <f>UPPER('Nach Mannschaften sortiert'!F45)</f>
         <v>WIESEN</v>
       </c>
+      <c r="F45" s="108" t="s">
+        <v>237</v>
+      </c>
       <c r="G45" s="108" t="str">
         <f>'Nach Mannschaften sortiert'!H45</f>
         <v>Auswärts</v>
@@ -6478,6 +6502,9 @@
       <c r="E61" s="39" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F61)</f>
         <v>NEUFELD</v>
+      </c>
+      <c r="F61" s="108" t="s">
+        <v>238</v>
       </c>
       <c r="G61" s="108" t="str">
         <f>'Nach Mannschaften sortiert'!H61</f>

--- a/Terminefussball_2026_Frühjahr.xlsx
+++ b/Terminefussball_2026_Frühjahr.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DTB\asv-neufeld\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EDAAD00C-D181-4BF6-8BA5-D8976024A8CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71AE699A-7DE4-4154-9586-85BC439B4825}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="846" uniqueCount="239">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="849" uniqueCount="242">
   <si>
     <t>Mannschaft</t>
   </si>
@@ -762,6 +762,15 @@
   </si>
   <si>
     <t>Endstand 2:0 für Leithaprodersdorf</t>
+  </si>
+  <si>
+    <t>Qualifikationsturnier zum Geza Gallos Gedenturnier</t>
+  </si>
+  <si>
+    <t>16 Mannschaften</t>
+  </si>
+  <si>
+    <t>Sieger TWL-Elektra zweiter Wiener Sportclu Dritter SV Donau Luckylooser FC A11 Rapid Oberlaa</t>
   </si>
 </sst>
 </file>
@@ -7499,13 +7508,11 @@
         <f>'Nach Mannschaften sortiert'!H88</f>
         <v>Heim</v>
       </c>
-      <c r="H88" t="str">
-        <f>'Nach Mannschaften sortiert'!G88</f>
-        <v>viele Gegner</v>
-      </c>
-      <c r="I88" t="str">
-        <f>'Nach Mannschaften sortiert'!C88</f>
-        <v>GGG</v>
+      <c r="H88" t="s">
+        <v>240</v>
+      </c>
+      <c r="I88" t="s">
+        <v>239</v>
       </c>
       <c r="J88" s="108" t="s">
         <v>144</v>
@@ -7529,6 +7536,9 @@
       <c r="E89" s="39" t="str">
         <f>UPPER('Nach Mannschaften sortiert'!F89)</f>
         <v>NEUFELD</v>
+      </c>
+      <c r="F89" s="108" t="s">
+        <v>241</v>
       </c>
       <c r="G89" s="108" t="str">
         <f>'Nach Mannschaften sortiert'!H89</f>

--- a/Terminefussball_2026_Frühjahr.xlsx
+++ b/Terminefussball_2026_Frühjahr.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DTB\asv-neufeld\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71AE699A-7DE4-4154-9586-85BC439B4825}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3DF8A83A-4951-4EBA-B561-12DF2136774C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="849" uniqueCount="242">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="849" uniqueCount="243">
   <si>
     <t>Mannschaft</t>
   </si>
@@ -771,6 +771,9 @@
   </si>
   <si>
     <t>Sieger TWL-Elektra zweiter Wiener Sportclu Dritter SV Donau Luckylooser FC A11 Rapid Oberlaa</t>
+  </si>
+  <si>
+    <t>abgesagz</t>
   </si>
 </sst>
 </file>
@@ -6255,7 +6258,7 @@
         <v>U13</v>
       </c>
       <c r="J54" s="108" t="s">
-        <v>144</v>
+        <v>242</v>
       </c>
       <c r="K54" t="s">
         <v>157</v>

--- a/Terminefussball_2026_Frühjahr.xlsx
+++ b/Terminefussball_2026_Frühjahr.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DTB\asv-neufeld\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3DF8A83A-4951-4EBA-B561-12DF2136774C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{429D6FD2-AD96-45B9-96EA-D00777D0D76E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="849" uniqueCount="243">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="850" uniqueCount="244">
   <si>
     <t>Mannschaft</t>
   </si>
@@ -774,6 +774,9 @@
   </si>
   <si>
     <t>abgesagz</t>
+  </si>
+  <si>
+    <t>Spiel abgesagt</t>
   </si>
 </sst>
 </file>
@@ -6245,6 +6248,9 @@
         <f>UPPER('Nach Mannschaften sortiert'!F54)</f>
         <v>NEUFELD</v>
       </c>
+      <c r="F54" s="108" t="s">
+        <v>243</v>
+      </c>
       <c r="G54" s="108" t="str">
         <f>'Nach Mannschaften sortiert'!H54</f>
         <v>Heim</v>

--- a/Terminefussball_2026_Frühjahr.xlsx
+++ b/Terminefussball_2026_Frühjahr.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DTB\asv-neufeld\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{429D6FD2-AD96-45B9-96EA-D00777D0D76E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8CC7DA4B-1AB1-4638-9D58-F1BB6873CBB1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -773,10 +773,10 @@
     <t>Sieger TWL-Elektra zweiter Wiener Sportclu Dritter SV Donau Luckylooser FC A11 Rapid Oberlaa</t>
   </si>
   <si>
-    <t>abgesagz</t>
-  </si>
-  <si>
     <t>Spiel abgesagt</t>
+  </si>
+  <si>
+    <t>abgesagt</t>
   </si>
 </sst>
 </file>
@@ -6249,7 +6249,7 @@
         <v>NEUFELD</v>
       </c>
       <c r="F54" s="108" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="G54" s="108" t="str">
         <f>'Nach Mannschaften sortiert'!H54</f>
@@ -6264,7 +6264,7 @@
         <v>U13</v>
       </c>
       <c r="J54" s="108" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="K54" t="s">
         <v>157</v>
